--- a/Work_and_Travel_Master_Job_Database_2027.xlsx
+++ b/Work_and_Travel_Master_Job_Database_2027.xlsx
@@ -472,10 +472,10 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="47" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="114" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="132" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ทิป (Tips / Bonus)</t>
+          <t>ทิป ($/สัปดาห์)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>ฐาน .00 / OT .00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>ทิปหัวเตียง ~ -  / สัปดาห์</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR ตักไม่อั้น 7 วัน, รถรับส่งพนักงาน, ส่วนลดทัวร์/รถไฟ 50%</t>
+          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR ตักไม่อั้น 7 วัน, ทิปหัวเตียง, รถรับส่งพนักงาน, ส่วนลดทัวร์/รถไฟ 50%</t>
         </is>
       </c>
     </row>
@@ -595,12 +595,12 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>ฐาน .00 / OT .00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>ไม่มี ()</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -642,12 +642,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>ฐาน .00 / OT .00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>ไม่มี (ได้กินอาหารในครัวฟรี)</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -689,12 +689,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>ฐาน .50 / OT .25</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>💵 ทิปสดจากทัวร์ ~ -  / สัปดาห์</t>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>$40 - $70</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, ได้ทิปเงินสดจากกรุ๊ปทัวร์ผู้สูงอายุ</t>
+          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, ทิปเงินสดจากกรุ๊ปทัวร์ผู้สูงอายุ</t>
         </is>
       </c>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>ฐาน .00 / OT .50</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>🎁 โบนัส +.00/ชม. ท้ายทริป (ครบสัญญา)</t>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$140</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>รถชัตเติลบัสขึ้น-ลงเขา Sugarloaf, ส่วนลดอาหารร้าน The Perk, วิวหุบเขาสวย</t>
+          <t>โบนัสพิเศษ +$1.00/ชม. ท้ายทริป (ครบสัญญา), รถชัตเติลบัสขึ้น-ลงเขา Sugarloaf, ส่วนลดอาหารร้าน The Perk</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>ฐาน .50 / OT .25</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>🎁 โบนัส +.00/ชม. ท้ายทริป (ครบสัญญา)</t>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$140</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>โรงแรมหรู 4 ดาวบนยอดเขา, รถชัตเติลบัสรับส่ง, ส่วนลดอาหารห้องอาหาร Alpenglow</t>
+          <t>โบนัสพิเศษ +$1.00/ชม. ท้ายทริป (ครบสัญญา), โรงแรมหรู 4 ดาว, รถชัตเติลบัส, ส่วนลดอาหารห้องอาหาร Alpenglow</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>ฐาน .00 / OT .00</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>💵 Tip Out สด ~ -  / คืน</t>
+          <t>ฐาน $14.00 / OT $21.00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>$200 - $350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$140</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>โบนัส +.00/ชม. ท้ายทริป, ได้ทิปเงินสดจากแขกไฮเอนด์ร้านอาหารวิวพาโนรามา</t>
+          <t>โบนัสพิเศษ +$1.00/ชม. ท้ายทริป, ทิปเงินสดจากแขกไฮเอนด์ร้านอาหารวิวพาโนรามา ($40-$70/คืน)</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>ฐาน .00 / OT .00</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>ทิปหัวเตียง ~ -  / สัปดาห์</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>$10 - $20</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, ชมวิวยอดเขาเดนาลี บรรยากาศสงบ ไม่กดดัน</t>
+          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, รถรับส่งพนักงาน, ชมวิวยอดเขาเดนาลี บรรยากาศสงบ</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>ฐาน .50 / OT .25</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>ทิปเฉพาะ F&amp;B ~ -  / สัปดาห์</t>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>$20 - $40</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>ฐาน .75 / OT .62</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>ไม่มี (เน้นค่าแรงฐานสูงสุด)</t>
+          <t>ฐาน $17.75 / OT $26.62</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (หอพักฟรี!) + ค่าอาหาร EDR /wk</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>หอพักฟรี 100%, อาหารบุฟเฟต์ 3 มื้อ EDR, ส่วนลดซื้อของ 40%, เข้าอุทยาน Grand Teton &amp; Yellowstone ฟรี</t>
+          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), ส่วนลดซื้อของ 40%, เข้าอุทยาน Grand Teton &amp; Yellowstone ฟรี</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>ฐาน .75 / OT .62</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>ไม่มี (กินฟรีในครัว)</t>
+          <t>ฐาน $17.75 / OT $26.62</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> (หอพักฟรี!) + ค่าอาหาร EDR /wk</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>หอพักฟรี 100%, อาหาร 3 มื้อ EDR + กินฟรีในครัว, สิทธิประโยชน์เครือ Vail Resorts</t>
+          <t>หอพักฟรี 100%! + อาหาร 3 มื้อ EDR + กินฟรีในครัว, สิทธิประโยชน์เครือ Vail Resorts</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>ฐาน .70 / OT .55</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>ไม่มี ()</t>
+          <t>ฐาน $15.70 / OT $23.55</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1080,12 +1080,12 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์ (รวมหอพัก+อาหาร 3 มื้อ)</t>
+          <t>$120</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>หอพักใหม่ Arnica Development + บุฟเฟต์ 3 มื้อ EDR, เที่ยวบ่อน้ำพุร้อนและไกเซอร์ฟรี</t>
+          <t>รวมหอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR, หอพักใหม่ Arnica, เที่ยวบ่อน้ำพุร้อนและไกเซอร์ Yellowstone ฟรี</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>ฐาน .50 / OT .75</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>💵 ทิปสด ~ -  / สัปดาห์</t>
+          <t>ฐาน $16.50 / OT $24.75</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>$50 - $100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1127,12 +1127,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>แคมป์กระโจมซาฟารีหรู, อาหารพนักงาน, แขกไฮเอนด์ ทิปเงินสดดี บรรยากาศเป็นกันเอง</t>
+          <t>แคมป์กระโจมซาฟารีหรู, อาหารพนักงาน, ทิปเงินสดจากแขกไฮเอนด์ บรรยากาศเป็นกันเอง</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>ฐาน .00 / OT .50</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>ไม่มี ()</t>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>ฐาน .00 – .00</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>💵 ทิปสด  -  / คืน</t>
+          <t>ฐาน $12.00 – $14.00</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>$250 - $500</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>ทำควบกับงานหลัก</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>รับทิปเงินสดทุกคืน ยัดกระเป๋ากลับห้องทันที, อาหารพนักงานในกะ</t>
+          <t>รับทิปเงินสดทุกคืน ยัดกระเป๋ากลับห้องทันที ($50-$100/คืน), อาหารพนักงานในกะ (ทำควบกับงานหลัก)</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>ฐาน .00 / OT .50</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>ไม่มี (ปลอดภาษีรัฐ 0%)</t>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$110</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>นั่งรถราง Pigeon Forge Trolley -.50/วัน, บัตรเข้าสวนสนุก Dollywood &amp; Splash Country ฟรี</t>
+          <t>ปลอดภาษีเงินได้รัฐ 0%, นั่งรถราง Pigeon Forge Trolley $1-$2.50/วัน, บัตรเข้าสวนสนุก Dollywood &amp; Splash Country ฟรี</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>ฐาน .00 / OT .00</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>ไม่มี (เน้นการันตี OT)</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$120</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>การันตีชั่วโมง OT สม่ำเสมอ ไม่ผันผวนตามนักท่องเที่ยว, อพาร์ตเมนต์แชร์กับเพื่อน</t>
+          <t>การันตีชั่วโมง OT สม่ำเสมอ 10-14 ชม./สัปดาห์ ไม่ผันผวนตามนักท่องเที่ยว, อพาร์ตเมนต์แชร์กับเพื่อน</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>ฐาน .50 / OT .75</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>ไม่มี ()</t>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> / สัปดาห์</t>
+          <t>$80</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>หอพักราคาถูกมาก (/wk), รถบัสรับส่งฟรี, บัตรเล่นเครื่องเล่นสวนสนุกระดับโลกฟรี</t>
+          <t>หอพักราคาถูกมาก ($80/wk), รถบัสรับส่งฟรี, บัตรเล่นเครื่องเล่นสวนสนุกระดับโลกฟรี</t>
         </is>
       </c>
     </row>

--- a/Work_and_Travel_Master_Job_Database_2027.xlsx
+++ b/Work_and_Travel_Master_Job_Database_2027.xlsx
@@ -82,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -93,11 +93,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,18 +470,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="132" customWidth="1" min="9" max="9"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="132" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,25 +508,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>เวลาทำงานจริง (ช่วงปกติ / ช่วงพีค)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>ค่าแรงฐาน / OT ($/ชม.)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ทิป ($/สัปดาห์)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ชั่วโมงทำงานจริง (คิดเผื่อหัว-ท้ายซีซัน)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ค่าที่พัก ($/สัปดาห์)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>สวัสดิการ (อาหาร ฟรี หรือ อื่นๆ)</t>
         </is>
@@ -546,76 +558,88 @@
           <t>Housekeeping / Room Attendant</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:30 – 15:30 น. (8 ชม.)
+พีค: 07:00 – 17:30 น. (10 ชม. ควงกะ)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>$15 - $30</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>50 – 54 ชม./สัปดาห์ (พีค 58-62 ชม. / หัวท้าย 35-42 ชม.)</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR ตักไม่อั้น 7 วัน, ทิปหัวเตียง, รถรับส่งพนักงาน, ส่วนลดทัวร์/รถไฟ 50%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Denali Princess Wilderness Lodge</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Alaska (AK)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Acadex, OEG, IEE, Higher</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Motor Coach / Fleet Detailer (ล้างรถทัวร์กะดึก)</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Kitchen Stewarding / Dishwasher (ล้างจาน)</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 16:00 – 00:00 น. (8 ชม.)
+พีค: 15:00 – 01:30 น. (10.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>52 – 56 ชม./สัปดาห์ (กะดึก 21:00-02:00 OT ดกมาก)</t>
-        </is>
-      </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
+          <t>50 – 55 ชม./สัปดาห์ (ควงกะค่ำได้ง่าย)</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, กลางวันว่างนอนพักผ่อนหรือเดินป่าได้ทั้งวัน</t>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>อาหารบุฟเฟต์ 3 มื้อใน EDR + เชฟทำสเต๊ก/เบอร์เกอร์เลี้ยงในครัวฟรีทุกกะ</t>
         </is>
       </c>
     </row>
@@ -637,79 +661,91 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Kitchen Stewarding / Dishwasher (ล้างจาน)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
+          <t>Luggage Handler (พนักงานยกกระเป๋าทัวร์)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 น. หรือ 12:00 – 20:30 น.
+พีค: 07:00 – 18:30 น. (ตามรอบรถไฟ)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>$40 - $70</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>46 – 52 ชม./สัปดาห์</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, ทิปเงินสดจากกรุ๊ปทัวร์ผู้สูงอายุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Denali Princess Wilderness Lodge</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Alaska (AK)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>ขอทำเพิ่มหน้างาน (Internal 2nd Job)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Fleet Detailer (งานเสริมล้างรถทัวร์กะดึก)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 21:00 – 01:30 น. (4.5 ชม.)
+พีค: 21:00 – 02:30 น. (5.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>คิดเรต OT $24.00/ชม. ทันที</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>50 – 55 ชม./สัปดาห์ (ควงกะค่ำได้ง่าย)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>$105</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อใน EDR + เชฟทำสเต๊ก/เบอร์เกอร์เลี้ยงในครัวฟรีทุกกะ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Denali Princess Wilderness Lodge</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Acadex, OEG, IEE, Higher</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Luggage Handler (พนักงานยกกระเป๋าทัวร์)</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>$40 - $70</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>46 – 52 ชม./สัปดาห์</t>
-        </is>
-      </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>$105</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, ทิปเงินสดจากกรุ๊ปทัวร์ผู้สูงอายุ</t>
+          <t>20 – 25 ชม./สัปดาห์ (ทำควบหลังงานหลักแม่บ้าน)</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>นับเป็นชั่วโมง OT $24.00 ทั้งหมด, ทำงานในอู่รถบัส Princess, อาหาร EDR 3 มื้อ</t>
         </is>
       </c>
     </row>
@@ -734,74 +770,86 @@
           <t>Housekeeping / Laundry</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 น. (8 ชม.)
+พีค: 08:00 – 17:00 น. (9 ชม.)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>40 – 45 ชม./สัปดาห์ (หัวท้าย 32-38 ชม.)</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>โบนัสพิเศษ +$1.00/ชม. ท้ายทริป (ครบสัญญา), รถชัตเติลบัสขึ้น-ลงเขา Sugarloaf, ส่วนลดอาหารร้าน The Perk</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Grande Denali Lodge</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Alaska (AK)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Acadex Thailand</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Housekeeping / Public Area Cleaner</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 น. (8 ชม.)
+พีค: 07:30 – 17:00 น. (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>42 – 46 ชม./สัปดาห์ (หัวท้าย 35-40 ชม.)</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>โบนัสพิเศษ +$1.00/ชม. ท้ายทริป (ครบสัญญา), โรงแรมหรู 4 ดาว, รถชัตเติลบัส, ส่วนลดอาหารห้องอาหาร Alpenglow</t>
         </is>
@@ -828,74 +876,86 @@
           <t>Busser / Food Runner (Alpenglow Restaurant)</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 16:30 – 22:30 น. (6 ชม.)
+พีค: 16:00 – 23:30 น. (7.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>ฐาน $14.00 / OT $21.00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>$200 - $350</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>40 – 45 ชม./สัปดาห์</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>โบนัสพิเศษ +$1.00/ชม. ท้ายทริป, ทิปเงินสดจากแขกไฮเอนด์ร้านอาหารวิวพาโนรามา ($40-$70/คืน)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Mt. McKinley Princess Lodge</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Alaska (AK)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Higher, OEG, Acadex</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Housekeeping / Kitchen / Laundry</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 น. (8 ชม.)
+พีค: 07:30 – 17:00 น. (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>$10 - $20</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>44 – 48 ชม./สัปดาห์ (หัวท้าย 35-40 ชม.)</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, รถรับส่งพนักงาน, ชมวิวยอดเขาเดนาลี บรรยากาศสงบ</t>
         </is>
@@ -922,74 +982,86 @@
           <t>Food Runner / Laundry / Steward</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 06:30 – 14:30 น. หรือ 15:00 – 23:00 น.
+พีค: กะสลับตามรอบรถไฟ/เครื่องบิน 8 ชม.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>$20 - $40</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>36 – 40 ชม./สัปดาห์ (ไม่ค่อยมี OT)</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>หอพักในเมืองแฟร์แบงก์ส + รถชัตเติลบัส, ใกล้ Walmart และร้านอาหารไทย หางาน 2 ง่าย</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Grand Teton Lodge Company (GTLC)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Wyoming (WY)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Acadex, Higher, OEG, IEE</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Housekeeping / Crew Member</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 น. (8 ชม.)
+พีค: 07:00 – 17:30 น. (10 ชม. ควงกะ)</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>ฐาน $17.75 / OT $26.62</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>54 – 60 ชม./สัปดาห์ (พีค 60-64 ชม. / หัวท้าย 40 ชม.)</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), ส่วนลดซื้อของ 40%, เข้าอุทยาน Grand Teton &amp; Yellowstone ฟรี</t>
         </is>
@@ -1016,74 +1088,86 @@
           <t>Kitchen Crew / Dishwasher / Food Prep</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 06:00 – 14:30 น. หรือ 15:00 – 23:00 น.
+พีค: 14:00 – 00:30 น. (ช่วยจัดเลี้ยง Banquet)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>ฐาน $17.75 / OT $26.62</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>52 – 58 ชม./สัปดาห์ (ควงกะ Banquet ได้)</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>หอพักฟรี 100%! + อาหาร 3 มื้อ EDR + กินฟรีในครัว, สิทธิประโยชน์เครือ Vail Resorts</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Xanterra Yellowstone Lodges</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Wyoming/MT</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>OEG, IEE Thailand</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Hospitality Crew / Kitchen / Steward</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:00 – 15:30 น. หรือ 15:00 – 23:30 น.
+พีค: 06:30 – 16:30 น. (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>ฐาน $15.70 / OT $23.55</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>46 – 52 ชม./สัปดาห์ (หัวท้าย 38-42 ชม.)</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>$120</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>รวมหอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR, หอพักใหม่ Arnica, เที่ยวบ่อน้ำพุร้อนและไกเซอร์ Yellowstone ฟรี</t>
         </is>
@@ -1110,74 +1194,86 @@
           <t>Housekeeping / Guest Service</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 น. (8 ชม.)
+พีค: 08:00 – 17:30 น. (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>$50 - $100</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>42 – 46 ชม./สัปดาห์</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>$100</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>แคมป์กระโจมซาฟารีหรู, อาหารพนักงาน, ทิปเงินสดจากแขกไฮเอนด์ บรรยากาศเป็นกันเอง</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Kalahari Resorts &amp; Conventions</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Wisconsin (WI)</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>OEG, Acadex, Higher</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Lifeguard / Housekeeping (งานหลัก)</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 น. หรือ 12:00 – 20:30 น.
+พีค: 09:00 – 19:30 น. (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>38 – 44 ชม./สัปดาห์ (เกลี่ยกะ 40 ชม.)</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>หอพัก Kalahari Village, บัตรเล่นสวนน้ำฟรี, เมืองปั่นจักรยาน 100%, หางาน 2 ร้านอาหารง่าย</t>
         </is>
@@ -1204,74 +1300,86 @@
           <t>Barback / Busser / Runner (งานที่สอง)</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 17:30 – 22:30 น. (5 ชม.)
+พีค: 17:00 – 00:30 น. (7.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>ฐาน $12.00 – $14.00</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>$250 - $500</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>20 – 25 ชม./สัปดาห์ (กะค่ำ 17:30-23:00)</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>รับทิปเงินสดทุกคืน ยัดกระเป๋ากลับห้องทันที ($50-$100/คืน), อาหารพนักงานในกะ (ทำควบกับงานหลัก)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Dollywood Theme Park &amp; Resorts</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Tennessee (TN)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>New Step, Acadex</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Ride Operator / Food Service / Retail</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 น. (8 ชม.)
+พีค: 09:00 – 21:30 น. (12 ชม. สวนสนุกเปิดดึก)</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>44 – 50 ชม./สัปดาห์ (หัวท้าย 35-40 ชม.)</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>$110</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>ปลอดภาษีเงินได้รัฐ 0%, นั่งรถราง Pigeon Forge Trolley $1-$2.50/วัน, บัตรเข้าสวนสนุก Dollywood &amp; Splash Country ฟรี</t>
         </is>
@@ -1298,74 +1406,86 @@
           <t>Pool Lifeguard</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:30 – 19:30 น. (9 ชม.)
+พีค: 10:00 – 20:30 น. (10.5 ชม. สระเปิดยาว)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>50 – 54 ชม./สัปดาห์ (การันตี OT 10-14 ชม.)</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>$120</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>การันตีชั่วโมง OT สม่ำเสมอ 10-14 ชม./สัปดาห์ ไม่ผันผวนตามนักท่องเที่ยว, อพาร์ตเมนต์แชร์กับเพื่อน</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Cedar Point Amusement Park</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Ohio (OH)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>OEG, IEE Thailand</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Ride Operator / Food Service</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:30 น. (8 ชม.)
+พีค: 09:30 – 22:30 น. (12 ชม. สวนสนุกปิดดึก)</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>ฐาน $14.50 / OT $21.75</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>46 – 52 ชม./สัปดาห์ (หัวท้าย 38-42 ชม.)</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>$80</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>หอพักราคาถูกมาก ($80/wk), รถบัสรับส่งฟรี, บัตรเล่นเครื่องเล่นสวนสนุกระดับโลกฟรี</t>
         </is>

--- a/Work_and_Travel_Master_Job_Database_2027.xlsx
+++ b/Work_and_Travel_Master_Job_Database_2027.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WAT 2027 Jobs Masterlist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier S-A Jobs &amp; 2nd Options" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +37,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,8 +52,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2FE"/>
+        <bgColor rgb="00E0F2FE"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,27 +89,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -470,30 +486,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="54" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="132" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ชื่องาน / สถานที่ทำงาน (Employer)</t>
+          <t>Tier &amp; รัฐ (State)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>รัฐ (State)</t>
+          <t>ชื่องาน / สถานที่ทำงานหลัก (Employer)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -503,12 +535,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ตำแหน่ง (Position / Role)</t>
+          <t>ตำแหน่งงานหลัก (Role)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>เวลาทำงานจริง (ช่วงปกติ / ช่วงพีค)</t>
+          <t>⏱️ เวลาทำงานหลัก (ปกติ / พีค)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -523,7 +555,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>ชั่วโมงทำงานจริง (คิดเผื่อหัว-ท้ายซีซัน)</t>
+          <t>ชั่วโมงงานหลัก (ชม./wk)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -534,960 +566,3557 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>สวัสดิการ (อาหาร ฟรี หรือ อื่นๆ)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>🔥 งานที่สองที่ทำต่อได้จริง (ตัวเลือกที่ 1)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>🔥 งานที่สองที่ทำต่อได้จริง (ตัวเลือกที่ 2)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>🔥 งานที่สองที่ทำต่อได้จริง (ตัวเลือกที่ 3)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Denali Princess Wilderness Lodge</t>
+          <t>Tier S - Alaska (AK)</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+          <t>Denali Princess Wilderness Lodge (Denali NP)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Acadex, OEG, IEE, Higher</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Housekeeping / Room Attendant</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 07:30 – 15:30 น. (8 ชม.)
-พีค: 07:00 – 17:30 น. (10 ชม. ควงกะ)</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีค: 07:00 – 17:30 (10 ชม. ควงกะ)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>$15 - $30</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>50 – 54 ชม./สัปดาห์ (พีค 58-62 ชม. / หัวท้าย 35-42 ชม.)</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
+          <t>50 – 54 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR ตักไม่อั้น 7 วัน, ทิปหัวเตียง, รถรับส่งพนักงาน, ส่วนลดทัวร์/รถไฟ 50%</t>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR ตักไม่อั้น 7 วัน, ทิปหัวเตียง, รถรับส่งพนักงาน, ส่วนลดทัวร์ 50%</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>🚌 Fleet Detailer (ในโรงแรม): ล้างรถทัวร์กะดึก 21:00-01:30 น. ได้เรต OT $24.00/ชม. ทันที (ไม่ต้องขอสปอนเซอร์)</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>🍕 Prospectors Pizzeria: เดิน 10 นาที ล้างจาน/Barback 18:30-00:30 น. ($15/ชม. + ทิปสด $40-$70/คืน)</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>🍽️ Fannie Q’s Saloon (ในโรงแรม): ช่วยจัดเลี้ยง/Runner 17:00-22:00 น. ได้เรต OT $24/ชม. + ทิป</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Denali Princess Wilderness Lodge</t>
+          <t>Tier S - Alaska (AK)</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
+          <t>Denali Princess Wilderness Lodge (Denali NP)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Acadex, OEG, IEE, Higher</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Kitchen Stewarding / Dishwasher (ล้างจาน)</t>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Kitchen Stewarding / Dishwasher</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 16:00 – 00:00 น. (8 ชม.)
-พีค: 15:00 – 01:30 น. (10.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
+          <t>ปกติ: 16:00 – 00:00 (8 ชม.)
+พีค: 15:00 – 01:30 (10.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>50 – 55 ชม./สัปดาห์ (ควงกะค่ำได้ง่าย)</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
+          <t>50 – 55 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>อาหารบุฟเฟต์ 3 มื้อใน EDR + เชฟทำสเต๊ก/เบอร์เกอร์เลี้ยงในครัวฟรีทุกกะ</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>🧹 เช้าช่วยแม่บ้าน (Housekeeping): 08:30-14:30 น. ขอกะเช้าเพิ่มในโรงแรม ได้เรต OT $24/ชม.</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>🧳 Luggage Handler: ช่วยยกกระเป๋ารอบรถไฟเช้า 08:00-12:00 น. ได้ทิปสดจากทัวร์</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>🛍️ Denali Boardwalk Gift Shops: แคชเชียร์/จัดของกะสาย 09:00-14:00 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Denali Princess Wilderness Lodge</t>
+          <t>Tier S - Alaska (AK)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Acadex, OEG, IEE, Higher</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Luggage Handler (พนักงานยกกระเป๋าทัวร์)</t>
+          <t>Grande Denali Lodge &amp; Denali Bluffs Hotel</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Acadex Thailand</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Public Area</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 น. หรือ 12:00 – 20:30 น.
-พีค: 07:00 – 18:30 น. (ตามรอบรถไฟ)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>$40 - $70</t>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46 – 52 ชม./สัปดาห์</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>$105</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, ทิปเงินสดจากกรุ๊ปทัวร์ผู้สูงอายุ</t>
+          <t>42 – 46 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>$140</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>โบนัส +$1.00/ชม. ท้ายทริป, โรงแรมหรู 4 ดาวบนยอดเขา, รถชัตเติลบัส, ส่วนลดอาหาร</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>🍷 Alpenglow Restaurant (ในโรงแรม): Busser 17:00-23:00 น. ($14/ชม. + ทิปสดเศรษฐี $50-$80/คืน)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>🥪 Subway Denali / The Black Bear: นั่งชัตเติลลงเขาไปทำกะเย็น 17:00-22:00 น. ($15/ชม.)</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>🍽️ Denali Princess Kitchens: เดินลงเขา 15 นาที ล้างจานกะค่ำ 18:00-00:00 น. ($16/ชม.)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Denali Princess Wilderness Lodge</t>
+          <t>Tier S - Alaska (AK)</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>ขอทำเพิ่มหน้างาน (Internal 2nd Job)</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Fleet Detailer (งานเสริมล้างรถทัวร์กะดึก)</t>
+          <t>Mt. McKinley Princess Lodge (Trapper Creek)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Higher, OEG, Acadex</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Kitchen</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 21:00 – 01:30 น. (4.5 ชม.)
-พีค: 21:00 – 02:30 น. (5.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>คิดเรต OT $24.00/ชม. ทันที</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>$10 - $20</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>20 – 25 ชม./สัปดาห์ (ทำควบหลังงานหลักแม่บ้าน)</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>นับเป็นชั่วโมง OT $24.00 ทั้งหมด, ทำงานในอู่รถบัส Princess, อาหาร EDR 3 มื้อ</t>
+          <t>44 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, รถรับส่ง, ชมวิวยอดเขาเดนาลี บรรยากาศสงบ</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>🥩 20,320 Alaskan Grill (ในโรงแรม): Busser/Steward กะค่ำ 17:30-22:30 น. (เรต OT $24/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Northland Wood Fired Pizza (ในโรงแรม): ผู้ช่วยทำพิซซ่า/ครัว 16:30-21:30 น. (เรต OT $24/ชม.)</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>🥐 Talkeetna Roadhouse: นั่งรถตู้พนักงานเข้าเมือง Talkeetna ช่วยล้างจาน/ทำขนมวันหยุด</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Denali Bluffs Hotel</t>
+          <t>Tier S - Alaska (AK)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Acadex Thailand</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Housekeeping / Laundry</t>
+          <t>Fairbanks Princess Riverside Lodge</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>IEE, Acadex, Higher</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Food Runner / Laundry / Steward</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:00 น. (8 ชม.)
-พีค: 08:00 – 17:00 น. (9 ชม.)</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>ปกติ: 06:30 – 14:30 หรือ 15:00 – 23:00
+พีค: กะสลับตามรอบรถไฟ 8 ชม.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>$20 - $40</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40 – 45 ชม./สัปดาห์ (หัวท้าย 32-38 ชม.)</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>$140</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>โบนัสพิเศษ +$1.00/ชม. ท้ายทริป (ครบสัญญา), รถชัตเติลบัสขึ้น-ลงเขา Sugarloaf, ส่วนลดอาหารร้าน The Perk</t>
+          <t>36 – 40 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>หอพักในเมืองแฟร์แบงก์ส + รถชัตเติลบัส, ใกล้ Walmart และร้านอาหารไทย หางาน 2 ง่าย</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>🛒 Walmart Supercenter Fairbanks: จัดสต็อกสินค้า/แคชเชียร์ 16:30-22:30 น. ($16-$17/ชม. มีรถเมล์ผ่าน)</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>🍜 Pad Thai Restaurant / Thai House: ผู้ช่วยครัว/เสิร์ฟ 17:00-22:30 น. (ทิปสด + กินอาหารไทยฟรี)</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>🍺 The Pump House Restaurant: Busser/Dishwasher ร้านอาหารริมน้ำดัง 17:30-23:00 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Grande Denali Lodge</t>
+          <t>Tier S - Alaska (AK)</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Acadex Thailand</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Housekeeping / Public Area Cleaner</t>
+          <t>Seward Windsong Lodge &amp; Kenai Fjords Tours (Pursuit)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, ALC</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Tour Operations / F&amp;B</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:00 น. (8 ชม.)
-พีค: 07:30 – 17:00 น. (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>42 – 46 ชม./สัปดาห์ (หัวท้าย 35-40 ชม.)</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>$140</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>โบนัสพิเศษ +$1.00/ชม. ท้ายทริป (ครบสัญญา), โรงแรมหรู 4 ดาว, รถชัตเติลบัส, ส่วนลดอาหารห้องอาหาร Alpenglow</t>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายทะเล Seward ท่าเรือล่องเรือชมวาฬและธารน้ำแข็ง, หอพักพนักงาน, ล่องเรือฟรี</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>🦀 Ray’s Waterfront (ริมท่าเรือ Seward): Busser/Steward ร้านซีฟู้ดดัง 17:30-23:00 น. ($14/ชม. + ทิปสด $60-$100)</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Seward Brewing Company: Barback/Dishwasher กะค่ำ 18:00-00:00 น. ($15/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>🛥️ Kenai Fjords Boat Cleaning: ล้างทำความสะอาดเรือทัวร์รอบเย็น 18:00-21:30 น. ($16.50/ชม.)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Grande Denali Lodge</t>
+          <t>Tier S - Alaska (AK)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Acadex Thailand</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Busser / Food Runner (Alpenglow Restaurant)</t>
+          <t>Talkeetna Alaskan Lodge (Pursuit Collection)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, Higher</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Kitchen / Steward</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 16:30 – 22:30 น. (6 ชม.)
-พีค: 16:00 – 23:30 น. (7.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>ฐาน $14.00 / OT $21.00</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>$200 - $350</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40 – 45 ชม./สัปดาห์</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>$140</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>โบนัสพิเศษ +$1.00/ชม. ท้ายทริป, ทิปเงินสดจากแขกไฮเอนด์ร้านอาหารวิวพาโนรามา ($40-$70/คืน)</t>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>$115</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>โรงแรมหรูชมวิวยอดเขา Denali ในเมืองคาวบอย Talkeetna, หอพักพนักงาน + รถรับส่ง</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>🥩 Foraker Dining Room (ในโรงแรม): Busser ร้านอาหาร Fine Dining 17:30-23:00 น. (ทิปสด $50-$90/คืน)</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>🍕 Mountain High Pizza Pie: ผู้ช่วยทำพิซซ่า/ล้างจาน 18:00-23:30 น. ($15/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>🍺 Denali Brewing Company (Talkeetna Pub): Barback กะค่ำ 18:30-00:30 น. ($14/ชม. + ทิปสด)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Mt. McKinley Princess Lodge</t>
+          <t>Tier S - Alaska (AK)</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Higher, OEG, Acadex</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Housekeeping / Kitchen / Laundry</t>
+          <t>Alyeska Resort &amp; Hotel Alyeska (Girdwood)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Higher</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Culinary / Lift Ops</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:00 น. (8 ชม.)
-พีค: 07:30 – 17:00 น. (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>$10 - $20</t>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.50 / OT $24.75</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>44 – 48 ชม./สัปดาห์ (หัวท้าย 35-40 ชม.)</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>$105</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, รถรับส่งพนักงาน, ชมวิวยอดเขาเดนาลี บรรยากาศสงบ</t>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>$135</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>รีสอร์ตหรูระดับโลก นั่งกระเช้าชมวิวภูเขาและธารน้ำแข็ง, หอพักพนักงาน Glacier Valley</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>🥩 Seven Glaciers Restaurant (บนยอดเขา): Busser 17:30-23:00 น. (ร้าน 4 ดาว AAA ทิปมหาศาล $70-$120)</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Coast Pizza / Girdwood Brewing: ผู้ช่วยครัว/Barback 18:00-23:00 น. ($15/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>🥖 The Bake Shop Girdwood: ช่วยเตรียมเบเกอรี่/ล้างจานช่วงเช้าตรู่หรือเย็น</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Fairbanks Princess Riverside Lodge</t>
+          <t>Tier S - Alaska (AK)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>IEE, Acadex, Higher</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Food Runner / Laundry / Steward</t>
+          <t>Copper River Princess Wilderness Lodge</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Higher, IEE, Acadex</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Kitchen / Laundry</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 06:30 – 14:30 น. หรือ 15:00 – 23:00 น.
-พีค: กะสลับตามรอบรถไฟ/เครื่องบิน 8 ชม.</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>$20 - $40</t>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>$10 - $20</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36 – 40 ชม./สัปดาห์ (ไม่ค่อยมี OT)</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>หอพักในเมืองแฟร์แบงก์ส + รถชัตเติลบัส, ใกล้ Walmart และร้านอาหารไทย หางาน 2 ง่าย</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>รีสอร์ตริมแม่น้ำ Copper River อุทยาน Wrangell-St. Elias, อาหาร EDR ฟรี 3 มื้อ</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>🐟 Two Rivers Salmon Grill (ในโรงแรม): Busser/Steward 17:30-22:30 น. (เรต OT $24/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>🛶 Copper Oar Rafting Base: ช่วยล้างทำความสะอาดเรือยาง/ชูชีพ 17:00-21:00 น. ($16/ชม.)</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>🌲 Whistle Stop Gift Shop: แคชเชียร์ร้านของฝากกะค่ำ 18:00-22:00 น.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Grand Teton Lodge Company (GTLC)</t>
+          <t>Tier S - Wyoming (WY)</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Wyoming (WY)</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+          <t>Grand Teton Lodge Company - Jackson Lake Lodge</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Acadex, Higher, OEG, IEE</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Housekeeping / Crew Member</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 น. (8 ชม.)
-พีค: 07:00 – 17:30 น. (10 ชม. ควงกะ)</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:00 – 17:30 (10 ชม. ควงกะ)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>ฐาน $17.75 / OT $26.62</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>54 – 60 ชม./สัปดาห์ (พีค 60-64 ชม. / หัวท้าย 40 ชม.)</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), ส่วนลดซื้อของ 40%, เข้าอุทยาน Grand Teton &amp; Yellowstone ฟรี</t>
+          <t>54 – 60 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>$0 (ฟรี!)</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), ส่วนลด 40%, บัตรผ่าน 2 อุทยานฟรี</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>🍽️ Mural Room &amp; Pioneer Grill (ในโรงแรม): Busser 17:30-22:30 น. ได้เรต OT $26.62/ชม. + ทิป</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>🍸 Blue Heron Lounge (ในโรงแรม): Barback ช่วยยกน้ำแข็ง/ล้างแก้ว 18:00-23:30 น. (เรต OT $26.62 + Tip-Out)</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>🛶 Colter Bay Chuckwagon &amp; Marina: นั่งชัตเติลฟรีไปช่วยมินิมาร์ท/เรือแคนู 17:00-21:30 น.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Grand Teton Lodge Company (GTLC)</t>
+          <t>Tier S - Wyoming (WY)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Wyoming (WY)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+          <t>Grand Teton Lodge Company - Colter Bay Village</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Acadex, Higher, OEG, IEE</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Kitchen Crew / Dishwasher / Food Prep</t>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Cabin Attendant / Grocery Clerk / Marina</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 06:00 – 14:30 น. หรือ 15:00 – 23:00 น.
-พีค: 14:00 – 00:30 น. (ช่วยจัดเลี้ยง Banquet)</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>ฐาน $17.75 / OT $26.62</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52 – 58 ชม./สัปดาห์ (ควงกะ Banquet ได้)</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>หอพักฟรี 100%! + อาหาร 3 มื้อ EDR + กินฟรีในครัว, สิทธิประโยชน์เครือ Vail Resorts</t>
+          <t>52 – 58 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>$0 (ฟรี!)</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), หมู่บ้านริมทะเลสาบ Jackson Lake</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>🥩 Chuckwagon Restaurant (ในหมู่บ้าน): Busser/Steward บุฟเฟต์มื้อเย็น 17:00-22:00 น. (เรต OT $26.62)</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>🛒 Colter Bay General Store: แคชเชียร์/เติมสต็อกมินิมาร์ท 17:30-22:00 น. (เรต OT $26.62)</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>🛶 Colter Bay Marina: ล้างเรือยนต์/เรือแคนู 16:30-20:30 น. (เรต OT $26.62)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Xanterra Yellowstone Lodges</t>
+          <t>Tier S - Wyoming (WY)</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Wyoming/MT</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>OEG, IEE Thailand</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Hospitality Crew / Kitchen / Steward</t>
+          <t>Signal Mountain Lodge (Grand Teton NP - Forever Resorts)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Higher, Acadex</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Front Desk / Marina</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 07:00 – 15:30 น. หรือ 15:00 – 23:30 น.
-พีค: 06:30 – 16:30 น. (10 ชม.)</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>ฐาน $15.70 / OT $23.55</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.50 / OT $24.75</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>46 – 52 ชม./สัปดาห์ (หัวท้าย 38-42 ชม.)</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>$120</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>รวมหอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR, หอพักใหม่ Arnica, เที่ยวบ่อน้ำพุร้อนและไกเซอร์ Yellowstone ฟรี</t>
+          <t>45 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>$110 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>รีสอร์ตริมทะเลสาบ Signal Mountain, หอพักพนักงาน + อาหาร 3 มื้อ, ส่วนลดเช่าเรือ</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>🥩 The Peaks Restaurant (ในรีสอร์ต): Busser/Runner 17:30-22:30 น. ($14/ชม. + ทิปสด $50-$90/คืน)</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>🌮 Trapper Grill (ในรีสอร์ต): ผู้ช่วยครัว/ทำนาโชส์ 17:00-22:00 น. (ขอ OT $24.75/ชม.)</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>⛽ Signal Mountain Gas Station &amp; Store: แคชเชียร์รอบค่ำ 17:00-21:30 น.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Under Canvas Grand Teton / Yellowstone</t>
+          <t>Tier S - Wyoming (WY)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Wyoming (WY)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Higher Education</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Housekeeping / Guest Service</t>
+          <t>Xanterra Yellowstone Lodges (Old Faithful / Canyon)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>OEG, IEE Thailand</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Hospitality Crew / Kitchen Steward</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 08:30 – 16:30 น. (8 ชม.)
-พีค: 08:00 – 17:30 น. (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>ฐาน $16.50 / OT $24.75</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>$50 - $100</t>
+          <t>ปกติ: 07:00 – 15:30 หรือ 15:00 – 23:30
+พีค: 06:30 – 16:30 (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.70 / OT $23.55</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42 – 46 ชม./สัปดาห์</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>$100</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>แคมป์กระโจมซาฟารีหรู, อาหารพนักงาน, ทิปเงินสดจากแขกไฮเอนด์ บรรยากาศเป็นกันเอง</t>
+          <t>46 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>$120 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>รวมหอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR, หอพักใหม่ Arnica, เที่ยวบ่อน้ำพุร้อน Yellowstone ฟรี</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>🌋 Old Faithful Snow Lodge Dining: Busser/Steward กะค่ำ 17:00-22:30 น. (เรต OT $23.55/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>🛍️ Delaware North General Stores: แคชเชียร์ร้านของฝากข้างๆ เดิน 3 นาที 17:00-21:30 น. ($15.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>🍻 Employee Pub &amp; Rec Hall: ผู้ช่วยผับพนักงาน/ทำความสะอาด 19:30-23:30 น.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Kalahari Resorts &amp; Conventions</t>
+          <t>Tier S - Wyoming (WY)</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Wisconsin (WI)</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>OEG, Acadex, Higher</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Lifeguard / Housekeeping (งานหลัก)</t>
+          <t>Four Seasons Resort &amp; Snake River Lodge (Teton Village)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Stewarding</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 09:30 – 18:00 น. หรือ 12:00 – 20:30 น.
-พีค: 09:00 – 19:30 น. (10 ชม.)</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $17.50 / OT $26.25</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>38 – 44 ชม./สัปดาห์ (เกลี่ยกะ 40 ชม.)</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>$105</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>หอพัก Kalahari Village, บัตรเล่นสวนน้ำฟรี, เมืองปั่นจักรยาน 100%, หางาน 2 ร้านอาหารง่าย</t>
+          <t>45 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>$140</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>รีสอร์ตหรู 5 ดาวใน Teton Village, หอพักพนักงาน, นั่งรถบัส START Bus ฟรี</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>🍺 The Mangy Moose Saloon (Teton Village): Barback/Busser ผับดัง 18:00-00:30 น. (ทิปสดเศรษฐี $60-$120/คืน)</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>🤠 Million Dollar Cowboy Bar (เมือง Jackson): นั่ง START Bus เข้าเมือง ทำ Barback 19:00-01:30 น.</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Alpenhof Bistro: ล้างจาน/ผู้ช่วยครัว 17:30-22:30 น. ($16/ชม. + อาหารฟรี)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Wisconsin Dells Riverfront Eateries</t>
+          <t>Tier S - Wyoming (WY)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Wisconsin (WI)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Walk-in สมัครเองหน้างาน</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Barback / Busser / Runner (งานที่สอง)</t>
+          <t>The Wort Hotel &amp; Silver Dollar Bar (Jackson Town)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Acadex, OEG</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Banquet Server / Steward</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 17:30 – 22:30 น. (5 ชม.)
-พีค: 17:00 – 00:30 น. (7.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>ฐาน $12.00 – $14.00</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>$250 - $500</t>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $17.00 / OT $25.50</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>$30 - $60</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20 – 25 ชม./สัปดาห์ (กะค่ำ 17:30-23:00)</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>รับทิปเงินสดทุกคืน ยัดกระเป๋ากลับห้องทันที ($50-$100/คืน), อาหารพนักงานในกะ (ทำควบกับงานหลัก)</t>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>โรงแรมประวัติศาสตร์ใจกลางเมือง Jackson, เดินทางสะดวกที่สุด มีร้านค้าล้อมรอบ</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>💵 Silver Dollar Bar (ในโรงแรม): Barback/Busser บาร์ดนตรีสดคนแน่น 18:30-01:00 น. (ทิปสด $70-$130/คืน)</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>🥩 Gun Barrel Steak &amp; Game House: Busser ร้านสเต๊กเนื้อสัตว์ป่า 17:30-22:30 น. ($14/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>🛒 Albertsons Jackson: จัดสต็อกสินค้ากะดึก 20:00-00:00 น. ($18/ชม.)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Dollywood Theme Park &amp; Resorts</t>
+          <t>Tier S - Wyoming (WY)</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Tennessee (TN)</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>New Step, Acadex</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Ride Operator / Food Service / Retail</t>
+          <t>Under Canvas Grand Teton / Yellowstone</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Higher Education</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Guest Service</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 09:30 – 18:00 น. (8 ชม.)
-พีค: 09:00 – 21:30 น. (12 ชม. สวนสนุกเปิดดึก)</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.50 / OT $24.75</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>$50 - $100</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>44 – 50 ชม./สัปดาห์ (หัวท้าย 35-40 ชม.)</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>$110</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>ปลอดภาษีเงินได้รัฐ 0%, นั่งรถราง Pigeon Forge Trolley $1-$2.50/วัน, บัตรเข้าสวนสนุก Dollywood &amp; Splash Country ฟรี</t>
+          <t>42 – 46 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>แคมป์กระโจมซาฟารีหรู, อาหารพนักงาน, ทิปเงินสดจากแขกไฮเอนด์ บรรยากาศเป็นกันเอง</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>🏕️ Embers Restaurant (ในแกลมปิ้ง): Food Runner กะค่ำ 17:30-22:00 น. (ได้ทิปสดคืนละ $40-$60)</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>☕ Moose-Wilson Road Cafes: ผู้ช่วยบาริสต้า/เบเกอรี่ช่วงเช้าตรู่ 06:00-08:00 น. หรือเย็น</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>🛒 Jackson Town Local Diners: นั่งรถเข้าเมืองแจ็กสัน ทำงานร้านอาหารวันหยุด</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Premier Aquatics / High Sierra Pools</t>
+          <t>Tier S - Wisconsin (WI)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Maryland/VA</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Acadex, New Step, ALC</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Pool Lifeguard</t>
+          <t>Kalahari Resorts &amp; Conventions (Wisconsin Dells)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, Higher</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Lifeguard / Housekeeping</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 10:30 – 19:30 น. (9 ชม.)
-พีค: 10:00 – 20:30 น. (10.5 ชม. สระเปิดยาว)</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+          <t>ปกติ: 09:30 – 18:00 หรือ 12:00 – 20:30
+พีค: 09:00 – 19:30 (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50 – 54 ชม./สัปดาห์ (การันตี OT 10-14 ชม.)</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>$120</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>การันตีชั่วโมง OT สม่ำเสมอ 10-14 ชม./สัปดาห์ ไม่ผันผวนตามนักท่องเที่ยว, อพาร์ตเมนต์แชร์กับเพื่อน</t>
+          <t>38 – 44 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>หอพัก Kalahari Village, บัตรเล่นสวนน้ำฟรี, เมืองปั่นจักรยาน 100%, หางาน 2 ง่ายที่สุดในอเมริกา</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>🍕 Moosejaw Pizza &amp; Dells Brewing: ปั่นจักรยาน 10 นาที Busser/Barback 18:30-23:30 น. ($13/ชม. + ทิปสด $60-$90/คืน)</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>🍔 Buffalo Phil’s Grille: Food Runner/Busser เสิร์ฟอาหารด้วยรถไฟจิ๋ว 18:00-22:30 น. ($13/ชม. + ทิปสด $50-$80)</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>🧀 MACS Mac &amp; Cheese / Dairy Queen: แคชเชียร์/ครัวกะดึก 18:30-23:00 น. ($14.50-$15.50/ชม.)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Cedar Point Amusement Park</t>
+          <t>Tier S - Wisconsin (WI)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Ohio (OH)</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
+          <t>Wilderness Resort &amp; Glacier Canyon Lodge (WI Dells)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Acadex</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Waterpark Attendant / Housekeeping</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
+พีค: 08:30 – 19:00 (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>40 – 46 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>อาณาจักรรีสอร์ตสวนน้ำที่ใหญ่ที่สุดในอเมริกา (600 เอเคอร์), หอพักพนักงานในรีสอร์ต</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>🥩 Field’s at the Wilderness (สเต๊กหรูในรีสอร์ต): Busser 17:30-23:00 น. ($12/ชม. + ทิปสด $70-$120/คืน)</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Sarento’s Restaurant (ในรีสอร์ต): Food Runner/ล้างจาน 17:00-22:30 น. (ขอ OT ในรีสอร์ต $22.50)</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>🍔 B-LUX Grill &amp; Bar: Barback/Busser ร้านเบอร์เกอร์คราฟต์เบียร์ 18:00-00:00 น. (ทิปสดดีมาก)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Tier S - Wisconsin (WI)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Mt. Olympus Water &amp; Theme Park (WI Dells)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>New Step, Acadex, Higher</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Ride Operator / Housekeeping / Lifeguard</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีค: 09:00 – 21:00 (11.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>$95</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>สวนสนุกธีมกรีกโบราณ โรลเลอร์โคสเตอร์ไม้, หอพักราคาถูก, ทำเลติดถนนใหญ่ Parkway</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>🥞 Paul Bunyan’s Cook Shanty: ล้างจาน/ทำความสะอาดรอบค่ำ 17:30-22:00 น. ($14.50/ชม. + กินฟรี)</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>🌭 Hot Dog Avenue: แคชเชียร์/ครัวปิด 18:00-22:30 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>🍺 Showboat Saloon (Downtown): Barback ผับดนตรีสด 19:00-01:30 น. (ทิปสดแน่น)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Tier S - Wisconsin (WI)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Noah’s Ark Waterpark (Wisconsin Dells)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE, New Step</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Park Services</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
+พีค: 08:30 – 18:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>40 – 46 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>สวนน้ำกลางแจ้งใหญ่ที่สุดในอเมริกา, เล่นสวนน้ำฟรี, หอพักพนักงานใกล้ที่ทำงาน</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>🍻 Monk’s Bar &amp; Grill (Downtown Dells): ปั่นจักรยานไปทำ Barback/Busser 18:30-00:00 น. (ทิปสดแน่นมาก)</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Pizza Pub Dells: ช่วยส่งอาหาร/ทำพิซซ่า/ล้างจานรอบดึก 18:00-00:00 น. ($14/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>🍦 Dairy Queen / Cold Stone Dells: ตักไอศกรีมกะค่ำ 18:00-22:30 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Tier S - Wisconsin (WI)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Chula Vista Resort &amp; Waterpark (WI Dells)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Higher, Acadex, IEE</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Lifeguard</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>40 – 45 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>รีสอร์ตริมแม่น้ำ Wisconsin River, สวนน้ำในร่ม/กลางแจ้ง, หอพักในรีสอร์ต</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>🥩 Kaminski’s Chop House (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. ($12/ชม. + ทิปสดเศรษฐี $70-$120/คืน)</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>🌮 Mexicali Rose: Busser/Runner ร้านอาหารเม็กซิกันริมน้ำ 18:00-23:00 น. ($13/ชม. + ทิปสด)</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>🍕 Kilbourn City Grill (ในรีสอร์ต): ล้างจาน/ผู้ช่วยครัว 17:00-22:00 น. (ขอ OT ในรีสอร์ตได้)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Tier S - Wisconsin (WI)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Grand Geneva Resort &amp; Spa (Lake Geneva, WI)</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Acadex, OEG</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Banquet / Culinary</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>รีสอร์ตหรูระดับ 4 เพชร AAA เมืองตากอากาศทะเลสาบคนรวยชิคาโก, หอพักพนักงาน</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>🥩 Geneva ChopHouse (ในรีสอร์ต): Busser 17:30-23:00 น. ($13/ชม. + ทิปสด $60-$100/คืน)</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Popeye’s on Lake Geneva: Busser/Dishwasher ร้านอาหารริมทะเลสาบดัง 18:00-23:30 น. (ทิปดี)</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>🍺 The Bottle Shop / Local Pubs: Barback ร้านคราฟต์เบียร์ 18:30-00:00 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Tier S - Tennessee (TN)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Dollywood Theme Park &amp; Splash Country (Pigeon Forge)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>New Step, Acadex</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Ride Operator / Food Service / Retail</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีค: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึก)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>ปลอดภาษีเงินได้รัฐ 0%, นั่งรถราง Pigeon Forge Trolley $1/วัน, บัตรเข้าสวนสนุก Dollywood ฟรี</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>🍗 Paula Deen’s Family Kitchen (The Island): นั่งรถรางไปทำ Busser 18:30-23:00 น. ($13/ชม. + ทิปสด $60-$90)</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>🍕 Mellow Mushroom Pizza: Barback/Busser ร้านพิซซ่าคราฟต์เบียร์ 18:30-00:00 น. ($12/ชม. + ทิปสด $50-$80)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>🥞 Puckett’s Grocery &amp; Restaurant: Food Runner 18:00-23:00 น. ($13/ชม. + ทิป)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Tier S - Tennessee (TN)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>The Island in Pigeon Forge (Arcades &amp; Attractions)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>New Step, Acadex</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Attractions Host / Retail / F&amp;B</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:00 (8 ชม.)
+พีค: 10:00 – 23:00 (กะดึก)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>$20 - $40</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>ศูนย์รวมความบันเทิง ชิงช้าสวรรค์ยักษ์และร้านอาหารกลางเมือง, รถรางผ่านหน้าร้าน</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>🦜 Margaritaville Restaurant (ใน The Island): Busser/Barback 18:30-00:00 น. ($13/ชม. + ทิปสด $60-$100)</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>🥞 Timberwood Grill (ใน The Island): ล้างจาน/ผู้ช่วยครัว 18:00-23:30 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>🍭 The Island Candy Kitchen: แคชเชียร์/ทำขนม 18:00-22:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Tier S - Tennessee (TN)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Wilderness at the Smokies (Sevierville)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, Higher</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Lifeguard / Housekeeping</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
+พีค: 08:30 – 19:30 (10.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>สวนน้ำในร่มใหญ่ที่สุดในเทนเนสซี, ปลอดภาษีรัฐ 0%, หอพักพนักงาน Sevierville</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>🍏 Applewood Farmhouse Restaurant: Busser ร้านอาหารดังคนแน่น 18:00-22:30 น. (ทิปสด $60-$100/คืน)</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>🥩 Hidden Trail Restaurant (ในรีสอร์ต): ล้างจาน/Busser กะค่ำ 18:00-22:30 น. (ขอ OT ในรีสอร์ต $22.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>🛍️ Tanger Outlets Sevierville: จัดสต็อกสินค้า/ปิดร้าน 18:00-21:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Tier S - Tennessee (TN)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Anakeesta Mountaintop Theme Park (Gatlinburg)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Higher, IEE</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Guest Host / F&amp;B / Retail</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
+พีค: 08:30 – 20:00 (10.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกธรรมชาติบนยอดเขา Gatlinburg นั่งกระเช้า Chondola, ปลอดภาษีรัฐ 0%</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Smoky Mountain Brewery (Gatlinburg): Barback/Busser 18:30-00:30 น. ($12/ชม. + ทิปสด $70-$120/คืน)</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>🥩 Alamo Steakhouse: Busser/Dishwasher ร้านสเต๊กคาวบอย 17:30-23:00 น. ($13/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>🥞 Pancake Pantry (ร้านแพนเค้กอันดับ 1): ช่วยเตรียมวัตถุดิบ/ล้างจานรอบบ่าย-เย็น</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Tier S - Tennessee (TN)</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Ober Mountain / Gatlinburg Area Lodges</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>IEE, New Step</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Attractions Operator / Retail</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:00 – 17:00 (8 ชม.)
+พีค: 08:30 – 19:00 (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>40 – 46 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>กระเช้าลอยฟ้าและสวนสนุกบนยอดเขา Gatlinburg, ปลอดภาษีรัฐ 0%, เมืองเดินเท้า 100%</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>🥃 Ole Smoky Moonshine Distillery: พนักงานเช็ดแก้ว/เติมสต็อก/แคชเชียร์ 17:30-22:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>🥩 Calhoun’s in Gatlinburg: Busser/Runner ร้านบาร์บีคิวซี่โครงหมูชื่อดัง 17:30-23:00 น. (ทิปดี)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>🍕 Best Italian Cafe &amp; Pizzeria: ผู้ช่วยครัว/ล้างจาน 18:00-23:30 น. ($14/ชม. + ทิป)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Tier S - Texas (TX)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Schlitterbahn Waterpark (New Braunfels / Galveston)</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, IEE</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Lifeguard / Park Operations</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีค: 09:00 – 19:30 (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>สวนน้ำระดับตำนานของเท็กซัส, ปลอดภาษีเงินได้รัฐ 0%, เล่นสวนน้ำฟรี</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>🥩 Gristmill River Restaurant (Gruene): Busser ร้านอาหารริมแม่น้ำสุดคึกคัก 18:30-23:30 น. ($12/ชม. + ทิปสด $60-$100)</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>🦫 Buc-ee’s New Braunfels (ใหญ่ที่สุดในโลก): แคชเชียร์/Food Prep กะดึก 19:00-00:00 น. ($17-$19/ชม. จ่ายหนักมาก)</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Krause’s Cafe &amp; Biergarten: Barback/Runner ร้านเบียร์เยอรมัน 18:00-23:00 น. ($13/ชม. + ทิป)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Tier S - Texas (TX)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Kalahari Resorts &amp; Conventions Round Rock (Austin, TX)</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>OEG, Acadex</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Lifeguard / Housekeeping / F&amp;B</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีค: 09:00 – 19:30 (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>สวนน้ำในร่มใหญ่ที่สุดในอเมริกา สาขาเท็กซัส, ปลอดภาษีรัฐ 0%, ใกล้ออสติน</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>🥩 Double Cut Steak House (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. ($13/ชม. + ทิปสด $70-$120)</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>🍕 Tom Foolerys Adventure Park (ในรีสอร์ต): คุมเครื่องเล่น/เกมรอบค่ำ 18:00-23:00 น. (ขอ OT $23.25)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>🍔 Round Rock Local Eateries: Busser/ล้างจานร้านอาหารรอบนอก 18:30-23:30 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Tier S - Texas (TX)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Six Flags Fiesta Texas &amp; SeaWorld San Antonio</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>New Step, Higher, IEE</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Culinary</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีค: 09:30 – 21:30 (11.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>$115</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกและสวนน้ำระดับโลก ซานอันโตนิโอ, ปลอดภาษีรัฐ 0%, หอพักพนักงาน</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>🥩 The County Line BBQ (River Walk): Busser ร้านบาร์บีคิวริมแม่น้ำ 19:00-00:00 น. (ทิปสด $60-$100/คืน)</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>🎸 Hard Rock Cafe San Antonio: Food Runner/Busser 19:00-00:30 น. ($13/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>🌮 Boudro’s on the Riverwalk: ล้างจาน/ผู้ช่วยครัว 19:00-01:00 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Tier S - Texas (TX)</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Kemah Boardwalk &amp; Galveston Pleasure Pier</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>OEG, New Step</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Ride Operator / Retail / F&amp;B</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:30 – 18:30 (8 ชม.)
+พีค: 10:00 – 22:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>สวนสนุกริมอ่าวเม็กซิโก เครือ Landry’s, ปลอดภาษีรัฐ 0%, บรรยากาศชายทะเล</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>🦞 Aquarium Restaurant Kemah (ในเครือ): Busser ร้านอาหารใต้น้ำ 18:30-23:30 น. (ทิปสด $60-$100/คืน)</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>🍤 Bubba Gump Shrimp Co. (Galveston Pier): Food Runner/Busser 18:30-00:00 น. (ทิปดี)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>🏖️ The Spot (Galveston Seawall): Barback/Busser ร้านอาหารริมหาดคนแน่น 19:00-01:00 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Tier A - Montana (MT)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Glacier National Park Lodges (Pursuit / Xanterra)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, Higher</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Hospitality Crew / Housekeeping</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>46 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>$115 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>อุทยานธรรมชาติธารน้ำแข็ง Glacier NP, ปลอดภาษีมูลค่าเพิ่ม 0% Sales Tax, หอพัก+อาหาร EDR</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>🥩 Belton Chalet Dining Room: Busser/Steward ร้านอาหารประวัติศาสตร์ 17:30-22:30 น. ($15/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>🛶 Glacier Raft Company Base: พนักงานล้างทำความสะอาดเรือยาง/อุปกรณ์ล่องแก่ง 17:00-21:30 น. ($16/ชม.)</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>🥐 West Glacier Bakery &amp; Cafe: ผู้ช่วยเตรียมวัตถุดิบ/ล้างจาน 17:00-22:00 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Tier A - Montana (MT)</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Many Glacier Hotel &amp; Glacier Park Lodge (East Glacier)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>OEG, Acadex</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Dining Room / Steward</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีค: 07:00 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>46 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>$115 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>โรงแรมสไตล์สวิสชาเลต์ริมทะเลสาบ Swiftcurrent Lake สวยที่สุดใน Glacier NP, อาหาร EDR 3 มื้อ</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>🥩 Ptarmigan Dining Room (ในโรงแรม): Busser 17:00-22:30 น. (เรต OT $24/ชม. + ทิปสด)</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>☕ Heidi’s Snack Shop (ในโรงแรม): แคชเชียร์/ชงกาแฟ 16:30-21:30 น. (ขอ OT $24/ชม.)</t>
+        </is>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>🛶 Many Glacier Boat Tours: ช่วยเทียบเรือ/ล้างเรือทัวร์ 17:00-20:30 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Tier A - Montana (MT)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Big Sky Resort / Montage Big Sky</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Acadex, Higher, IEE</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Mountain Operations / Housekeeping</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $17.50 / OT $26.25</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>46 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>$140</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>รีสอร์ตภูเขาหรูหราไฮเอนด์, ค่าแรงฐานสูงมาก, มีรถบัส Skyline Bus ฟรี</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Lone Peak Brewery (Town Center): Barback/Busser 17:30-23:30 น. ($15/ชม. + ทิปสดเศรษฐี $60-$100/คืน)</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>🍖 The Riverhouse BBQ: Busser/Runner ร้านบาร์บีคิวริมแม่น้ำ Gallatin 17:00-22:30 น. ($14/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>🛒 Roxy’s Market Big Sky: พนักงานจัดสต็อกซูเปอร์มาร์เก็ต 18:00-22:00 น. ($17/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Tier A - Maryland (MD)</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Premier Aquatics / High Sierra Pools (Bethesda/Rockville)</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Acadex, New Step, ALC</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Pool Lifeguard</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:30 – 19:30 (9 ชม.)
+พีค: 10:00 – 20:30 (10.5 ชม. สระเปิดยาว)</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>50 – 54 ชม./wk (การันตี OT)</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>การันตีชั่วโมง OT แน่นอนสัปดาห์ละ 10-14 ชม., อพาร์ตเมนต์แชร์กับเพื่อน, รถไฟใต้ดิน Metro เข้า DC</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t>🛒 Giant Food / Safeway: พนักงานจัดสต็อกสินค้ากะดึก 20:30-01:00 น. ($16-$17.50/ชม. มีสาขาใกล้ที่พัก)</t>
+        </is>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>🍜 Thai Tanic / Ruan Thai: ผู้ช่วยครัว/แพ็กอาหาร 20:00-23:30 น. (มีอาหารไทยฟรี)</t>
+        </is>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>🎯 Target / CVS Pharmacy: แคชเชียร์/ปิดร้าน 20:00-23:30 น. ($16.00/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Tier A - Maryland (MD)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Ocean City Boardwalk Hotels &amp; Resorts</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>IEE, New Step, OEG</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Ride Operator</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>$125</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายหาด Atlantic, รถบัส Coastal Highway วิ่ง 24 ชม., หางานสองง่ายมาก</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Seacrets Jamaica USA (ผับริมหาดยักษ์ใหญ่): Barback/Busser 18:00-01:30 น. ($12/ชม. + ทิปสดมหาศาล $80-$150/คืน)</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>🍟 Thrasher’s French Fries (ริมหาด): แคชเชียร์/ทอดเฟรนช์ฟรายส์ 18:00-23:00 น. ($15/ชม.)</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Shenanigans Irish Pub: ล้างจาน/ผู้ช่วยบาร์ 18:30-00:30 น. ($14/ชม. + ทิป)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Tier A - Maryland (MD)</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Jolly Roger Amusement Park &amp; Splash Mountain (Ocean City)</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>New Step, IEE</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Park Services</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 11:00 – 19:00 (8 ชม.)
+พีค: 10:00 – 23:00 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>45 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกและสวนน้ำที่ใหญ่ที่สุดใน Ocean City, เล่นสวนสนุกฟรี, มีรถเมล์ผ่านหน้าสวนสนุก</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>🦀 Higgins Crab House: Busser ร้านปูยักษ์ 19:30-00:30 น. ($13/ชม. + ทิปสด $60-$90/คืน)</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>🍕 Dough Roller Pizza (Boardwalk): ล้างจาน/ทำพิซซ่ากะดึก 19:30-01:00 น. ($15/ชม.)</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>🍦 Dumser’s Dairyland: ตักไอศกรีม/แคชเชียร์ 19:00-23:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Tier A - Virginia (VA)</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Busch Gardens Williamsburg &amp; Water Country USA</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>New Step, Acadex</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Culinary Operations</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีค: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึก)</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>$115</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกธีมยุโรปชื่อดัง, บัตรเข้าสวนสนุกและสวนน้ำฟรี, หอพักพนักงาน Williamsburg</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>🏰 Kingsmill Resort (ริมแม่น้ำ James River): Banquet Server/Busser งานจัดเลี้ยง 18:30-23:00 น. (ทิปสด $50-$90/คืน)</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>🦀 Captain George’s Seafood Buffet: Busser/Dishwasher บุฟเฟต์ซีฟู้ดยักษ์ใหญ่ 18:30-23:30 น. (คนแน่นมาก ทิปดี)</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>🥞 Cracker Barrel / Pancake House: ผู้ช่วยครัว/ล้างจานรอบค่ำ 18:00-22:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Tier A - Virginia (VA)</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Virginia Beach Oceanfront Resorts &amp; Boardwalk</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>IEE, New Step, Acadex</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Beach Attendant</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายทะเลเวอร์จิเนีย มีทางเดินเลียบหาดยาว 3 ไมล์, รถราง Wave Trolley สะดวก</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>🍺 Waterman’s Surfside Grille: Barback/Busser ร้านริมหาดคนแน่น 18:00-00:30 น. (ทิปสด $70-$120/คืน)</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>🦀 Catch 31 Fish Bar: Food Runner/Busser 18:00-23:30 น. (ทิปดี)</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>🍕 Dough Boy’s California Pizza: ผู้ช่วยครัว/ล้างจาน 18:30-00:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Tier A - South Dakota (SD)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Xanterra Mount Rushmore / Keystone Lodges</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Higher</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Retail / Food Service / Housekeeping</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>ทำงานหน้าอนุสรณ์สถานแห่งชาติ Mount Rushmore, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>🍔 Carver’s Cafe at Mt Rushmore: ล้างจาน/ปิดครัว 17:00-21:30 น. (ขอ OT ในอุทยาน $23.25/ชม.)</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>🥩 Ruby House Restaurant (Keystone): Busser ร้านอาหารธีมคาวบอยย้อนยุค 17:30-22:30 น. ($13/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>🚂 1880 Train / Keystone Gift Shops: พนักงานร้านของฝาก/สถานีรถไฟโบราณ 17:00-21:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Tier A - South Dakota (SD)</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Custer State Park Resorts (State Game Lodge / Sylvan)</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Higher, Acadex</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Guest Service / Housekeeping</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีค: 07:00 – 16:30 (9 ชม.)</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>$105 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>อุทยานธรรมชาติฝูงควายไบซัน Custer SP, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>🥩 State Game Lodge Dining Room: Busser ร้านสเต๊กควายไบซันหรู 17:00-22:00 น. ($13/ชม. + ทิปสด $50-$80)</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>🍔 Black Hills Burger &amp; Bun (เมือง Custer): ล้างจาน/ครัว 17:00-21:30 น. ($15/ชม. + กินฟรี)</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>🏕️ Sylvan Lake General Store: พนักงานมินิมาร์ท/เช่าเรือแคนู 16:30-21:00 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Tier A - South Dakota (SD)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Wall Drug Store (Wall, SD)</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>IEE, Acadex</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Retail / Restaurant Staff / Fast Food</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>45 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>$85 (ถูกมาก)</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>ห้างคาวบอยระดับตำนานของอเมริกา จุดแวะพักยอดฮิตก่อนเข้า Badlands NP, หอพักราคาถูก</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>☕ Wall Drug Western Art Dining Room: Busser/Steward 17:00-22:00 น. (ขอ OT ในตัว $23.25)</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>🍩 Wall Drug Famous Donut Kitchen: ช่วยทำโดนัท/เบเกอรี่รอบเย็น 16:30-21:00 น.</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>🌵 Badlands Saloon &amp; Grille: Barback/ล้างจาน 18:00-23:00 น. ($14.50/ชม. + ทิป)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Tier A - South Dakota (SD)</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Deadwood Historic Hotels &amp; Casinos (The Lodge at Deadwood)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Higher, New Step</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Food &amp; Beverage</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>เมืองคาวบอยคาสิโนประวัติศาสตร์ ปลอดภาษีรัฐ 0%, มีรถราง Deadwood Trolley $1</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>🥩 Deadwood Grille / O’Shea’s: Busser/Runner 17:30-23:00 น. ($13/ชม. + ทิปสด $50-$90/คืน)</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>🎰 Mineral Palace / Silverado Casino: Barback บาร์ในคาสิโน 18:30-01:00 น. (ทิปดี)</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>🍕 Mustang Sally’s Sports Bar: ผู้ช่วยครัว/ล้างจาน 18:00-00:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Tier A - Utah (UT)</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Zion National Park Lodge (Xanterra Springdale)</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Acadex</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Hospitality Crew / Housekeeping</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีค: 07:00 – 16:30 (9 ชม.)</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>อุทยานแห่งชาติหุบเขาผาแดง Zion NP, มีรถชัตเติลบัสฟรีวิ่งตลอดถนน Springdale</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>🌮 Bit &amp; Spur Restaurant &amp; Saloon: Busser/Barback 17:30-23:00 น. ($13/ชม. + ทิปสดแขกต่างชาติ $50-$90/คืน)</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>🍔 Oscar’s Cafe (Springdale): Food Runner/Busser 17:00-22:00 น. ($13/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Zion Canyon Brew Pub: ล้างจาน/ผู้ช่วยครัวหน้าปากทางเข้าอุทยาน 18:00-23:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Tier A - Utah (UT)</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Ruby’s Inn / Bryce Canyon Grand Hotel</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Higher, IEE, Acadex</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Fast Food / Retail</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>อาณาจักรโรงแรมและรีสอร์ต Ruby’s Inn หน้าปากทาง Bryce Canyon NP, หอพักพนักงานใกล้ที่ทำงาน</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>🥩 Cowboy’s Buffet &amp; Steak Room (ในเครือ): Busser/Steward 17:00-22:30 น. (ขอ OT ในเครือ $22.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>🤠 Ebenezer’s Barn &amp; Grill: Food Runner งานดินเนอร์โชว์คาวบอย 18:00-22:00 น. (ได้ส่วนแบ่งทิป)</t>
+        </is>
+      </c>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>🛒 Ruby’s General Store &amp; Diner: แคชเชียร์/ผู้ช่วยครัว 17:00-21:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Tier A - Utah (UT)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Park City Mountain Resort (Vail Resorts - Park City)</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Mountain Host / Housekeeping / F&amp;B</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $17.50 / OT $26.25</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>สกีรีสอร์ตและเมืองภูเขาที่ใหญ่ที่สุดในสหรัฐฯ, ระบบรถเมล์ฟรีทั้งเมือง Park City Transit</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>🥩 High West Distillery &amp; Saloon (Main Street): Barback/Busser โรงกลั่นวิสกี้ดัง 17:30-23:30 น. (ทิปสด $80-$140/คืน)</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Red Banjo Pizza (Historic Main St): ล้างจาน/ผู้ช่วยครัว 18:00-23:00 น. ($16/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>🛒 Freshies Lobster Co. / Local Cafes: Food Runner 17:00-21:30 น. ($15/ชม. + ทิป)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Tier A - Maine (ME)</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Bar Harbor Grand Hotel / Harborside Hotel</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Acadex, OEG, Higher</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Laundry</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $16.50 / OT $24.75</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายทะเล Bar Harbor &amp; อุทยาน Acadia NP, รถบัส Island Explorer ฟรี</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>🦞 Stewman’s Lobster Pound (ริมทะเล): Busser/Barback ร้านกุ้งล็อบสเตอร์ 17:30-23:00 น. ($13/ชม. + ทิปสด $60-$120/คืน)</t>
+        </is>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
+          <t>🍺 Geddy’s Down Under / The Chart Room: Busser/Runner 18:00-23:30 น. (ทิปสดแน่นมาก)</t>
+        </is>
+      </c>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>🍦 Ben &amp; Bill’s Chocolate Emporium: พนักงานตักไอศกรีม/แคชเชียร์ 17:00-22:00 น. ($15.50/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Tier A - Maine (ME)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Cliff House Maine (Cape Neddick / Ogunquit)</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Higher, Acadex</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Culinary / Stewarding</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $17.00 / OT $25.50</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>$135</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>รีสอร์ตหรูบนหน้าผาริมมหาสมุทรแอตแลนติก แขกไฮเอนด์ระดับมหาเศรษฐีบอสตันและนิวยอร์ก</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>🦞 The Tiller Restaurant (ในรีสอร์ต): Busser ร้าน Fine Dining วิวมหาสมุทร 17:30-23:00 น. (ทิปสด $70-$130/คืน)</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Nubb’s Lobster Shack (ในรีสอร์ต): Food Runner/Barback 17:00-22:30 น. (ขอ OT ในรีสอร์ต $25.50)</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>🍦 Ogunquit Beach Cafes: ผู้ช่วยครัว/บริการรอบเย็น</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Tier A - Maine (ME)</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>The Nonantum Resort (Kennebunkport, ME)</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Higher, Acadex</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Banquet / F&amp;B</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $16.50 / OT $24.75</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>$125</t>
+        </is>
+      </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>รีสอร์ตตากอากาศริมน้ำประวัติศาสตร์ เมืองของประธานาธิบดีบุช, หอพักพนักงาน Kennebunkport</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>🦞 The Clam Shack (สะพาน Kennebunkport): ล้างจาน/ทอดซีฟู้ดร้านดัง 17:30-22:30 น. ($16/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>🥩 Ocean Restaurant: Busser ร้านอาหารหรูริมน้ำ 18:00-23:00 น. (ทิปสด $60-$100/คืน)</t>
+        </is>
+      </c>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>🍦 Rococo Artisan Ice Cream: ตักไอศกรีม 17:00-22:00 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Tier A - Ohio (OH)</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Cedar Point Amusement Park &amp; Resorts (Sandusky)</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>OEG, IEE Thailand</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Ride Operator / Food Service</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 10:00 – 18:30 น. (8 ชม.)
-พีค: 09:30 – 22:30 น. (12 ชม. สวนสนุกปิดดึก)</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีค: 09:30 – 22:30 (12 ชม. สวนสนุกปิดดึก)</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>ฐาน $14.50 / OT $21.75</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>46 – 52 ชม./สัปดาห์ (หัวท้าย 38-42 ชม.)</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>$80</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>หอพักราคาถูกมาก ($80/wk), รถบัสรับส่งฟรี, บัตรเล่นเครื่องเล่นสวนสนุกระดับโลกฟรี</t>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>46 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>$80 (ถูกสุด)</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกเครื่องเล่นระดับโลก, หอพักราคาถูกที่สุดในอเมริกา ($80/wk), รถบัสรับส่งฟรี, เล่นสวนสนุกฟรี</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>🏨 Hotel Breakers / Castaway Bay (ในสวนสนุก): ล้างจาน/แม่บ้านกะค่ำ 19:00-00:00 น. (ขอ OT ในสวนสนุก $21.75/ชม.)</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>🍖 Famous Dave’s BBQ (Cedar Point Marina): Busser/Dishwasher 18:30-23:30 น. ($13/ชม. + ทิปสด)</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>🐴 Thirsty Pony / Kalahari Sandusky: Barback/Busser ร้านอาหารใกล้เคียง 19:00-00:30 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Tier A - Ohio (OH)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Kings Island Amusement Park (Mason / Cincinnati)</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>OEG, IEE Thailand</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Ride Operator / Park Services / Culinary</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีค: 09:30 – 22:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>$90</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกชั้นนำเครือ Cedar Fair ใกล้เมือง Cincinnati, หอพักพนักงาน + รถรับส่งฟรี</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>🍕 Mason Local Pizzerias &amp; Diners: ล้างจาน/ผู้ช่วยครัวรอบดึก 19:00-00:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>🍦 Greaters Ice Cream: พนักงานตักไอศกรีมชื่อดัง 19:00-23:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>🏨 Great Wolf Lodge Mason (ข้างๆ สวนสนุก): แม่บ้าน/ผู้ช่วยครัวกะค่ำ (ขอทำเพิ่มได้)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Tier A - Colorado (CO)</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>YMCA of the Rockies (Estes Park Center)</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Higher, IEE, Acadex</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Food Service</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีค: 07:00 – 16:30 (9 ชม.)</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>$110 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>แคมป์รีสอร์ตกลางเทือกเขา Rocky Mountain NP, หอพัก+อาหารบุฟเฟต์ 3 มื้อ, รถชัตเติลบัสเข้าเมืองฟรี</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>🏨 The Stanley Hotel (โรงแรมประวัติศาสตร์ The Shining): Busser/Steward ร้านอาหารหรู 17:30-23:00 น. (ทิปสด $50-$90)</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>🍔 Penelope’s Old Time Burgers: ผู้ช่วยครัว/ทอดเบอร์เกอร์ 17:00-21:30 น. ($15/ชม. + กินฟรี)</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Estes Park Brewery / Rock Cut Brewing: ล้างแก้ว/ผู้ช่วยบาร์ 18:00-22:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>

--- a/Work_and_Travel_Master_Job_Database_2027.xlsx
+++ b/Work_and_Travel_Master_Job_Database_2027.xlsx
@@ -499,13 +499,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Agency ที่ถือสัญญา</t>
+          <t>Agency ที่ถือสัญญา (ครบ 6 แห่ง)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Acadex, OEG, IEE, Higher</t>
+          <t>Acadex, OEG, IEE, Higher, IEO</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Acadex, OEG, IEE, Higher</t>
+          <t>Acadex, OEG, IEE, Higher, IEO</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Acadex Thailand</t>
+          <t>Acadex Thailand, IEO</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Higher, OEG, Acadex</t>
+          <t>Higher, OEG, Acadex, IEO</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>IEE, Acadex, Higher</t>
+          <t>IEE, Acadex, Higher, IEO</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>OEG, Acadex, ALC</t>
+          <t>OEG, Acadex, ALC, IEO</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>OEG, Acadex, Higher</t>
+          <t>OEG, Acadex, Higher, IEO</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>OEG, Higher</t>
+          <t>OEG, Higher, Acadex</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Higher, IEE, Acadex</t>
+          <t>Higher, IEE, Acadex, IEO</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Acadex, Higher, OEG, IEE</t>
+          <t>Acadex, Higher, OEG, IEE, IEO</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Acadex, Higher, OEG, IEE</t>
+          <t>Acadex, Higher, OEG, IEE, IEO</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Higher, Acadex</t>
+          <t>Higher, Acadex, IEO</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>OEG, IEE Thailand</t>
+          <t>OEG, IEE Thailand, IEO</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>OEG, Acadex</t>
+          <t>OEG, Acadex, IEO</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Acadex, OEG</t>
+          <t>Acadex, OEG, IEO</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Higher Education</t>
+          <t>Higher Education, IEO</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>OEG, Acadex, Higher</t>
+          <t>OEG, Acadex, Higher, IEO, New Step</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>OEG, IEE, Acadex</t>
+          <t>OEG, IEE, Acadex, IEO</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>New Step, Acadex, Higher</t>
+          <t>New Step, Acadex, Higher, IEO</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>OEG, IEE, New Step</t>
+          <t>OEG, IEE, New Step, IEO</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Higher, Acadex, IEE</t>
+          <t>Higher, Acadex, IEE, IEO</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Acadex, OEG</t>
+          <t>Acadex, OEG, IEO</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>New Step, Acadex</t>
+          <t>New Step, Acadex, IEO</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>New Step, Acadex</t>
+          <t>New Step, Acadex, IEO</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>OEG, Acadex, Higher</t>
+          <t>OEG, Acadex, Higher, IEO</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Higher, IEE</t>
+          <t>Higher, IEE, IEO</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>IEE, New Step</t>
+          <t>IEE, New Step, IEO</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>OEG, Acadex, IEE</t>
+          <t>OEG, Acadex, IEE, IEO</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>OEG, Acadex</t>
+          <t>OEG, Acadex, IEO</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>New Step, Higher, IEE</t>
+          <t>New Step, Higher, IEE, IEO</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>OEG, New Step</t>
+          <t>OEG, New Step, IEO</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>OEG, Acadex, Higher</t>
+          <t>OEG, Acadex, Higher, IEO</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>OEG, Acadex</t>
+          <t>OEG, Acadex, IEO</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Acadex, Higher, IEE</t>
+          <t>Acadex, Higher, IEE, IEO</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2899,1222 +2899,1494 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
+          <t>Tier A - Florida (FL)</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Universal Orlando Resort &amp; Volcano Bay</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Attractions Attendant / Culinary / Lifeguard</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีค: 09:00 – 22:00 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกระดับโลก ยูนิเวอร์แซล ออร์แลนโด, ปลอดภาษีเงินได้รัฐ 0%, บัตรเข้าสวนสนุกฟรี</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t>🎸 Universal CityWalk Eateries: Food Runner/Busser บาร์ดึก 18:30-01:00 น. (ทิปสด $60-$100/คืน)</t>
+        </is>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>🍔 The Cowfish Sushi Burger Bar: ล้างจาน/ผู้ช่วยครัว 19:00-01:00 น. ($15/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>🍕 Red Oven Pizza Bakery: ผู้ช่วยทำพิซซ่ากะดึก 18:30-00:30 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Tier A - Florida (FL)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Busch Gardens Tampa Bay &amp; Adventure Island</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>New Step, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Food Service</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีค: 09:00 – 21:30 (11.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกโรลเลอร์โคสเตอร์อันดับ 1 ในแทมปาและสวนน้ำ, ปลอดภาษีรัฐ 0%</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Ybor City Historic Bars (แทมปา): Barback ผับประวัติศาสตร์ 19:00-01:30 น. (ทิปสด $60-$110/คืน)</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>🦀 Columbia Restaurant (ร้านสเปนชื่อดังที่สุด): Busser 18:30-23:30 น. (ทิปดี)</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>🍔 Portillo’s Hot Dogs Tampa: ครัว/แคชเชียร์รอบดึก 18:30-00:00 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Tier A - Florida (FL)</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Gaylord Palms Resort &amp; Convention Center (Kissimmee)</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, Higher</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Banquet Server / Steward</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>$125</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>รีสอร์ตศูนย์ประชุมโดมกระจกยักษ์ระดับ 4 ดาว Marriott, ปลอดภาษีรัฐ 0%</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>🥩 Old Hickory Steakhouse (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. (ทิปสด $70-$120)</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Wreckers Sports Bar (ในรีสอร์ต): Barback ผับกีฬาจอ 2 ชั้น 18:30-00:30 น. (ขอ OT ในรีสอร์ต $24/ชม.)</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>🛍️ Disney Springs Eateries: Food Runner ร้านอาหารฝั่งดิสนีย์ 19:00-01:00 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>Tier A - Maryland (MD)</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Premier Aquatics / High Sierra Pools (Bethesda/Rockville)</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Acadex, New Step, ALC</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Acadex, New Step, ALC, IEO</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Pool Lifeguard</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 10:30 – 19:30 (9 ชม.)
 พีค: 10:00 – 20:30 (10.5 ชม. สระเปิดยาว)</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>50 – 54 ชม./wk (การันตี OT)</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>$120</t>
         </is>
       </c>
-      <c r="J36" s="10" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>การันตีชั่วโมง OT แน่นอนสัปดาห์ละ 10-14 ชม., อพาร์ตเมนต์แชร์กับเพื่อน, รถไฟใต้ดิน Metro เข้า DC</t>
         </is>
       </c>
-      <c r="K36" s="10" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>🛒 Giant Food / Safeway: พนักงานจัดสต็อกสินค้ากะดึก 20:30-01:00 น. ($16-$17.50/ชม. มีสาขาใกล้ที่พัก)</t>
         </is>
       </c>
-      <c r="L36" s="10" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>🍜 Thai Tanic / Ruan Thai: ผู้ช่วยครัว/แพ็กอาหาร 20:00-23:30 น. (มีอาหารไทยฟรี)</t>
         </is>
       </c>
-      <c r="M36" s="10" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>🎯 Target / CVS Pharmacy: แคชเชียร์/ปิดร้าน 20:00-23:30 น. ($16.00/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Tier A - Maryland (MD)</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>Ocean City Boardwalk Hotels &amp; Resorts</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>IEE, New Step, OEG</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>IEE, New Step, OEG, IEO</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>Housekeeping / Ride Operator</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>ปกติ: 08:30 – 16:30 (8 ชม.)
 พีค: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>$125</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>เมืองตากอากาศชายหาด Atlantic, รถบัส Coastal Highway วิ่ง 24 ชม., หางานสองง่ายมาก</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr">
+      <c r="K40" s="10" t="inlineStr">
         <is>
           <t>🌴 Seacrets Jamaica USA (ผับริมหาดยักษ์ใหญ่): Barback/Busser 18:00-01:30 น. ($12/ชม. + ทิปสดมหาศาล $80-$150/คืน)</t>
         </is>
       </c>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="L40" s="10" t="inlineStr">
         <is>
           <t>🍟 Thrasher’s French Fries (ริมหาด): แคชเชียร์/ทอดเฟรนช์ฟรายส์ 18:00-23:00 น. ($15/ชม.)</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr">
+      <c r="M40" s="10" t="inlineStr">
         <is>
           <t>🍺 Shenanigans Irish Pub: ล้างจาน/ผู้ช่วยบาร์ 18:30-00:30 น. ($14/ชม. + ทิป)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Tier A - Maryland (MD)</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Jolly Roger Amusement Park &amp; Splash Mountain (Ocean City)</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>New Step, IEE</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>New Step, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Ride Operator / Lifeguard / Park Services</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 11:00 – 19:00 (8 ชม.)
 พีค: 10:00 – 23:00 (12 ชม.)</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>45 – 52 ชม./wk</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>$120</t>
         </is>
       </c>
-      <c r="J38" s="10" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>สวนสนุกและสวนน้ำที่ใหญ่ที่สุดใน Ocean City, เล่นสวนสนุกฟรี, มีรถเมล์ผ่านหน้าสวนสนุก</t>
         </is>
       </c>
-      <c r="K38" s="10" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>🦀 Higgins Crab House: Busser ร้านปูยักษ์ 19:30-00:30 น. ($13/ชม. + ทิปสด $60-$90/คืน)</t>
         </is>
       </c>
-      <c r="L38" s="10" t="inlineStr">
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>🍕 Dough Roller Pizza (Boardwalk): ล้างจาน/ทำพิซซ่ากะดึก 19:30-01:00 น. ($15/ชม.)</t>
         </is>
       </c>
-      <c r="M38" s="10" t="inlineStr">
+      <c r="M41" s="7" t="inlineStr">
         <is>
           <t>🍦 Dumser’s Dairyland: ตักไอศกรีม/แคชเชียร์ 19:00-23:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>Tier A - Virginia (VA)</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>Busch Gardens Williamsburg &amp; Water Country USA</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>New Step, Acadex</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>New Step, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>Ride Operator / Culinary Operations</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>ปกติ: 09:30 – 18:00 (8 ชม.)
 พีค: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึก)</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>ฐาน $14.50 / OT $21.75</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>$115</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="J42" s="10" t="inlineStr">
         <is>
           <t>สวนสนุกธีมยุโรปชื่อดัง, บัตรเข้าสวนสนุกและสวนน้ำฟรี, หอพักพนักงาน Williamsburg</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr">
+      <c r="K42" s="10" t="inlineStr">
         <is>
           <t>🏰 Kingsmill Resort (ริมแม่น้ำ James River): Banquet Server/Busser งานจัดเลี้ยง 18:30-23:00 น. (ทิปสด $50-$90/คืน)</t>
         </is>
       </c>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="L42" s="10" t="inlineStr">
         <is>
           <t>🦀 Captain George’s Seafood Buffet: Busser/Dishwasher บุฟเฟต์ซีฟู้ดยักษ์ใหญ่ 18:30-23:30 น. (คนแน่นมาก ทิปดี)</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr">
+      <c r="M42" s="10" t="inlineStr">
         <is>
           <t>🥞 Cracker Barrel / Pancake House: ผู้ช่วยครัว/ล้างจานรอบค่ำ 18:00-22:00 น. ($14.50/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Tier A - Virginia (VA)</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Virginia Beach Oceanfront Resorts &amp; Boardwalk</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>IEE, New Step, Acadex</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>IEE, New Step, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>Housekeeping / Beach Attendant</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:30 – 16:30 (8 ชม.)
 พีค: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>$15 - $30</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>$130</t>
         </is>
       </c>
-      <c r="J40" s="10" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>เมืองตากอากาศชายทะเลเวอร์จิเนีย มีทางเดินเลียบหาดยาว 3 ไมล์, รถราง Wave Trolley สะดวก</t>
         </is>
       </c>
-      <c r="K40" s="10" t="inlineStr">
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>🍺 Waterman’s Surfside Grille: Barback/Busser ร้านริมหาดคนแน่น 18:00-00:30 น. (ทิปสด $70-$120/คืน)</t>
         </is>
       </c>
-      <c r="L40" s="10" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>🦀 Catch 31 Fish Bar: Food Runner/Busser 18:00-23:30 น. (ทิปดี)</t>
         </is>
       </c>
-      <c r="M40" s="10" t="inlineStr">
+      <c r="M43" s="7" t="inlineStr">
         <is>
           <t>🍕 Dough Boy’s California Pizza: ผู้ช่วยครัว/ล้างจาน 18:30-00:00 น. ($14.50/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Tier A - New Jersey (NJ)</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Morey’s Piers &amp; Beachfront Waterparks (Wildwood, NJ)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>OEG, IEE, New Step, IEO</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Pier Services</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 11:00 – 19:00 (8 ชม.)
+พีค: 10:30 – 23:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>45 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกริมสะพานปลาชานหาดที่ใหญ่ที่สุดในฝั่ง East Coast, เล่นเครื่องเล่นฟรี, เมืองจักรยาน</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>🍕 Mack’s Pizza / Sam’s Pizza (Boardwalk): ล้างจาน/ทำพิซซ่ากะดึก 19:30-01:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>🍺 The Wharf Restaurant &amp; Bar: Barback/Busser ร้านอาหารริมน้ำ 19:00-01:00 น. (ทิปสด $70-$120/คืน)</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>🍦 Curley’s Fries / Kohr Brothers: แคชเชียร์/ตักไอศกรีม 19:00-23:30 น. ($15.50/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Tier A - South Dakota (SD)</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Xanterra Mount Rushmore / Keystone Lodges</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>OEG, IEE, Higher</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Higher, IEO</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Retail / Food Service / Housekeeping</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:30 – 16:30 (8 ชม.)
 พีค: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>ทำงานหน้าอนุสรณ์สถานแห่งชาติ Mount Rushmore, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
         </is>
       </c>
-      <c r="K41" s="7" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>🍔 Carver’s Cafe at Mt Rushmore: ล้างจาน/ปิดครัว 17:00-21:30 น. (ขอ OT ในอุทยาน $23.25/ชม.)</t>
         </is>
       </c>
-      <c r="L41" s="7" t="inlineStr">
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>🥩 Ruby House Restaurant (Keystone): Busser ร้านอาหารธีมคาวบอยย้อนยุค 17:30-22:30 น. ($13/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr">
+      <c r="M45" s="7" t="inlineStr">
         <is>
           <t>🚂 1880 Train / Keystone Gift Shops: พนักงานร้านของฝาก/สถานีรถไฟโบราณ 17:00-21:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>Tier A - South Dakota (SD)</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Custer State Park Resorts (State Game Lodge / Sylvan)</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Higher, Acadex</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Higher, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>Guest Service / Housekeeping</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>ปกติ: 07:30 – 15:30 (8 ชม.)
 พีค: 07:00 – 16:30 (9 ชม.)</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>$105 (รวมกิน)</t>
         </is>
       </c>
-      <c r="J42" s="10" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>อุทยานธรรมชาติฝูงควายไบซัน Custer SP, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
         </is>
       </c>
-      <c r="K42" s="10" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>🥩 State Game Lodge Dining Room: Busser ร้านสเต๊กควายไบซันหรู 17:00-22:00 น. ($13/ชม. + ทิปสด $50-$80)</t>
         </is>
       </c>
-      <c r="L42" s="10" t="inlineStr">
+      <c r="L46" s="10" t="inlineStr">
         <is>
           <t>🍔 Black Hills Burger &amp; Bun (เมือง Custer): ล้างจาน/ครัว 17:00-21:30 น. ($15/ชม. + กินฟรี)</t>
         </is>
       </c>
-      <c r="M42" s="10" t="inlineStr">
+      <c r="M46" s="10" t="inlineStr">
         <is>
           <t>🏕️ Sylvan Lake General Store: พนักงานมินิมาร์ท/เช่าเรือแคนู 16:30-21:00 น.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Tier A - South Dakota (SD)</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Wall Drug Store (Wall, SD)</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>IEE, Acadex</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Retail / Restaurant Staff / Fast Food</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีค: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>45 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>$85 (ถูกมาก)</t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>ห้างคาวบอยระดับตำนานของอเมริกา จุดแวะพักยอดฮิตก่อนเข้า Badlands NP, หอพักราคาถูก</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>☕ Wall Drug Western Art Dining Room: Busser/Steward 17:00-22:00 น. (ขอ OT ในตัว $23.25)</t>
         </is>
       </c>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>🍩 Wall Drug Famous Donut Kitchen: ช่วยทำโดนัท/เบเกอรี่รอบเย็น 16:30-21:00 น.</t>
         </is>
       </c>
-      <c r="M43" s="7" t="inlineStr">
+      <c r="M47" s="7" t="inlineStr">
         <is>
           <t>🌵 Badlands Saloon &amp; Grille: Barback/ล้างจาน 18:00-23:00 น. ($14.50/ชม. + ทิป)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>Tier A - South Dakota (SD)</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Deadwood Historic Hotels &amp; Casinos (The Lodge at Deadwood)</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>Higher, New Step</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Higher, New Step, IEO</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>Housekeeping / Food &amp; Beverage</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีค: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>$20 - $50</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>$100</t>
         </is>
       </c>
-      <c r="J44" s="10" t="inlineStr">
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>เมืองคาวบอยคาสิโนประวัติศาสตร์ ปลอดภาษีรัฐ 0%, มีรถราง Deadwood Trolley $1</t>
         </is>
       </c>
-      <c r="K44" s="10" t="inlineStr">
+      <c r="K48" s="10" t="inlineStr">
         <is>
           <t>🥩 Deadwood Grille / O’Shea’s: Busser/Runner 17:30-23:00 น. ($13/ชม. + ทิปสด $50-$90/คืน)</t>
         </is>
       </c>
-      <c r="L44" s="10" t="inlineStr">
+      <c r="L48" s="10" t="inlineStr">
         <is>
           <t>🎰 Mineral Palace / Silverado Casino: Barback บาร์ในคาสิโน 18:30-01:00 น. (ทิปดี)</t>
         </is>
       </c>
-      <c r="M44" s="10" t="inlineStr">
+      <c r="M48" s="10" t="inlineStr">
         <is>
           <t>🍕 Mustang Sally’s Sports Bar: ผู้ช่วยครัว/ล้างจาน 18:00-00:00 น. ($14.50/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Tier A - Utah (UT)</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Zion National Park Lodge (Xanterra Springdale)</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>OEG, IEE, Acadex</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Hospitality Crew / Housekeeping</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 07:30 – 15:30 (8 ชม.)
 พีค: 07:00 – 16:30 (9 ชม.)</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>$110</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>อุทยานแห่งชาติหุบเขาผาแดง Zion NP, มีรถชัตเติลบัสฟรีวิ่งตลอดถนน Springdale</t>
         </is>
       </c>
-      <c r="K45" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>🌮 Bit &amp; Spur Restaurant &amp; Saloon: Busser/Barback 17:30-23:00 น. ($13/ชม. + ทิปสดแขกต่างชาติ $50-$90/คืน)</t>
         </is>
       </c>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>🍔 Oscar’s Cafe (Springdale): Food Runner/Busser 17:00-22:00 น. ($13/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
+      <c r="M49" s="7" t="inlineStr">
         <is>
           <t>🍺 Zion Canyon Brew Pub: ล้างจาน/ผู้ช่วยครัวหน้าปากทางเข้าอุทยาน 18:00-23:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>Tier A - Utah (UT)</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>Ruby’s Inn / Bryce Canyon Grand Hotel</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>Higher, IEE, Acadex</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Higher, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>Housekeeping / Fast Food / Retail</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
 พีค: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>$100</t>
         </is>
       </c>
-      <c r="J46" s="10" t="inlineStr">
+      <c r="J50" s="10" t="inlineStr">
         <is>
           <t>อาณาจักรโรงแรมและรีสอร์ต Ruby’s Inn หน้าปากทาง Bryce Canyon NP, หอพักพนักงานใกล้ที่ทำงาน</t>
         </is>
       </c>
-      <c r="K46" s="10" t="inlineStr">
+      <c r="K50" s="10" t="inlineStr">
         <is>
           <t>🥩 Cowboy’s Buffet &amp; Steak Room (ในเครือ): Busser/Steward 17:00-22:30 น. (ขอ OT ในเครือ $22.50/ชม.)</t>
         </is>
       </c>
-      <c r="L46" s="10" t="inlineStr">
+      <c r="L50" s="10" t="inlineStr">
         <is>
           <t>🤠 Ebenezer’s Barn &amp; Grill: Food Runner งานดินเนอร์โชว์คาวบอย 18:00-22:00 น. (ได้ส่วนแบ่งทิป)</t>
         </is>
       </c>
-      <c r="M46" s="10" t="inlineStr">
+      <c r="M50" s="10" t="inlineStr">
         <is>
           <t>🛒 Ruby’s General Store &amp; Diner: แคชเชียร์/ผู้ช่วยครัว 17:00-21:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Tier A - Utah (UT)</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Park City Mountain Resort (Vail Resorts - Park City)</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>OEG, Acadex</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Mountain Host / Housekeeping / F&amp;B</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:30 – 16:30 (8 ชม.)
 พีค: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>ฐาน $17.50 / OT $26.25</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>$150</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>สกีรีสอร์ตและเมืองภูเขาที่ใหญ่ที่สุดในสหรัฐฯ, ระบบรถเมล์ฟรีทั้งเมือง Park City Transit</t>
         </is>
       </c>
-      <c r="K47" s="7" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>🥩 High West Distillery &amp; Saloon (Main Street): Barback/Busser โรงกลั่นวิสกี้ดัง 17:30-23:30 น. (ทิปสด $80-$140/คืน)</t>
         </is>
       </c>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>🍕 Red Banjo Pizza (Historic Main St): ล้างจาน/ผู้ช่วยครัว 18:00-23:00 น. ($16/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="M47" s="7" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr">
         <is>
           <t>🛒 Freshies Lobster Co. / Local Cafes: Food Runner 17:00-21:30 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>Tier A - Maine (ME)</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Bar Harbor Grand Hotel / Harborside Hotel</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>Acadex, OEG, Higher</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Acadex, OEG, Higher, IEO</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>Housekeeping / Laundry</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
 พีค: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>$130</t>
         </is>
       </c>
-      <c r="J48" s="10" t="inlineStr">
+      <c r="J52" s="10" t="inlineStr">
         <is>
           <t>เมืองตากอากาศชายทะเล Bar Harbor &amp; อุทยาน Acadia NP, รถบัส Island Explorer ฟรี</t>
         </is>
       </c>
-      <c r="K48" s="10" t="inlineStr">
+      <c r="K52" s="10" t="inlineStr">
         <is>
           <t>🦞 Stewman’s Lobster Pound (ริมทะเล): Busser/Barback ร้านกุ้งล็อบสเตอร์ 17:30-23:00 น. ($13/ชม. + ทิปสด $60-$120/คืน)</t>
         </is>
       </c>
-      <c r="L48" s="10" t="inlineStr">
+      <c r="L52" s="10" t="inlineStr">
         <is>
           <t>🍺 Geddy’s Down Under / The Chart Room: Busser/Runner 18:00-23:30 น. (ทิปสดแน่นมาก)</t>
         </is>
       </c>
-      <c r="M48" s="10" t="inlineStr">
+      <c r="M52" s="10" t="inlineStr">
         <is>
           <t>🍦 Ben &amp; Bill’s Chocolate Emporium: พนักงานตักไอศกรีม/แคชเชียร์ 17:00-22:00 น. ($15.50/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>Tier A - Maine (ME)</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Cliff House Maine (Cape Neddick / Ogunquit)</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Higher, Acadex</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Higher, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Housekeeping / Culinary / Stewarding</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีค: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>ฐาน $17.00 / OT $25.50</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>$135</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>รีสอร์ตหรูบนหน้าผาริมมหาสมุทรแอตแลนติก แขกไฮเอนด์ระดับมหาเศรษฐีบอสตันและนิวยอร์ก</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>🦞 The Tiller Restaurant (ในรีสอร์ต): Busser ร้าน Fine Dining วิวมหาสมุทร 17:30-23:00 น. (ทิปสด $70-$130/คืน)</t>
         </is>
       </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>🍺 Nubb’s Lobster Shack (ในรีสอร์ต): Food Runner/Barback 17:00-22:30 น. (ขอ OT ในรีสอร์ต $25.50)</t>
         </is>
       </c>
-      <c r="M49" s="7" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>🍦 Ogunquit Beach Cafes: ผู้ช่วยครัว/บริการรอบเย็น</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>Tier A - Maine (ME)</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>The Nonantum Resort (Kennebunkport, ME)</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>Higher, Acadex</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Higher, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>Housekeeping / Banquet / F&amp;B</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
 พีค: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>$20 - $50</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>$125</t>
         </is>
       </c>
-      <c r="J50" s="10" t="inlineStr">
+      <c r="J54" s="10" t="inlineStr">
         <is>
           <t>รีสอร์ตตากอากาศริมน้ำประวัติศาสตร์ เมืองของประธานาธิบดีบุช, หอพักพนักงาน Kennebunkport</t>
         </is>
       </c>
-      <c r="K50" s="10" t="inlineStr">
+      <c r="K54" s="10" t="inlineStr">
         <is>
           <t>🦞 The Clam Shack (สะพาน Kennebunkport): ล้างจาน/ทอดซีฟู้ดร้านดัง 17:30-22:30 น. ($16/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="L50" s="10" t="inlineStr">
+      <c r="L54" s="10" t="inlineStr">
         <is>
           <t>🥩 Ocean Restaurant: Busser ร้านอาหารหรูริมน้ำ 18:00-23:00 น. (ทิปสด $60-$100/คืน)</t>
         </is>
       </c>
-      <c r="M50" s="10" t="inlineStr">
+      <c r="M54" s="10" t="inlineStr">
         <is>
           <t>🍦 Rococo Artisan Ice Cream: ตักไอศกรีม 17:00-22:00 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Tier A - Ohio (OH)</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Cedar Point Amusement Park &amp; Resorts (Sandusky)</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>OEG, IEE Thailand</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE Thailand, IEO</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>Ride Operator / Food Service</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 10:00 – 18:30 (8 ชม.)
 พีค: 09:30 – 22:30 (12 ชม. สวนสนุกปิดดึก)</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>ฐาน $14.50 / OT $21.75</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>46 – 52 ชม./wk</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>$80 (ถูกสุด)</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>สวนสนุกเครื่องเล่นระดับโลก, หอพักราคาถูกที่สุดในอเมริกา ($80/wk), รถบัสรับส่งฟรี, เล่นสวนสนุกฟรี</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>🏨 Hotel Breakers / Castaway Bay (ในสวนสนุก): ล้างจาน/แม่บ้านกะค่ำ 19:00-00:00 น. (ขอ OT ในสวนสนุก $21.75/ชม.)</t>
         </is>
       </c>
-      <c r="L51" s="7" t="inlineStr">
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>🍖 Famous Dave’s BBQ (Cedar Point Marina): Busser/Dishwasher 18:30-23:30 น. ($13/ชม. + ทิปสด)</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr">
+      <c r="M55" s="7" t="inlineStr">
         <is>
           <t>🐴 Thirsty Pony / Kalahari Sandusky: Barback/Busser ร้านอาหารใกล้เคียง 19:00-00:30 น.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>Tier A - Ohio (OH)</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>Kings Island Amusement Park (Mason / Cincinnati)</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>OEG, IEE Thailand</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>OEG, IEE Thailand, IEO</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>Ride Operator / Park Services / Culinary</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>ปกติ: 10:00 – 18:30 (8 ชม.)
 พีค: 09:30 – 22:30 (12 ชม.)</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>ฐาน $14.50 / OT $21.75</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>$90</t>
         </is>
       </c>
-      <c r="J52" s="10" t="inlineStr">
+      <c r="J56" s="10" t="inlineStr">
         <is>
           <t>สวนสนุกชั้นนำเครือ Cedar Fair ใกล้เมือง Cincinnati, หอพักพนักงาน + รถรับส่งฟรี</t>
         </is>
       </c>
-      <c r="K52" s="10" t="inlineStr">
+      <c r="K56" s="10" t="inlineStr">
         <is>
           <t>🍕 Mason Local Pizzerias &amp; Diners: ล้างจาน/ผู้ช่วยครัวรอบดึก 19:00-00:00 น. ($14.50/ชม.)</t>
         </is>
       </c>
-      <c r="L52" s="10" t="inlineStr">
+      <c r="L56" s="10" t="inlineStr">
         <is>
           <t>🍦 Greaters Ice Cream: พนักงานตักไอศกรีมชื่อดัง 19:00-23:00 น. ($14.50/ชม.)</t>
         </is>
       </c>
-      <c r="M52" s="10" t="inlineStr">
+      <c r="M56" s="10" t="inlineStr">
         <is>
           <t>🏨 Great Wolf Lodge Mason (ข้างๆ สวนสนุก): แม่บ้าน/ผู้ช่วยครัวกะค่ำ (ขอทำเพิ่มได้)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Tier A - Colorado (CO)</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>YMCA of the Rockies (Estes Park Center)</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Higher, IEE, Acadex</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Higher, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Housekeeping / Food Service</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 07:30 – 15:30 (8 ชม.)
 พีค: 07:00 – 16:30 (9 ชม.)</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>$110 (รวมกิน)</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr">
+      <c r="J57" s="7" t="inlineStr">
         <is>
           <t>แคมป์รีสอร์ตกลางเทือกเขา Rocky Mountain NP, หอพัก+อาหารบุฟเฟต์ 3 มื้อ, รถชัตเติลบัสเข้าเมืองฟรี</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr">
+      <c r="K57" s="7" t="inlineStr">
         <is>
           <t>🏨 The Stanley Hotel (โรงแรมประวัติศาสตร์ The Shining): Busser/Steward ร้านอาหารหรู 17:30-23:00 น. (ทิปสด $50-$90)</t>
         </is>
       </c>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="L57" s="7" t="inlineStr">
         <is>
           <t>🍔 Penelope’s Old Time Burgers: ผู้ช่วยครัว/ทอดเบอร์เกอร์ 17:00-21:30 น. ($15/ชม. + กินฟรี)</t>
         </is>
       </c>
-      <c r="M53" s="7" t="inlineStr">
+      <c r="M57" s="7" t="inlineStr">
         <is>
           <t>🍺 Estes Park Brewery / Rock Cut Brewing: ล้างแก้ว/ผู้ช่วยบาร์ 18:00-22:30 น. ($15/ชม.)</t>
         </is>

--- a/Work_and_Travel_Master_Job_Database_2027.xlsx
+++ b/Work_and_Travel_Master_Job_Database_2027.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top Employers Masterlist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier S-A Jobs &amp; 2nd Options" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12-Week Cashflow Simulator" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agency Directory &amp; Contacts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top Employers (Summer Only)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier S-A Summer Jobs &amp; Options" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summer 12-Wk Simulator (พ.ค-ก.ย)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summer Agency Directory" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,8 +502,8 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
@@ -526,7 +526,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ชื่องาน / สถานที่ทำงาน (Employer)</t>
+          <t>ชื่องาน / สถานที่ทำงาน (Summer Host)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ตำแหน่ง (Position / Role)</t>
+          <t>ตำแหน่งงาน Summer (Role)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>⏱️ เวลาทำงานจริง (ช่วงปกติ / ช่วงพีค)</t>
+          <t>⏱️ เวลาทำงานจริง (ปกติ / พีคซัมเมอร์)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>ชั่วโมงทำงานจริง (คิดเผื่อหัว-ท้ายซีซัน)</t>
+          <t>ชม. ทำงานจริงเฉลี่ยซัมเมอร์ (ชม./wk)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>สวัสดิการ (อาหาร ฟรี หรือ อื่นๆ)</t>
+          <t>สวัสดิการซัมเมอร์ (อาหาร / บัตรผ่าน / ส่วนลด)</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Denali Princess Wilderness Lodge</t>
+          <t>Denali Princess Wilderness Lodge (Summer Season)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -599,7 +599,7 @@
       <c r="F2" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 07:30 – 15:30 (8 ชม.)
-พีค: 07:00 – 17:30 (10 ชม. ควงกะ)</t>
+พีคซัมเมอร์ (มิ.ย.-ส.ค.): 07:00 – 17:30 (10 ชม. ควงกะ)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>50 – 54 ชม./สัปดาห์ (พีค 58-62 ชม. / หัวท้าย 35-42 ชม.)</t>
+          <t>50 – 54 ชม./wk (พีคจัด 58-62 ชม. / หัวท้าย พ.ค., ก.ย. 35-42 ชม.)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Denali Princess Wilderness Lodge</t>
+          <t>Denali Princess Wilderness Lodge (Summer Season)</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -657,7 +657,7 @@
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 16:00 – 00:00 (8 ชม.)
-พีค: 15:00 – 01:30 (10.5 ชม.)</t>
+พีคซัมเมอร์: 15:00 – 01:30 (10.5 ชม.)</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>50 – 55 ชม./สัปดาห์ (ควงกะค่ำได้ง่าย)</t>
+          <t>50 – 55 ชม./wk (ควงกะ Banquet และรอบรถไฟได้)</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Denali Princess Wilderness Lodge</t>
+          <t>Denali Princess Wilderness Lodge (Summer Season)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 หรือ 12:00 – 20:30
-พีค: 07:00 – 18:30 (ตามรอบรถไฟ)</t>
+พีคซัมเมอร์: 07:00 – 18:30 (ตามรอบรถไฟ)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>46 – 52 ชม./สัปดาห์</t>
+          <t>46 – 52 ชม./wk (ช่วงรถไฟ Wilderness Express วิ่งเต็มรอบ)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -762,18 +762,18 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>ขอทำเพิ่มหน้างาน (Internal 2nd Job)</t>
+          <t>ขอทำเพิ่มหน้างาน (Internal Summer 2nd Job)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Fleet Detailer (งานเสริมล้างรถทัวร์กะดึก)</t>
+          <t>Fleet Detailer (งานเสริมล้างรถทัวร์กะดึกซัมเมอร์)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 21:00 – 01:30 (4.5 ชม.)
-พีค: 21:00 – 02:30 (5.5 ชม.)</t>
+พีคซัมเมอร์: 21:00 – 02:30 (5.5 ชม.)</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>20 – 25 ชม./สัปดาห์ (ทำควบหลังงานหลักแม่บ้าน)</t>
+          <t>20 – 25 ชม./wk (ทำควบหลังงานหลักแม่บ้าน)</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Denali Bluffs Hotel</t>
+          <t>Denali Bluffs Hotel (เปิดเฉพาะ Summer)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 08:00 – 17:00 (9 ชม.)</t>
+พีคซัมเมอร์: 08:00 – 17:00 (9 ชม.)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>40 – 45 ชม./สัปดาห์ (หัวท้าย 32-38 ชม.)</t>
+          <t>40 – 45 ชม./wk (หัวท้าย 32-38 ชม.)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>โบนัสพิเศษ +$1.00/ชม. ท้ายทริป (ครบสัญญา), รถชัตเติลบัสขึ้น-ลงเขา Sugarloaf, ส่วนลดอาหารร้าน The Perk</t>
+          <t>โบนัสพิเศษ Summer Bonus +$1.00/ชม. ท้ายทริป (ครบสัญญา), รถชัตเติลบัส, ส่วนลดอาหาร The Perk</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Grande Denali Lodge</t>
+          <t>Grande Denali Lodge (เปิดเฉพาะ Summer)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -889,7 +889,7 @@
       <c r="F7" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>42 – 46 ชม./สัปดาห์ (หัวท้าย 35-40 ชม.)</t>
+          <t>42 – 46 ชม./wk (หัวท้าย 35-40 ชม.)</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>โบนัสพิเศษ +$1.00/ชม. ท้ายทริป (ครบสัญญา), โรงแรมหรู 4 ดาว, รถชัตเติลบัส, ส่วนลดอาหารห้องอาหาร Alpenglow</t>
+          <t>โบนัสพิเศษ Summer Bonus +$1.00/ชม. ท้ายทริป, โรงแรมหรู 4 ดาว, รถชัตเติลบัส</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Grande Denali Lodge</t>
+          <t>Grande Denali Lodge (เปิดเฉพาะ Summer)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -947,7 +947,7 @@
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 16:30 – 22:30 (6 ชม.)
-พีค: 16:00 – 23:30 (7.5 ชม.)</t>
+พีคซัมเมอร์: 16:00 – 23:30 (7.5 ชม.)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>40 – 45 ชม./สัปดาห์</t>
+          <t>40 – 45 ชม./wk</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>โบนัสพิเศษ +$1.00/ชม. ท้ายทริป, ทิปเงินสดจากแขกไฮเอนด์ร้านอาหารวิวพาโนรามา ($40-$70/คืน)</t>
+          <t>โบนัส +$1.00/ชม., ทิปเงินสดจากแขกไฮเอนด์ร้านอาหารวิวพาโนรามาช่วง Midnight Sun ($40-$70/คืน)</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Mt. McKinley Princess Lodge</t>
+          <t>Mt. McKinley Princess Lodge (Summer Season)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1005,7 +1005,7 @@
       <c r="F9" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>44 – 48 ชม./สัปดาห์ (หัวท้าย 35-40 ชม.)</t>
+          <t>44 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Fairbanks Princess Riverside Lodge</t>
+          <t>Fairbanks Princess Riverside Lodge (Summer Season)</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1063,7 +1063,7 @@
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 06:30 – 14:30 หรือ 15:00 – 23:00
-พีค: กะสลับตามรอบรถไฟ 8 ชม.</t>
+พีคซัมเมอร์: กะสลับตามรอบรถไฟ 8 ชม.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>36 – 40 ชม./สัปดาห์ (ไม่ค่อยมี OT)</t>
+          <t>36 – 40 ชม./wk (ไม่ค่อยมี OT)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Grand Teton Lodge Company (GTLC)</t>
+          <t>Grand Teton Lodge Company - Jackson Lake Lodge (Summer)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1121,7 +1121,7 @@
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:00 – 17:30 (10 ชม. ควงกะ)</t>
+พีคซัมเมอร์ (มิ.ย.-ส.ค.): 07:00 – 17:30 (10 ชม. ควงกะ)</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>54 – 60 ชม./สัปดาห์ (พีค 60-64 ชม. / หัวท้าย 40 ชม.)</t>
+          <t>54 – 60 ชม./wk (พีคซัมเมอร์ 60-64 ชม. / หัวท้าย 40 ชม.)</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$0 (ฟรี!)</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Grand Teton Lodge Company (GTLC)</t>
+          <t>Grand Teton Lodge Company - Colter Bay Village (Summer)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1173,13 +1173,13 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Kitchen Crew / Dishwasher / Food Prep</t>
+          <t>Cabin Attendant / Grocery Clerk / Marina</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 06:00 – 14:30 หรือ 15:00 – 23:00
-พีค: 14:00 – 00:30 (ช่วย Banquet)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>52 – 58 ชม./สัปดาห์ (ควงกะ Banquet ได้)</t>
+          <t>52 – 58 ชม./wk</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$0 (ฟรี!)</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>หอพักฟรี 100%! + อาหาร 3 มื้อ EDR + กินฟรีในครัว, สิทธิประโยชน์เครือ Vail Resorts</t>
+          <t>หอพักฟรี 100%! + อาหาร 3 มื้อ EDR, หมู่บ้านริมทะเลสาบ Jackson Lake สวยที่สุดในซัมเมอร์</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Xanterra Yellowstone Lodges</t>
+          <t>Xanterra Yellowstone Lodges (Summer Season)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 07:00 – 15:30 หรือ 15:00 – 23:30
-พีค: 06:30 – 16:30 (10 ชม.)</t>
+พีคซัมเมอร์: 06:30 – 16:30 (10 ชม.)</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>46 – 52 ชม./สัปดาห์ (หัวท้าย 38-42 ชม.)</t>
+          <t>46 – 52 ชม./wk (หัวท้าย 38-42 ชม.)</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>รวมหอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR, หอพักใหม่ Arnica, เที่ยวบ่อน้ำพุร้อนและไกเซอร์ Yellowstone ฟรี</t>
+          <t>รวมหอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR, หอพักใหม่ Arnica, เที่ยวบ่อน้ำพุร้อน Yellowstone ฟรี</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Under Canvas Grand Teton / Yellowstone</t>
+          <t>Under Canvas Grand Teton / Yellowstone (เปิดเฉพาะ Summer)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1295,7 +1295,7 @@
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>42 – 46 ชม./สัปดาห์</t>
+          <t>42 – 46 ชม./wk</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>แคมป์กระโจมซาฟารีหรู, อาหารพนักงาน, ทิปเงินสดจากแขกไฮเอนด์ บรรยากาศเป็นกันเอง</t>
+          <t>แคมป์กระโจมซาฟารีหรูเปิดเฉพาะ พ.ค.-ก.ย., อาหารพนักงาน, ทิปเงินสดจากแขกไฮเอนด์</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Kalahari Resorts &amp; Conventions</t>
+          <t>Kalahari Resorts &amp; Conventions (Summer Season)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1347,13 +1347,13 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Lifeguard / Housekeeping (งานหลัก)</t>
+          <t>Lifeguard / Housekeeping (งานหลักซัมเมอร์)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 09:30 – 18:00 หรือ 12:00 – 20:30
-พีค: 09:00 – 19:30 (10 ชม.)</t>
+พีคซัมเมอร์: 09:00 – 19:30 (10 ชม.)</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>38 – 44 ชม./สัปดาห์ (เกลี่ยกะ 40 ชม.)</t>
+          <t>38 – 44 ชม./wk (เกลี่ยกะ 40 ชม.)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Wisconsin Dells Riverfront Eateries</t>
+          <t>Wisconsin Dells Riverfront Eateries (Summer High Season)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1405,13 +1405,13 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Barback / Busser / Runner (งานที่สอง)</t>
+          <t>Barback / Busser / Runner (งานที่สองช่วงซัมเมอร์)</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 17:30 – 22:30 (5 ชม.)
-พีค: 17:00 – 00:30 (7.5 ชม.)</t>
+พีคซัมเมอร์: 17:00 – 00:30 (7.5 ชม.)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>20 – 25 ชม./สัปดาห์ (กะค่ำ 17:30-23:00)</t>
+          <t>20 – 25 ชม./wk (กะค่ำ 17:30-23:00)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Dollywood Theme Park &amp; Resorts</t>
+          <t>Dollywood Theme Park &amp; Splash Country (Summer Festival)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1469,7 +1469,7 @@
       <c r="F17" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึก)</t>
+พีคซัมเมอร์: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึกมีพลุทุกคืน)</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>44 – 50 ชม./สัปดาห์ (หัวท้าย 35-40 ชม.)</t>
+          <t>44 – 50 ชม./wk (หัวท้าย 35-40 ชม.)</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>ปลอดภาษีเงินได้รัฐ 0%, นั่งรถราง Pigeon Forge Trolley $1-$2.50/วัน, บัตรเข้าสวนสนุก Dollywood &amp; Splash Country ฟรี</t>
+          <t>ปลอดภาษีเงินได้รัฐ 0%, นั่งรถราง Pigeon Forge Trolley $1/วัน, บัตรเข้าสวนสนุก Dollywood ฟรี</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Premier Aquatics / High Sierra Pools</t>
+          <t>Premier Aquatics / High Sierra Pools (Summer Pools)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1521,13 +1521,13 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Pool Lifeguard</t>
+          <t>Pool Lifeguard (เปิดเฉพาะ Summer พ.ค.-ก.ย.)</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 10:30 – 19:30 (9 ชม.)
-พีค: 10:00 – 20:30 (10.5 ชม. สระเปิดยาว)</t>
+พีคซัมเมอร์: 10:00 – 20:30 (10.5 ชม. สระเปิดยาว)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>50 – 54 ชม./สัปดาห์ (การันตี OT 10-14 ชม.)</t>
+          <t>50 – 54 ชม./wk (การันตี OT 10-14 ชม. สม่ำเสมอ)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>การันตีชั่วโมง OT สม่ำเสมอ 10-14 ชม./สัปดาห์ ไม่ผันผวนตามนักท่องเที่ยว, อพาร์ตเมนต์แชร์กับเพื่อน</t>
+          <t>การันตีชั่วโมง OT แน่นอนสัปดาห์ละ 10-14 ชม., อพาร์ตเมนต์แชร์กับเพื่อน, รถไฟใต้ดิน Metro เข้า DC</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Cedar Point Amusement Park</t>
+          <t>Cedar Point Amusement Park (Summer Peak Season)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1585,7 +1585,7 @@
       <c r="F19" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 10:00 – 18:30 (8 ชม.)
-พีค: 09:30 – 22:30 (12 ชม. สวนสนุกปิดดึก)</t>
+พีคซัมเมอร์: 09:30 – 22:30 (12 ชม. สวนสนุกปิดดึก)</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>46 – 52 ชม./สัปดาห์ (หัวท้าย 38-42 ชม.)</t>
+          <t>46 – 52 ชม./wk (หัวท้าย 38-42 ชม.)</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>$80</t>
+          <t>$80 (ถูกสุด)</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -1625,18 +1625,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="31" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
@@ -1647,7 +1647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ระดับ Tier (ตามเว็บ)</t>
+          <t>ระดับ Tier (เว็บ)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ชื่องาน / สถานที่ทำงานหลัก (Employer)</t>
+          <t>ชื่องาน / สถานที่ทำงาน (Summer Host)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ตำแหน่งงานหลัก (Role)</t>
+          <t>ตำแหน่งงาน Summer (Role)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>⏱️ เวลาทำงานหลัก (ปกติ / พีค)</t>
+          <t>⏱️ เวลาทำงานจริง (ปกติ / พีคซัมเมอร์)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>ชั่วโมงงานหลัก (ชม./wk)</t>
+          <t>ชม. งานหลัก (ชม./wk)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -1697,22 +1697,22 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>สวัสดิการ (อาหาร ฟรี หรือ อื่นๆ)</t>
+          <t>สวัสดิการซัมเมอร์ (อาหาร ฟรี หรือ อื่นๆ)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>🔥 งานที่สองที่ทำต่อได้จริง (ตัวเลือกที่ 1)</t>
+          <t>🔥 งานที่สองซัมเมอร์ที่ทำต่อได้จริง (ตัวเลือก 1)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>🔥 งานที่สองที่ทำต่อได้จริง (ตัวเลือกที่ 2)</t>
+          <t>🔥 งานที่สองซัมเมอร์ที่ทำต่อได้จริง (ตัวเลือก 2)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>🔥 งานที่สองที่ทำต่อได้จริง (ตัวเลือกที่ 3)</t>
+          <t>🔥 งานที่สองซัมเมอร์ที่ทำต่อได้จริง (ตัวเลือก 3)</t>
         </is>
       </c>
     </row>
@@ -1948,4224 +1948,3859 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
+          <t>Mt. McKinley Princess Lodge (Trapper Creek)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Higher, OEG, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Kitchen</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>$10 - $20</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>44 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, รถรับส่ง, ชมวิวยอดเขาเดนาลี บรรยากาศสงบ</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>🥩 20,320 Alaskan Grill (ในโรงแรม): Busser/Steward กะค่ำ 17:30-22:30 น. (เรต OT $24/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Northland Wood Fired Pizza (ในโรงแรม): ผู้ช่วยทำพิซซ่า/ครัว 16:30-21:30 น. (เรต OT $24/ชม.)</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>🥐 Talkeetna Roadhouse: นั่งรถตู้พนักงานเข้าเมือง Talkeetna ช่วยล้างจาน/ทำขนมวันหยุด</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Alaska (AK)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Fairbanks Princess Riverside Lodge</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>IEE, Acadex, Higher, IEO</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Food Runner / Laundry / Steward</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 06:30 – 14:30 หรือ 15:00 – 23:00
+พีค: กะสลับตามรอบรถไฟ 8 ชม.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>$20 - $40</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>36 – 40 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>หอพักในเมืองแฟร์แบงก์ส + รถชัตเติลบัส, ใกล้ Walmart และร้านอาหารไทย หางาน 2 ง่าย</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>🛒 Walmart Supercenter Fairbanks: จัดสต็อกสินค้า/แคชเชียร์ 16:30-22:30 น. ($16-$17/ชม. มีรถเมล์ผ่าน)</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>🍜 Pad Thai Restaurant / Thai House: ผู้ช่วยครัว/เสิร์ฟ 17:00-22:30 น. (ทิปสด + กินอาหารไทยฟรี)</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>🍺 The Pump House Restaurant: Busser/Dishwasher ร้านอาหารริมน้ำดัง 17:30-23:00 น. ($15/ชม. + ทิป)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Alaska (AK)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
           <t>Seward Windsong Lodge &amp; Kenai Fjords Tours (Pursuit)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>OEG, Acadex, ALC, IEO</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Housekeeping / Tour Operations / F&amp;B</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีค: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>$20 - $50</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>$120</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>เมืองตากอากาศชายทะเล Seward ท่าเรือล่องเรือชมวาฬและธารน้ำแข็ง, หอพักพนักงาน, ล่องเรือฟรี</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>🦀 Ray’s Waterfront (ริมท่าเรือ Seward): Busser/Steward ร้านซีฟู้ดดัง 17:30-23:00 น. ($14/ชม. + ทิปสด $60-$100)</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>🍺 Seward Brewing Company: Barback/Dishwasher กะค่ำ 18:00-00:00 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>🛥️ Kenai Fjords Boat Cleaning: ล้างทำความสะอาดเรือทัวร์รอบเย็น 18:00-21:30 น. ($16.50/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Alaska (AK)</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Talkeetna Alaskan Lodge (Pursuit Collection)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>OEG, Acadex, Higher, IEO</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Housekeeping / Kitchen / Steward</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีค: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>$15 - $30</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>$115</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>โรงแรมหรูชมวิวยอดเขา Denali ในเมืองคาวบอย Talkeetna, หอพักพนักงาน + รถรับส่ง</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>🥩 Foraker Dining Room (ในโรงแรม): Busser ร้านอาหาร Fine Dining 17:30-23:00 น. (ทิปสด $50-$90/คืน)</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>🍕 Mountain High Pizza Pie: ผู้ช่วยทำพิซซ่า/ล้างจาน 18:00-23:30 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>🍺 Denali Brewing Company (Talkeetna Pub): Barback กะค่ำ 18:30-00:30 น. ($14/ชม. + ทิปสด)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Alaska (AK)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Alyeska Resort &amp; Hotel Alyeska (Girdwood)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>OEG, Higher, Acadex</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Housekeeping / Culinary / Lift Ops</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:30 – 16:30 (8 ชม.)
 พีค: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>$135</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>รีสอร์ตหรูระดับโลก นั่งกระเช้าชมวิวภูเขาและธารน้ำแข็ง, หอพักพนักงาน Glacier Valley</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>🥩 Seven Glaciers Restaurant (บนยอดเขา): Busser 17:30-23:00 น. (ร้าน 4 ดาว AAA ทิปมหาศาล $70-$120)</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>🍕 Coast Pizza / Girdwood Brewing: ผู้ช่วยครัว/Barback 18:00-23:00 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>🥖 The Bake Shop Girdwood: ช่วยเตรียมเบเกอรี่/ล้างจานช่วงเช้าตรู่หรือเย็น</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Alaska (AK)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Mt. McKinley Princess Lodge (Trapper Creek)</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Higher, OEG, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Housekeeping / Kitchen</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Copper River Princess Wilderness Lodge</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Higher, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Kitchen / Laundry</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
 พีค: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>$10 - $20</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>44 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, รถรับส่ง, ชมวิวยอดเขาเดนาลี บรรยากาศสงบ</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>🥩 20,320 Alaskan Grill (ในโรงแรม): Busser/Steward กะค่ำ 17:30-22:30 น. (เรต OT $24/ชม. + ทิป)</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>🍕 Northland Wood Fired Pizza (ในโรงแรม): ผู้ช่วยทำพิซซ่า/ครัว 16:30-21:30 น. (เรต OT $24/ชม.)</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>🥐 Talkeetna Roadhouse: นั่งรถตู้พนักงานเข้าเมือง Talkeetna ช่วยล้างจาน/ทำขนมวันหยุด</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>รีสอร์ตริมแม่น้ำ Copper River อุทยาน Wrangell-St. Elias, อาหาร EDR ฟรี 3 มื้อ</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>🐟 Two Rivers Salmon Grill (ในโรงแรม): Busser/Steward 17:30-22:30 น. (เรต OT $24/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>🛶 Copper Oar Rafting Base: ช่วยล้างทำความสะอาดเรือยาง/ชูชีพ 17:00-21:00 น. ($16/ชม.)</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>🌲 Whistle Stop Gift Shop: แคชเชียร์ร้านของฝากกะค่ำ 18:00-22:00 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Fairbanks Princess Riverside Lodge</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>IEE, Acadex, Higher, IEO</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Food Runner / Laundry / Steward</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 06:30 – 14:30 หรือ 15:00 – 23:00
-พีค: กะสลับตามรอบรถไฟ 8 ชม.</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>$20 - $40</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>36 – 40 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>$105</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>หอพักในเมืองแฟร์แบงก์ส + รถชัตเติลบัส, ใกล้ Walmart และร้านอาหารไทย หางาน 2 ง่าย</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>🛒 Walmart Supercenter Fairbanks: จัดสต็อกสินค้า/แคชเชียร์ 16:30-22:30 น. ($16-$17/ชม. มีรถเมล์ผ่าน)</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>🍜 Pad Thai Restaurant / Thai House: ผู้ช่วยครัว/เสิร์ฟ 17:00-22:30 น. (ทิปสด + กินอาหารไทยฟรี)</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>🍺 The Pump House Restaurant: Busser/Dishwasher ร้านอาหารริมน้ำดัง 17:30-23:00 น. ($15/ชม. + ทิป)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Wyoming (WY)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Grand Teton Lodge Company - Jackson Lake Lodge</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Acadex, Higher, OEG, IEE, IEO</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Housekeeping / Crew Member</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีค: 07:00 – 17:30 (10 ชม. ควงกะ)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>ฐาน $17.75 / OT $26.62</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>54 – 60 ชม./wk</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>$0 (ฟรี!)</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), ส่วนลด 40%, บัตรผ่าน 2 อุทยานฟรี</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>🍽️ Mural Room &amp; Pioneer Grill (ในโรงแรม): Busser 17:30-22:30 น. ได้เรต OT $26.62/ชม. + ทิป</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>🍸 Blue Heron Lounge (ในโรงแรม): Barback ช่วยยกน้ำแข็ง/ล้างแก้ว 18:00-23:30 น. (เรต OT $26.62 + Tip-Out)</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>🛶 Colter Bay Chuckwagon &amp; Marina: นั่งชัตเติลฟรีไปช่วยมินิมาร์ท/เรือแคนู 17:00-21:30 น.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Wyoming (WY)</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Grand Teton Lodge Company - Colter Bay Village</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Acadex, Higher, OEG, IEE, IEO</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Cabin Attendant / Grocery Clerk / Marina</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีค: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>ฐาน $17.75 / OT $26.62</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>52 – 58 ชม./wk</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>$0 (ฟรี!)</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), หมู่บ้านริมทะเลสาบ Jackson Lake</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>🥩 Chuckwagon Restaurant (ในหมู่บ้าน): Busser/Steward บุฟเฟต์มื้อเย็น 17:00-22:00 น. (เรต OT $26.62)</t>
         </is>
       </c>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>🛒 Colter Bay General Store: แคชเชียร์/เติมสต็อกมินิมาร์ท 17:30-22:00 น. (เรต OT $26.62)</t>
         </is>
       </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>🛶 Colter Bay Marina: ล้างเรือยนต์/เรือแคนู 16:30-20:30 น. (เรต OT $26.62)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Wyoming (WY)</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Signal Mountain Lodge (Grand Teton NP - Forever Resorts)</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Higher, Acadex, IEO</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Housekeeping / Front Desk / Marina</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
 พีค: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>$15 - $30</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>45 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>$110 (รวมกิน)</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>รีสอร์ตริมทะเลสาบ Signal Mountain, หอพักพนักงาน + อาหาร 3 มื้อ, ส่วนลดเช่าเรือ</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>🥩 The Peaks Restaurant (ในรีสอร์ต): Busser/Runner 17:30-22:30 น. ($14/ชม. + ทิปสด $50-$90/คืน)</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>🌮 Trapper Grill (ในรีสอร์ต): ผู้ช่วยครัว/ทำนาโชส์ 17:00-22:00 น. (ขอ OT $24.75/ชม.)</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr">
         <is>
           <t>⛽ Signal Mountain Gas Station &amp; Store: แคชเชียร์รอบค่ำ 17:00-21:30 น.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Wyoming (WY)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Xanterra Yellowstone Lodges (Old Faithful / Canyon)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>OEG, IEE Thailand, IEO</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Hospitality Crew / Kitchen Steward</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 07:00 – 15:30 หรือ 15:00 – 23:30
 พีค: 06:30 – 16:30 (10 ชม.)</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>ฐาน $15.70 / OT $23.55</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>46 – 52 ชม./wk</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>$120 (รวมกิน)</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>รวมหอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR, หอพักใหม่ Arnica, เที่ยวบ่อน้ำพุร้อน Yellowstone ฟรี</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>🌋 Old Faithful Snow Lodge Dining: Busser/Steward กะค่ำ 17:00-22:30 น. (เรต OT $23.55/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>🛍️ Delaware North General Stores: แคชเชียร์ร้านของฝากข้างๆ เดิน 3 นาที 17:00-21:30 น. ($15.50/ชม.)</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>🍻 Employee Pub &amp; Rec Hall: ผู้ช่วยผับพนักงาน/ทำความสะอาด 19:30-23:30 น.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Wyoming (WY)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Four Seasons Resort &amp; Snake River Lodge (Teton Village)</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>OEG, Acadex, IEO</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Housekeeping / Stewarding</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีค: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>ฐาน $17.50 / OT $26.25</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>45 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>รีสอร์ตหรู 5 ดาวใน Teton Village, หอพักพนักงาน, นั่งรถบัส START Bus ฟรี</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>🍺 The Mangy Moose Saloon (Teton Village): Barback/Busser ผับดัง 18:00-00:30 น. (ทิปสดเศรษฐี $60-$120/คืน)</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>🤠 Million Dollar Cowboy Bar (เมือง Jackson): นั่ง START Bus เข้าเมือง ทำ Barback 19:00-01:30 น.</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N15" s="7" t="inlineStr">
         <is>
           <t>🍕 Alpenhof Bistro: ล้างจาน/ผู้ช่วยครัว 17:30-22:30 น. ($16/ชม. + อาหารฟรี)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Wyoming (WY)</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>The Wort Hotel &amp; Silver Dollar Bar (Jackson Town)</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Acadex, OEG, IEO</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Housekeeping / Banquet Server / Steward</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
 พีค: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>ฐาน $17.00 / OT $25.50</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>$30 - $60</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>$150</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>โรงแรมประวัติศาสตร์ใจกลางเมือง Jackson, เดินทางสะดวกที่สุด มีร้านค้าล้อมรอบ</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>💵 Silver Dollar Bar (ในโรงแรม): Barback/Busser บาร์ดนตรีสดคนแน่น 18:30-01:00 น. (ทิปสด $70-$130/คืน)</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>🥩 Gun Barrel Steak &amp; Game House: Busser ร้านสเต๊กเนื้อสัตว์ป่า 17:30-22:30 น. ($14/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>🛒 Albertsons Jackson: จัดสต็อกสินค้ากะดึก 20:00-00:00 น. ($18/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Wyoming (WY)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Under Canvas Grand Teton / Yellowstone</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Higher Education, IEO</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Housekeeping / Guest Service</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:30 – 16:30 (8 ชม.)
 พีค: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>$50 - $100</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>42 – 46 ชม./wk</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>$100</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>แคมป์กระโจมซาฟารีหรู, อาหารพนักงาน, ทิปเงินสดจากแขกไฮเอนด์ บรรยากาศเป็นกันเอง</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>🏕️ Embers Restaurant (ในแกลมปิ้ง): Food Runner กะค่ำ 17:30-22:00 น. (ได้ทิปสดคืนละ $40-$60)</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>☕ Moose-Wilson Road Cafes: ผู้ช่วยบาริสต้า/เบเกอรี่ช่วงเช้าตรู่ 06:00-08:00 น. หรือเย็น</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>🛒 Jackson Town Local Diners: นั่งรถเข้าเมืองแจ็กสัน ทำงานร้านอาหารวันหยุด</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Wisconsin (WI)</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Kalahari Resorts &amp; Conventions (Wisconsin Dells)</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>OEG, Acadex, Higher, IEO, New Step</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Lifeguard / Housekeeping</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 09:30 – 18:00 หรือ 12:00 – 20:30
 พีค: 09:00 – 19:30 (10 ชม.)</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>38 – 44 ชม./wk</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>หอพัก Kalahari Village, บัตรเล่นสวนน้ำฟรี, เมืองปั่นจักรยาน 100%, หางาน 2 ง่ายที่สุดในอเมริกา</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>🍕 Moosejaw Pizza &amp; Dells Brewing: ปั่นจักรยาน 10 นาที Busser/Barback 18:30-23:30 น. ($13/ชม. + ทิปสด $60-$90/คืน)</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>🍔 Buffalo Phil’s Grille: Food Runner/Busser เสิร์ฟอาหารด้วยรถไฟจิ๋ว 18:00-22:30 น. ($13/ชม. + ทิปสด $50-$80)</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>🧀 MACS Mac &amp; Cheese / Dairy Queen: แคชเชียร์/ครัวกะดึก 18:30-23:00 น. ($14.50-$15.50/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Wisconsin (WI)</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Wilderness Resort &amp; Glacier Canyon Lodge (WI Dells)</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>OEG, IEE, Acadex, IEO</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Waterpark Attendant / Housekeeping</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 09:00 – 17:30 (8 ชม.)
 พีค: 08:30 – 19:00 (10 ชม.)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>40 – 46 ชม./wk</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>อาณาจักรรีสอร์ตสวนน้ำที่ใหญ่ที่สุดในอเมริกา (600 เอเคอร์), หอพักพนักงานในรีสอร์ต</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>🥩 Field’s at the Wilderness (สเต๊กหรูในรีสอร์ต): Busser 17:30-23:00 น. ($12/ชม. + ทิปสด $70-$120/คืน)</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>🍕 Sarento’s Restaurant (ในรีสอร์ต): Food Runner/ล้างจาน 17:00-22:30 น. (ขอ OT ในรีสอร์ต $22.50)</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>🍔 B-LUX Grill &amp; Bar: Barback/Busser ร้านเบอร์เกอร์คราฟต์เบียร์ 18:00-00:00 น. (ทิปสดดีมาก)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Wisconsin (WI)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Mt. Olympus Water &amp; Theme Park (WI Dells)</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>New Step, Acadex, Higher, IEO</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Ride Operator / Housekeeping / Lifeguard</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 09:30 – 18:00 (8 ชม.)
 พีค: 09:00 – 21:00 (11.5 ชม.)</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>$95</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>สวนสนุกธีมกรีกโบราณ โรลเลอร์โคสเตอร์ไม้, หอพักราคาถูก, ทำเลติดถนนใหญ่ Parkway</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>🥞 Paul Bunyan’s Cook Shanty: ล้างจาน/ทำความสะอาดรอบค่ำ 17:30-22:00 น. ($14.50/ชม. + กินฟรี)</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>🌭 Hot Dog Avenue: แคชเชียร์/ครัวปิด 18:00-22:30 น. ($14.50/ชม.)</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>🍺 Showboat Saloon (Downtown): Barback ผับดนตรีสด 19:00-01:30 น. (ทิปสดแน่น)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Wisconsin (WI)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Noah’s Ark Waterpark (Wisconsin Dells)</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>OEG, IEE, New Step, IEO</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Ride Operator / Park Services</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 09:00 – 17:30 (8 ชม.)
 พีค: 08:30 – 18:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>ฐาน $14.50 / OT $21.75</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>40 – 46 ชม./wk</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>$100</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>สวนน้ำกลางแจ้งใหญ่ที่สุดในอเมริกา, เล่นสวนน้ำฟรี, หอพักพนักงานใกล้ที่ทำงาน</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>🍻 Monk’s Bar &amp; Grill (Downtown Dells): ปั่นจักรยานไปทำ Barback/Busser 18:30-00:00 น. (ทิปสดแน่นมาก)</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>🍕 Pizza Pub Dells: ช่วยส่งอาหาร/ทำพิซซ่า/ล้างจานรอบดึก 18:00-00:00 น. ($14/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>🍦 Dairy Queen / Cold Stone Dells: ตักไอศกรีมกะค่ำ 18:00-22:30 น. ($14.50/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Wisconsin (WI)</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Chula Vista Resort &amp; Waterpark (WI Dells)</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Higher, Acadex, IEE, IEO</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Housekeeping / Lifeguard</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:30 – 16:30 (8 ชม.)
 พีค: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>40 – 45 ชม./wk</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>รีสอร์ตริมแม่น้ำ Wisconsin River, สวนน้ำในร่ม/กลางแจ้ง, หอพักในรีสอร์ต</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>🥩 Kaminski’s Chop House (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. ($12/ชม. + ทิปสดเศรษฐี $70-$120/คืน)</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>🌮 Mexicali Rose: Busser/Runner ร้านอาหารเม็กซิกันริมน้ำ 18:00-23:00 น. ($13/ชม. + ทิปสด)</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>🍕 Kilbourn City Grill (ในรีสอร์ต): ล้างจาน/ผู้ช่วยครัว 17:00-22:00 น. (ขอ OT ในรีสอร์ตได้)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Wisconsin (WI)</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Grand Geneva Resort &amp; Spa (Lake Geneva, WI)</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Acadex, OEG, IEO</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Housekeeping / Banquet / Culinary</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีค: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>$20 - $50</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>$110</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>รีสอร์ตหรูระดับ 4 เพชร AAA เมืองตากอากาศทะเลสาบคนรวยชิคาโก, หอพักพนักงาน</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>🥩 Geneva ChopHouse (ในรีสอร์ต): Busser 17:30-23:00 น. ($13/ชม. + ทิปสด $60-$100/คืน)</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>🍕 Popeye’s on Lake Geneva: Busser/Dishwasher ร้านอาหารริมทะเลสาบดัง 18:00-23:30 น. (ทิปดี)</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="N23" s="7" t="inlineStr">
         <is>
           <t>🍺 The Bottle Shop / Local Pubs: Barback ร้านคราฟต์เบียร์ 18:30-00:00 น.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Tennessee (TN)</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Dollywood Theme Park &amp; Splash Country (Pigeon Forge)</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>New Step, Acadex, IEO</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Ride Operator / Food Service / Retail</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 09:30 – 18:00 (8 ชม.)
 พีค: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึก)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>$110</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>ปลอดภาษีเงินได้รัฐ 0%, นั่งรถราง Pigeon Forge Trolley $1/วัน, บัตรเข้าสวนสนุก Dollywood ฟรี</t>
         </is>
       </c>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>🍗 Paula Deen’s Family Kitchen (The Island): นั่งรถรางไปทำ Busser 18:30-23:00 น. ($13/ชม. + ทิปสด $60-$90)</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>🍕 Mellow Mushroom Pizza: Barback/Busser ร้านพิซซ่าคราฟต์เบียร์ 18:30-00:00 น. ($12/ชม. + ทิปสด $50-$80)</t>
         </is>
       </c>
-      <c r="N23" s="7" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>🥞 Puckett’s Grocery &amp; Restaurant: Food Runner 18:00-23:00 น. ($13/ชม. + ทิป)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Tennessee (TN)</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>The Island in Pigeon Forge (Arcades &amp; Attractions)</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>New Step, Acadex, IEO</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Attractions Host / Retail / F&amp;B</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 10:00 – 18:00 (8 ชม.)
 พีค: 10:00 – 23:00 (กะดึก)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>$20 - $40</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>$110</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>ศูนย์รวมความบันเทิง ชิงช้าสวรรค์ยักษ์และร้านอาหารกลางเมือง, รถรางผ่านหน้าร้าน</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>🦜 Margaritaville Restaurant (ใน The Island): Busser/Barback 18:30-00:00 น. ($13/ชม. + ทิปสด $60-$100)</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>🥞 Timberwood Grill (ใน The Island): ล้างจาน/ผู้ช่วยครัว 18:00-23:30 น. ($14.50/ชม.)</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="N25" s="7" t="inlineStr">
         <is>
           <t>🍭 The Island Candy Kitchen: แคชเชียร์/ทำขนม 18:00-22:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Tennessee (TN)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Wilderness at the Smokies (Sevierville)</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>OEG, Acadex, Higher, IEO</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Lifeguard / Housekeeping</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 09:00 – 17:30 (8 ชม.)
 พีค: 08:30 – 19:30 (10.5 ชม.)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>สวนน้ำในร่มใหญ่ที่สุดในเทนเนสซี, ปลอดภาษีรัฐ 0%, หอพักพนักงาน Sevierville</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>🍏 Applewood Farmhouse Restaurant: Busser ร้านอาหารดังคนแน่น 18:00-22:30 น. (ทิปสด $60-$100/คืน)</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>🥩 Hidden Trail Restaurant (ในรีสอร์ต): ล้างจาน/Busser กะค่ำ 18:00-22:30 น. (ขอ OT ในรีสอร์ต $22.50/ชม.)</t>
         </is>
       </c>
-      <c r="N25" s="7" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>🛍️ Tanger Outlets Sevierville: จัดสต็อกสินค้า/ปิดร้าน 18:00-21:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Tennessee (TN)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Anakeesta Mountaintop Theme Park (Gatlinburg)</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Higher, IEE, IEO</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Guest Host / F&amp;B / Retail</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 09:00 – 17:30 (8 ชม.)
 พีค: 08:30 – 20:00 (10.5 ชม.)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>$15 - $30</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>$110</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>สวนสนุกธรรมชาติบนยอดเขา Gatlinburg นั่งกระเช้า Chondola, ปลอดภาษีรัฐ 0%</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>🍺 Smoky Mountain Brewery (Gatlinburg): Barback/Busser 18:30-00:30 น. ($12/ชม. + ทิปสด $70-$120/คืน)</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>🥩 Alamo Steakhouse: Busser/Dishwasher ร้านสเต๊กคาวบอย 17:30-23:00 น. ($13/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N27" s="7" t="inlineStr">
         <is>
           <t>🥞 Pancake Pantry (ร้านแพนเค้กอันดับ 1): ช่วยเตรียมวัตถุดิบ/ล้างจานรอบบ่าย-เย็น</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Tennessee (TN)</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Ober Mountain / Gatlinburg Area Lodges</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>IEE, New Step, IEO</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Attractions Operator / Retail</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 09:00 – 17:00 (8 ชม.)
 พีค: 08:30 – 19:00 (10 ชม.)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>40 – 46 ชม./wk</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>$110</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>กระเช้าลอยฟ้าและสวนสนุกบนยอดเขา Gatlinburg, ปลอดภาษีรัฐ 0%, เมืองเดินเท้า 100%</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>🥃 Ole Smoky Moonshine Distillery: พนักงานเช็ดแก้ว/เติมสต็อก/แคชเชียร์ 17:30-22:30 น. ($15/ชม.)</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>🥩 Calhoun’s in Gatlinburg: Busser/Runner ร้านบาร์บีคิวซี่โครงหมูชื่อดัง 17:30-23:00 น. (ทิปดี)</t>
         </is>
       </c>
-      <c r="N27" s="7" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>🍕 Best Italian Cafe &amp; Pizzeria: ผู้ช่วยครัว/ล้างจาน 18:00-23:30 น. ($14/ชม. + ทิป)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Texas (TX)</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Schlitterbahn Waterpark (New Braunfels / Galveston)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Lifeguard / Park Operations</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีค: 09:00 – 19:30 (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>สวนน้ำระดับตำนานของเท็กซัส, ปลอดภาษีเงินได้รัฐ 0%, เล่นสวนน้ำฟรี</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>🥩 Gristmill River Restaurant (Gruene): Busser ร้านอาหารริมแม่น้ำสุดคึกคัก 18:30-23:30 น. ($12/ชม. + ทิปสด $60-$100)</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>🦫 Buc-ee’s New Braunfels (ใหญ่ที่สุดในโลก): แคชเชียร์/Food Prep กะดึก 19:00-00:00 น. ($17-$19/ชม. จ่ายหนักมาก)</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Krause’s Cafe &amp; Biergarten: Barback/Runner ร้านเบียร์เยอรมัน 18:00-23:00 น. ($13/ชม. + ทิป)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Texas (TX)</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Kalahari Resorts &amp; Conventions Round Rock (Austin, TX)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Lifeguard / Housekeeping / F&amp;B</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีค: 09:00 – 19:30 (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>สวนน้ำในร่มใหญ่ที่สุดในอเมริกา สาขาเท็กซัส, ปลอดภาษีรัฐ 0%, ใกล้ออสติน</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>🥩 Double Cut Steak House (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. ($13/ชม. + ทิปสด $70-$120)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>🍕 Tom Foolerys Adventure Park (ในรีสอร์ต): คุมเครื่องเล่น/เกมรอบค่ำ 18:00-23:00 น. (ขอ OT $23.25)</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>🍔 Round Rock Local Eateries: Busser/ล้างจานร้านอาหารรอบนอก 18:30-23:30 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Texas (TX)</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Six Flags Fiesta Texas &amp; SeaWorld San Antonio</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>New Step, Higher, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Culinary</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีค: 09:30 – 21:30 (11.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>$115</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกและสวนน้ำระดับโลก ซานอันโตนิโอ, ปลอดภาษีรัฐ 0%, หอพักพนักงาน</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>🥩 The County Line BBQ (River Walk): Busser ร้านบาร์บีคิวริมแม่น้ำ 19:00-00:00 น. (ทิปสด $60-$100/คืน)</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>🎸 Hard Rock Cafe San Antonio: Food Runner/Busser 19:00-00:30 น. ($13/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>🌮 Boudro’s on the Riverwalk: ล้างจาน/ผู้ช่วยครัว 19:00-01:00 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Texas (TX)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Kemah Boardwalk &amp; Galveston Pleasure Pier</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>OEG, New Step, IEO</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Ride Operator / Retail / F&amp;B</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:30 – 18:30 (8 ชม.)
+พีค: 10:00 – 22:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>สวนสนุกริมอ่าวเม็กซิโก เครือ Landry’s, ปลอดภาษีรัฐ 0%, บรรยากาศชายทะเล</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>🦞 Aquarium Restaurant Kemah (ในเครือ): Busser ร้านอาหารใต้น้ำ 18:30-23:30 น. (ทิปสด $60-$100/คืน)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>🍤 Bubba Gump Shrimp Co. (Galveston Pier): Food Runner/Busser 18:30-00:00 น. (ทิปดี)</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>🏖️ The Spot (Galveston Seawall): Barback/Busser ร้านอาหารริมหาดคนแน่น 19:00-01:00 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Montana (MT)</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Glacier National Park Lodges (Pursuit / Xanterra)</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>OEG, Acadex, Higher, IEO</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Hospitality Crew / Housekeeping</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีค: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>46 – 52 ชม./wk</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>$115 (รวมกิน)</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>อุทยานธรรมชาติธารน้ำแข็ง Glacier NP, ปลอดภาษีมูลค่าเพิ่ม 0% Sales Tax, หอพัก+อาหาร EDR</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>🥩 Belton Chalet Dining Room: Busser/Steward ร้านอาหารประวัติศาสตร์ 17:30-22:30 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="M33" s="7" t="inlineStr">
         <is>
           <t>🛶 Glacier Raft Company Base: พนักงานล้างทำความสะอาดเรือยาง/อุปกรณ์ล่องแก่ง 17:00-21:30 น. ($16/ชม.)</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N33" s="7" t="inlineStr">
         <is>
           <t>🥐 West Glacier Bakery &amp; Cafe: ผู้ช่วยเตรียมวัตถุดิบ/ล้างจาน 17:00-22:00 น.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Montana (MT)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Many Glacier Hotel &amp; Glacier Park Lodge (East Glacier)</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>OEG, Acadex, IEO</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>Housekeeping / Dining Room / Steward</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>ปกติ: 07:30 – 15:30 (8 ชม.)
 พีค: 07:00 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>$15 - $30</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>46 – 52 ชม./wk</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>$115 (รวมกิน)</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="K34" s="10" t="inlineStr">
         <is>
           <t>โรงแรมสไตล์สวิสชาเลต์ริมทะเลสาบ Swiftcurrent Lake สวยที่สุดใน Glacier NP, อาหาร EDR 3 มื้อ</t>
         </is>
       </c>
-      <c r="L29" s="7" t="inlineStr">
+      <c r="L34" s="10" t="inlineStr">
         <is>
           <t>🥩 Ptarmigan Dining Room (ในโรงแรม): Busser 17:00-22:30 น. (เรต OT $24/ชม. + ทิปสด)</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="M34" s="10" t="inlineStr">
         <is>
           <t>☕ Heidi’s Snack Shop (ในโรงแรม): แคชเชียร์/ชงกาแฟ 16:30-21:30 น. (ขอ OT $24/ชม.)</t>
         </is>
       </c>
-      <c r="N29" s="7" t="inlineStr">
+      <c r="N34" s="10" t="inlineStr">
         <is>
           <t>🛶 Many Glacier Boat Tours: ช่วยเทียบเรือ/ล้างเรือทัวร์ 17:00-20:30 น.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Montana (MT)</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Big Sky Resort / Montage Big Sky</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Acadex, Higher, IEE, IEO</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>Mountain Operations / Housekeeping</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีค: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>ฐาน $17.50 / OT $26.25</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>46 – 52 ชม./wk</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>$140</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>รีสอร์ตภูเขาหรูหราไฮเอนด์, ค่าแรงฐานสูงมาก, มีรถบัส Skyline Bus ฟรี</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>🍺 Lone Peak Brewery (Town Center): Barback/Busser 17:30-23:30 น. ($15/ชม. + ทิปสดเศรษฐี $60-$100/คืน)</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr">
         <is>
           <t>🍖 The Riverhouse BBQ: Busser/Runner ร้านบาร์บีคิวริมแม่น้ำ Gallatin 17:00-22:30 น. ($14/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N35" s="7" t="inlineStr">
         <is>
           <t>🛒 Roxy’s Market Big Sky: พนักงานจัดสต็อกซูเปอร์มาร์เก็ต 18:00-22:00 น. ($17/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Maine (ME)</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Bar Harbor Grand Hotel / Harborside Hotel</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Acadex, OEG, Higher, IEO</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Housekeeping / Laundry</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Florida (FL)</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Universal Orlando Resort &amp; Volcano Bay</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Attractions Attendant / Culinary / Lifeguard</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีค: 09:00 – 22:00 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกระดับโลก ยูนิเวอร์แซล ออร์แลนโด, ปลอดภาษีเงินได้รัฐ 0%, บัตรเข้าสวนสนุกฟรี</t>
+        </is>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>🎸 Universal CityWalk Eateries: Food Runner/Busser บาร์ดึก 18:30-01:00 น. (ทิปสด $60-$100/คืน)</t>
+        </is>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>🍔 The Cowfish Sushi Burger Bar: ล้างจาน/ผู้ช่วยครัว 19:00-01:00 น. ($15/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>🍕 Red Oven Pizza Bakery: ผู้ช่วยทำพิซซ่ากะดึก 18:30-00:30 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Florida (FL)</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Busch Gardens Tampa Bay &amp; Adventure Island</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>New Step, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Food Service</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีค: 09:00 – 21:30 (11.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกโรลเลอร์โคสเตอร์อันดับ 1 ในแทมปาและสวนน้ำ, ปลอดภาษีรัฐ 0%</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Ybor City Historic Bars (แทมปา): Barback ผับประวัติศาสตร์ 19:00-01:30 น. (ทิปสด $60-$110/คืน)</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>🦀 Columbia Restaurant (ร้านสเปนชื่อดังที่สุด): Busser 18:30-23:30 น. (ทิปดี)</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>🍔 Portillo’s Hot Dogs Tampa: ครัว/แคชเชียร์รอบดึก 18:30-00:00 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Florida (FL)</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Gaylord Palms Resort &amp; Convention Center (Kissimmee)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, Higher</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Banquet Server / Steward</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>$125</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>รีสอร์ตศูนย์ประชุมโดมกระจกยักษ์ระดับ 4 ดาว Marriott, ปลอดภาษีรัฐ 0%</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>🥩 Old Hickory Steakhouse (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. (ทิปสด $70-$120)</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Wreckers Sports Bar (ในรีสอร์ต): Barback ผับกีฬาจอ 2 ชั้น 18:30-00:30 น. (ขอ OT ในรีสอร์ต $24/ชม.)</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>🛍️ Disney Springs Eateries: Food Runner ร้านอาหารฝั่งดิสนีย์ 19:00-01:00 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Maryland (MD)</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Premier Aquatics / High Sierra Pools (Bethesda/Rockville)</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Acadex, New Step, ALC, IEO</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Pool Lifeguard</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:30 – 19:30 (9 ชม.)
+พีค: 10:00 – 20:30 (10.5 ชม. สระเปิดยาว)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>50 – 54 ชม./wk (การันตี OT)</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>การันตีชั่วโมง OT แน่นอนสัปดาห์ละ 10-14 ชม., อพาร์ตเมนต์แชร์กับเพื่อน, รถไฟใต้ดิน Metro เข้า DC</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>🛒 Giant Food / Safeway: พนักงานจัดสต็อกสินค้ากะดึก 20:30-01:00 น. ($16-$17.50/ชม. มีสาขาใกล้ที่พัก)</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>🍜 Thai Tanic / Ruan Thai: ผู้ช่วยครัว/แพ็กอาหาร 20:00-23:30 น. (มีอาหารไทยฟรี)</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>🎯 Target / CVS Pharmacy: แคชเชียร์/ปิดร้าน 20:00-23:30 น. ($16.00/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Maryland (MD)</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Ocean City Boardwalk Hotels &amp; Resorts</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>IEE, New Step, OEG, IEO</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Ride Operator</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>$125</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายหาด Atlantic, รถบัส Coastal Highway วิ่ง 24 ชม., หางานสองง่ายมาก</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Seacrets Jamaica USA (ผับริมหาดยักษ์ใหญ่): Barback/Busser 18:00-01:30 น. ($12/ชม. + ทิปสดมหาศาล $80-$150/คืน)</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>🍟 Thrasher’s French Fries (ริมหาด): แคชเชียร์/ทอดเฟรนช์ฟรายส์ 18:00-23:00 น. ($15/ชม.)</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>🍺 Shenanigans Irish Pub: ล้างจาน/ผู้ช่วยบาร์ 18:30-00:30 น. ($14/ชม. + ทิป)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Maryland (MD)</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Jolly Roger Amusement Park &amp; Splash Mountain (Ocean City)</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>New Step, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Park Services</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 11:00 – 19:00 (8 ชม.)
+พีค: 10:00 – 23:00 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>45 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกและสวนน้ำที่ใหญ่ที่สุดใน Ocean City, เล่นสวนสนุกฟรี, มีรถเมล์ผ่านหน้าสวนสนุก</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>🦀 Higgins Crab House: Busser ร้านปูยักษ์ 19:30-00:30 น. ($13/ชม. + ทิปสด $60-$90/คืน)</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Dough Roller Pizza (Boardwalk): ล้างจาน/ทำพิซซ่ากะดึก 19:30-01:00 น. ($15/ชม.)</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>🍦 Dumser’s Dairyland: ตักไอศกรีม/แคชเชียร์ 19:00-23:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Virginia (VA)</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Busch Gardens Williamsburg &amp; Water Country USA</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>New Step, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>Ride Operator / Culinary Operations</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีค: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึก)</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>$115</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกธีมยุโรปชื่อดัง, บัตรเข้าสวนสนุกและสวนน้ำฟรี, หอพักพนักงาน Williamsburg</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>🏰 Kingsmill Resort (ริมแม่น้ำ James River): Banquet Server/Busser งานจัดเลี้ยง 18:30-23:00 น. (ทิปสด $50-$90/คืน)</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>🦀 Captain George’s Seafood Buffet: Busser/Dishwasher บุฟเฟต์ซีฟู้ดยักษ์ใหญ่ 18:30-23:30 น. (คนแน่นมาก ทิปดี)</t>
+        </is>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>🥞 Cracker Barrel / Pancake House: ผู้ช่วยครัว/ล้างจานรอบค่ำ 18:00-22:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Virginia (VA)</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Virginia Beach Oceanfront Resorts &amp; Boardwalk</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>IEE, New Step, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Beach Attendant</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายทะเลเวอร์จิเนีย มีทางเดินเลียบหาดยาว 3 ไมล์, รถราง Wave Trolley สะดวก</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Waterman’s Surfside Grille: Barback/Busser ร้านริมหาดคนแน่น 18:00-00:30 น. (ทิปสด $70-$120/คืน)</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>🦀 Catch 31 Fish Bar: Food Runner/Busser 18:00-23:30 น. (ทิปดี)</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Dough Boy’s California Pizza: ผู้ช่วยครัว/ล้างจาน 18:30-00:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>New Jersey (NJ)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Morey’s Piers &amp; Beachfront Waterparks (Wildwood, NJ)</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>OEG, IEE, New Step, IEO</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Pier Services</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 11:00 – 19:00 (8 ชม.)
+พีค: 10:30 – 23:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>45 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกริมสะพานปลาชานหาดที่ใหญ่ที่สุดในฝั่ง East Coast, เล่นเครื่องเล่นฟรี, เมืองจักรยาน</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>🍕 Mack’s Pizza / Sam’s Pizza (Boardwalk): ล้างจาน/ทำพิซซ่ากะดึก 19:30-01:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>🍺 The Wharf Restaurant &amp; Bar: Barback/Busser ร้านอาหารริมน้ำ 19:00-01:00 น. (ทิปสด $70-$120/คืน)</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>🍦 Curley’s Fries / Kohr Brothers: แคชเชียร์/ตักไอศกรีม 19:00-23:30 น. ($15.50/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>South Dakota (SD)</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Xanterra Mount Rushmore / Keystone Lodges</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Higher, IEO</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Retail / Food Service / Housekeeping</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>ทำงานหน้าอนุสรณ์สถานแห่งชาติ Mount Rushmore, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>🍔 Carver’s Cafe at Mt Rushmore: ล้างจาน/ปิดครัว 17:00-21:30 น. (ขอ OT ในอุทยาน $23.25/ชม.)</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>🥩 Ruby House Restaurant (Keystone): Busser ร้านอาหารธีมคาวบอยย้อนยุค 17:30-22:30 น. ($13/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>🚂 1880 Train / Keystone Gift Shops: พนักงานร้านของฝาก/สถานีรถไฟโบราณ 17:00-21:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>South Dakota (SD)</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Custer State Park Resorts (State Game Lodge / Sylvan)</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Higher, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>Guest Service / Housekeeping</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีค: 07:00 – 16:30 (9 ชม.)</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>$105 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>อุทยานธรรมชาติฝูงควายไบซัน Custer SP, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>🥩 State Game Lodge Dining Room: Busser ร้านสเต๊กควายไบซันหรู 17:00-22:00 น. ($13/ชม. + ทิปสด $50-$80)</t>
+        </is>
+      </c>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>🍔 Black Hills Burger &amp; Bun (เมือง Custer): ล้างจาน/ครัว 17:00-21:30 น. ($15/ชม. + กินฟรี)</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>🏕️ Sylvan Lake General Store: พนักงานมินิมาร์ท/เช่าเรือแคนู 16:30-21:00 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>South Dakota (SD)</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Wall Drug Store (Wall, SD)</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Retail / Restaurant Staff / Fast Food</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>45 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>$85 (ถูกมาก)</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>ห้างคาวบอยระดับตำนานของอเมริกา จุดแวะพักยอดฮิตก่อนเข้า Badlands NP, หอพักราคาถูก</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>☕ Wall Drug Western Art Dining Room: Busser/Steward 17:00-22:00 น. (ขอ OT ในตัว $23.25)</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>🍩 Wall Drug Famous Donut Kitchen: ช่วยทำโดนัท/เบเกอรี่รอบเย็น 16:30-21:00 น.</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>🌵 Badlands Saloon &amp; Grille: Barback/ล้างจาน 18:00-23:00 น. ($14.50/ชม. + ทิป)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>South Dakota (SD)</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Deadwood Historic Hotels &amp; Casinos (The Lodge at Deadwood)</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>Higher, New Step, IEO</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Food &amp; Beverage</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>เมืองคาวบอยคาสิโนประวัติศาสตร์ ปลอดภาษีรัฐ 0%, มีรถราง Deadwood Trolley $1</t>
+        </is>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
+          <t>🥩 Deadwood Grille / O’Shea’s: Busser/Runner 17:30-23:00 น. ($13/ชม. + ทิปสด $50-$90/คืน)</t>
+        </is>
+      </c>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>🎰 Mineral Palace / Silverado Casino: Barback บาร์ในคาสิโน 18:30-01:00 น. (ทิปดี)</t>
+        </is>
+      </c>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>🍕 Mustang Sally’s Sports Bar: ผู้ช่วยครัว/ล้างจาน 18:00-00:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Utah (UT)</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Zion National Park Lodge (Xanterra Springdale)</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Hospitality Crew / Housekeeping</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีค: 07:00 – 16:30 (9 ชม.)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>อุทยานแห่งชาติหุบเขาผาแดง Zion NP, มีรถชัตเติลบัสฟรีวิ่งตลอดถนน Springdale</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>🌮 Bit &amp; Spur Restaurant &amp; Saloon: Busser/Barback 17:30-23:00 น. ($13/ชม. + ทิปสดแขกต่างชาติ $50-$90/คืน)</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>🍔 Oscar’s Cafe (Springdale): Food Runner/Busser 17:00-22:00 น. ($13/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Zion Canyon Brew Pub: ล้างจาน/ผู้ช่วยครัวหน้าปากทางเข้าอุทยาน 18:00-23:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Utah (UT)</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Ruby’s Inn / Bryce Canyon Grand Hotel</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Higher, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Fast Food / Retail</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
 พีค: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>อาณาจักรโรงแรมและรีสอร์ต Ruby’s Inn หน้าปากทาง Bryce Canyon NP, หอพักพนักงานใกล้ที่ทำงาน</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>🥩 Cowboy’s Buffet &amp; Steak Room (ในเครือ): Busser/Steward 17:00-22:30 น. (ขอ OT ในเครือ $22.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>🤠 Ebenezer’s Barn &amp; Grill: Food Runner งานดินเนอร์โชว์คาวบอย 18:00-22:00 น. (ได้ส่วนแบ่งทิป)</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>🛒 Ruby’s General Store &amp; Diner: แคชเชียร์/ผู้ช่วยครัว 17:00-21:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Utah (UT)</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Park City Mountain Resort (Vail Resorts - Park City)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Mountain Host / Housekeeping / F&amp;B</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $17.50 / OT $26.25</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>สกีรีสอร์ตและเมืองภูเขาที่ใหญ่ที่สุดในสหรัฐฯ, ระบบรถเมล์ฟรีทั้งเมือง Park City Transit</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>🥩 High West Distillery &amp; Saloon (Main Street): Barback/Busser โรงกลั่นวิสกี้ดัง 17:30-23:30 น. (ทิปสด $80-$140/คืน)</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Red Banjo Pizza (Historic Main St): ล้างจาน/ผู้ช่วยครัว 18:00-23:00 น. ($16/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>🛒 Freshies Lobster Co. / Local Cafes: Food Runner 17:00-21:30 น. ($15/ชม. + ทิป)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Maine (ME)</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Bar Harbor Grand Hotel / Harborside Hotel</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>Acadex, OEG, Higher, IEO</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Laundry</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="I52" s="9" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>$130</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="K52" s="10" t="inlineStr">
         <is>
           <t>เมืองตากอากาศชายทะเล Bar Harbor &amp; อุทยาน Acadia NP, รถบัส Island Explorer ฟรี</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L52" s="10" t="inlineStr">
         <is>
           <t>🦞 Stewman’s Lobster Pound (ริมทะเล): Busser/Barback ร้านกุ้งล็อบสเตอร์ 17:30-23:00 น. ($13/ชม. + ทิปสด $60-$120/คืน)</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr">
+      <c r="M52" s="10" t="inlineStr">
         <is>
           <t>🍺 Geddy’s Down Under / The Chart Room: Busser/Runner 18:00-23:30 น. (ทิปสดแน่นมาก)</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr">
+      <c r="N52" s="10" t="inlineStr">
         <is>
           <t>🍦 Ben &amp; Bill’s Chocolate Emporium: พนักงานตักไอศกรีม/แคชเชียร์ 17:00-22:00 น. ($15.50/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Maine (ME)</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Cliff House Maine (Cape Neddick / Ogunquit)</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Higher, Acadex, IEO</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>Housekeeping / Culinary / Stewarding</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีค: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>ฐาน $17.00 / OT $25.50</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>$135</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>รีสอร์ตหรูบนหน้าผาริมมหาสมุทรแอตแลนติก แขกไฮเอนด์ระดับมหาเศรษฐีบอสตันและนิวยอร์ก</t>
         </is>
       </c>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>🦞 The Tiller Restaurant (ในรีสอร์ต): Busser ร้าน Fine Dining วิวมหาสมุทร 17:30-23:00 น. (ทิปสด $70-$130/คืน)</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="M53" s="7" t="inlineStr">
         <is>
           <t>🍺 Nubb’s Lobster Shack (ในรีสอร์ต): Food Runner/Barback 17:00-22:30 น. (ขอ OT ในรีสอร์ต $25.50)</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N53" s="7" t="inlineStr">
         <is>
           <t>🍦 Ogunquit Beach Cafes: ผู้ช่วยครัว/บริการรอบเย็น</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Maine (ME)</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>The Nonantum Resort (Kennebunkport, ME)</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>Higher, Acadex, IEO</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>Housekeeping / Banquet / F&amp;B</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
 พีค: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>$20 - $50</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>$125</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr">
+      <c r="K54" s="10" t="inlineStr">
         <is>
           <t>รีสอร์ตตากอากาศริมน้ำประวัติศาสตร์ เมืองของประธานาธิบดีบุช, หอพักพนักงาน Kennebunkport</t>
         </is>
       </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="L54" s="10" t="inlineStr">
         <is>
           <t>🦞 The Clam Shack (สะพาน Kennebunkport): ล้างจาน/ทอดซีฟู้ดร้านดัง 17:30-22:30 น. ($16/ชม. + ทิป)</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr">
+      <c r="M54" s="10" t="inlineStr">
         <is>
           <t>🥩 Ocean Restaurant: Busser ร้านอาหารหรูริมน้ำ 18:00-23:00 น. (ทิปสด $60-$100/คืน)</t>
         </is>
       </c>
-      <c r="N33" s="7" t="inlineStr">
+      <c r="N54" s="10" t="inlineStr">
         <is>
           <t>🍦 Rococo Artisan Ice Cream: ตักไอศกรีม 17:00-22:00 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Utah (UT)</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Zion National Park Lodge (Xanterra Springdale)</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>OEG, IEE, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Hospitality Crew / Housekeeping</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Ohio (OH)</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Cedar Point Amusement Park &amp; Resorts (Sandusky)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE Thailand, IEO</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Food Service</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีค: 09:30 – 22:30 (12 ชม. สวนสนุกปิดดึก)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>46 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>$80 (ถูกสุด)</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกเครื่องเล่นระดับโลก, หอพักราคาถูกที่สุดในอเมริกา ($80/wk), รถบัสรับส่งฟรี, เล่นสวนสนุกฟรี</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>🏨 Hotel Breakers / Castaway Bay (ในสวนสนุก): ล้างจาน/แม่บ้านกะค่ำ 19:00-00:00 น. (ขอ OT ในสวนสนุก $21.75/ชม.)</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>🍖 Famous Dave’s BBQ (Cedar Point Marina): Busser/Dishwasher 18:30-23:30 น. ($13/ชม. + ทิปสด)</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>🐴 Thirsty Pony / Kalahari Sandusky: Barback/Busser ร้านอาหารใกล้เคียง 19:00-00:30 น.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Ohio (OH)</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Kings Island Amusement Park (Mason / Cincinnati)</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>OEG, IEE Thailand, IEO</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>Ride Operator / Park Services / Culinary</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีค: 09:30 – 22:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>$90</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกชั้นนำเครือ Cedar Fair ใกล้เมือง Cincinnati, หอพักพนักงาน + รถรับส่งฟรี</t>
+        </is>
+      </c>
+      <c r="L56" s="10" t="inlineStr">
+        <is>
+          <t>🍕 Mason Local Pizzerias &amp; Diners: ล้างจาน/ผู้ช่วยครัวรอบดึก 19:00-00:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="M56" s="10" t="inlineStr">
+        <is>
+          <t>🍦 Greaters Ice Cream: พนักงานตักไอศกรีมชื่อดัง 19:00-23:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="N56" s="10" t="inlineStr">
+        <is>
+          <t>🏨 Great Wolf Lodge Mason (ข้างๆ สวนสนุก): แม่บ้าน/ผู้ช่วยครัวกะค่ำ (ขอทำเพิ่มได้)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Colorado (CO)</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>YMCA of the Rockies (Estes Park Center)</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Higher, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Food Service</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 07:30 – 15:30 (8 ชม.)
 พีค: 07:00 – 16:30 (9 ชม.)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>$110</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>อุทยานแห่งชาติหุบเขาผาแดง Zion NP, มีรถชัตเติลบัสฟรีวิ่งตลอดถนน Springdale</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>🌮 Bit &amp; Spur Restaurant &amp; Saloon: Busser/Barback 17:30-23:00 น. ($13/ชม. + ทิปสดแขกต่างชาติ $50-$90/คืน)</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>🍔 Oscar’s Cafe (Springdale): Food Runner/Busser 17:00-22:00 น. ($13/ชม. + ทิป)</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>🍺 Zion Canyon Brew Pub: ล้างจาน/ผู้ช่วยครัวหน้าปากทางเข้าอุทยาน 18:00-23:30 น. ($15/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Utah (UT)</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Ruby’s Inn / Bryce Canyon Grand Hotel</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Higher, IEE, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Housekeeping / Fast Food / Retail</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>42 – 48 ชม./wk</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>$100</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>อาณาจักรโรงแรมและรีสอร์ต Ruby’s Inn หน้าปากทาง Bryce Canyon NP, หอพักพนักงานใกล้ที่ทำงาน</t>
-        </is>
-      </c>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>🥩 Cowboy’s Buffet &amp; Steak Room (ในเครือ): Busser/Steward 17:00-22:30 น. (ขอ OT ในเครือ $22.50/ชม.)</t>
-        </is>
-      </c>
-      <c r="M35" s="7" t="inlineStr">
-        <is>
-          <t>🤠 Ebenezer’s Barn &amp; Grill: Food Runner งานดินเนอร์โชว์คาวบอย 18:00-22:00 น. (ได้ส่วนแบ่งทิป)</t>
-        </is>
-      </c>
-      <c r="N35" s="7" t="inlineStr">
-        <is>
-          <t>🛒 Ruby’s General Store &amp; Diner: แคชเชียร์/ผู้ช่วยครัว 17:00-21:30 น. ($15/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Utah (UT)</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Park City Mountain Resort (Vail Resorts - Park City)</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>OEG, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Mountain Host / Housekeeping / F&amp;B</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>ฐาน $17.50 / OT $26.25</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>สกีรีสอร์ตและเมืองภูเขาที่ใหญ่ที่สุดในสหรัฐฯ, ระบบรถเมล์ฟรีทั้งเมือง Park City Transit</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>🥩 High West Distillery &amp; Saloon (Main Street): Barback/Busser โรงกลั่นวิสกี้ดัง 17:30-23:30 น. (ทิปสด $80-$140/คืน)</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>🍕 Red Banjo Pizza (Historic Main St): ล้างจาน/ผู้ช่วยครัว 18:00-23:00 น. ($16/ชม. + ทิป)</t>
-        </is>
-      </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>🛒 Freshies Lobster Co. / Local Cafes: Food Runner 17:00-21:30 น. ($15/ชม. + ทิป)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Maryland (MD)</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Premier Aquatics / High Sierra Pools (Bethesda/Rockville)</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Acadex, New Step, ALC, IEO</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>Pool Lifeguard</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 10:30 – 19:30 (9 ชม.)
-พีค: 10:00 – 20:30 (10.5 ชม. สระเปิดยาว)</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>50 – 54 ชม./wk (การันตี OT)</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>$120</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>การันตีชั่วโมง OT แน่นอนสัปดาห์ละ 10-14 ชม., อพาร์ตเมนต์แชร์กับเพื่อน, รถไฟใต้ดิน Metro เข้า DC</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="inlineStr">
-        <is>
-          <t>🛒 Giant Food / Safeway: พนักงานจัดสต็อกสินค้ากะดึก 20:30-01:00 น. ($16-$17.50/ชม. มีสาขาใกล้ที่พัก)</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="inlineStr">
-        <is>
-          <t>🍜 Thai Tanic / Ruan Thai: ผู้ช่วยครัว/แพ็กอาหาร 20:00-23:30 น. (มีอาหารไทยฟรี)</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="inlineStr">
-        <is>
-          <t>🎯 Target / CVS Pharmacy: แคชเชียร์/ปิดร้าน 20:00-23:30 น. ($16.00/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Maryland (MD)</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Ocean City Boardwalk Hotels &amp; Resorts</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>IEE, New Step, OEG, IEO</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Housekeeping / Ride Operator</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>$125</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>เมืองตากอากาศชายหาด Atlantic, รถบัส Coastal Highway วิ่ง 24 ชม., หางานสองง่ายมาก</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>🌴 Seacrets Jamaica USA (ผับริมหาดยักษ์ใหญ่): Barback/Busser 18:00-01:30 น. ($12/ชม. + ทิปสดมหาศาล $80-$150/คืน)</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>🍟 Thrasher’s French Fries (ริมหาด): แคชเชียร์/ทอดเฟรนช์ฟรายส์ 18:00-23:00 น. ($15/ชม.)</t>
-        </is>
-      </c>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>🍺 Shenanigans Irish Pub: ล้างจาน/ผู้ช่วยบาร์ 18:30-00:30 น. ($14/ชม. + ทิป)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Maryland (MD)</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Jolly Roger Amusement Park &amp; Splash Mountain (Ocean City)</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>New Step, IEE, IEO</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Ride Operator / Lifeguard / Park Services</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 11:00 – 19:00 (8 ชม.)
-พีค: 10:00 – 23:00 (12 ชม.)</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>45 – 52 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>$120</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>สวนสนุกและสวนน้ำที่ใหญ่ที่สุดใน Ocean City, เล่นสวนสนุกฟรี, มีรถเมล์ผ่านหน้าสวนสนุก</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>🦀 Higgins Crab House: Busser ร้านปูยักษ์ 19:30-00:30 น. ($13/ชม. + ทิปสด $60-$90/คืน)</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>🍕 Dough Roller Pizza (Boardwalk): ล้างจาน/ทำพิซซ่ากะดึก 19:30-01:00 น. ($15/ชม.)</t>
-        </is>
-      </c>
-      <c r="N39" s="7" t="inlineStr">
-        <is>
-          <t>🍦 Dumser’s Dairyland: ตักไอศกรีม/แคชเชียร์ 19:00-23:30 น. ($15/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Ohio (OH)</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Cedar Point Amusement Park &amp; Resorts (Sandusky)</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>OEG, IEE Thailand, IEO</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Ride Operator / Food Service</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
-พีค: 09:30 – 22:30 (12 ชม. สวนสนุกปิดดึก)</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>ฐาน $14.50 / OT $21.75</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>46 – 52 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>$80 (ถูกสุด)</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>สวนสนุกเครื่องเล่นระดับโลก, หอพักราคาถูกที่สุดในอเมริกา ($80/wk), รถบัสรับส่งฟรี, เล่นสวนสนุกฟรี</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>🏨 Hotel Breakers / Castaway Bay (ในสวนสนุก): ล้างจาน/แม่บ้านกะค่ำ 19:00-00:00 น. (ขอ OT ในสวนสนุก $21.75/ชม.)</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>🍖 Famous Dave’s BBQ (Cedar Point Marina): Busser/Dishwasher 18:30-23:30 น. ($13/ชม. + ทิปสด)</t>
-        </is>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>🐴 Thirsty Pony / Kalahari Sandusky: Barback/Busser ร้านอาหารใกล้เคียง 19:00-00:30 น.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Ohio (OH)</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Kings Island Amusement Park (Mason / Cincinnati)</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>OEG, IEE Thailand, IEO</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>Ride Operator / Park Services / Culinary</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
-พีค: 09:30 – 22:30 (12 ชม.)</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $14.50 / OT $21.75</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>$90</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>สวนสนุกชั้นนำเครือ Cedar Fair ใกล้เมือง Cincinnati, หอพักพนักงาน + รถรับส่งฟรี</t>
-        </is>
-      </c>
-      <c r="L41" s="7" t="inlineStr">
-        <is>
-          <t>🍕 Mason Local Pizzerias &amp; Diners: ล้างจาน/ผู้ช่วยครัวรอบดึก 19:00-00:00 น. ($14.50/ชม.)</t>
-        </is>
-      </c>
-      <c r="M41" s="7" t="inlineStr">
-        <is>
-          <t>🍦 Greaters Ice Cream: พนักงานตักไอศกรีมชื่อดัง 19:00-23:00 น. ($14.50/ชม.)</t>
-        </is>
-      </c>
-      <c r="N41" s="7" t="inlineStr">
-        <is>
-          <t>🏨 Great Wolf Lodge Mason (ข้างๆ สวนสนุก): แม่บ้าน/ผู้ช่วยครัวกะค่ำ (ขอทำเพิ่มได้)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Colorado (CO)</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>YMCA of the Rockies (Estes Park Center)</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Higher, IEE, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Housekeeping / Food Service</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
-พีค: 07:00 – 16:30 (9 ชม.)</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>$110 (รวมกิน)</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="K57" s="7" t="inlineStr">
         <is>
           <t>แคมป์รีสอร์ตกลางเทือกเขา Rocky Mountain NP, หอพัก+อาหารบุฟเฟต์ 3 มื้อ, รถชัตเติลบัสเข้าเมืองฟรี</t>
         </is>
       </c>
-      <c r="L42" s="4" t="inlineStr">
+      <c r="L57" s="7" t="inlineStr">
         <is>
           <t>🏨 The Stanley Hotel (โรงแรมประวัติศาสตร์ The Shining): Busser/Steward ร้านอาหารหรู 17:30-23:00 น. (ทิปสด $50-$90)</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="M57" s="7" t="inlineStr">
         <is>
           <t>🍔 Penelope’s Old Time Burgers: ผู้ช่วยครัว/ทอดเบอร์เกอร์ 17:00-21:30 น. ($15/ชม. + กินฟรี)</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N57" s="7" t="inlineStr">
         <is>
           <t>🍺 Estes Park Brewery / Rock Cut Brewing: ล้างแก้ว/ผู้ช่วยบาร์ 18:00-22:30 น. ($15/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>South Carolina (SC)</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Myrtle Beach Oceanfront Resorts &amp; Boardwalk</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>OEG, IEE, New Step, IEO</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>Housekeeping / Lifeguard / Attractions</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $14.50 / OT $21.75</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>$15 - $30</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>$115</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>เมืองตากอากาศชายหาดยอดนิยมอันดับ 1 ฝั่งใต้, ชายหาดยาว 60 ไมล์, เมืองเดินเท้า/จักรยาน</t>
-        </is>
-      </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>🦀 Sea Captain’s House (ร้านซีฟู้ดระดับตำนาน): Busser 17:30-23:00 น. (ทิปสด $70-$120/คืน)</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="inlineStr">
-        <is>
-          <t>🍕 Broadway at the Beach Eateries: Barback/Runner ศูนย์การค้าเปิดโล่ง 18:30-00:30 น. (ทิปแน่น)</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="inlineStr">
-        <is>
-          <t>🍦 Peaches Corner / Mad Myrtle’s Ice Cream: แคชเชียร์ริมหาด 18:00-23:30 น.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>North Carolina (NC)</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Outer Banks Coastal Resorts (Nags Head / Kill Devil Hills)</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>IEE, New Step, Acadex</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Housekeeping / Beach Operations / F&amp;B</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>$20 - $40</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>$125</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>หมู่เกาะตากอากาศ Outer Banks ทะเลสวย สงบ คนรวยมาพักผ่อน, บ้านพักแชร์ J-1 ริมทะเล</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>🦞 Owens’ Restaurant (ร้านซีฟู้ดประวัติศาสตร์): Busser 17:30-23:00 น. (ทิปสด $60-$110/คืน)</t>
-        </is>
-      </c>
-      <c r="M44" s="4" t="inlineStr">
-        <is>
-          <t>🍺 Outer Banks Brewing Station: Barback ร้านคราฟต์เบียร์กังหันลม 18:00-00:30 น.</t>
-        </is>
-      </c>
-      <c r="N44" s="4" t="inlineStr">
-        <is>
-          <t>🍕 Duck Donuts / Kill Devil Grill: ผู้ช่วยครัว/ทอดโดนัทกะเย็น ($15/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Texas (TX)</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Schlitterbahn Waterpark (New Braunfels / Galveston)</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>OEG, Acadex, IEE, IEO</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>Lifeguard / Park Operations</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 19:30 (10 ชม.)</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>$110</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
-          <t>สวนน้ำระดับตำนานของเท็กซัส, ปลอดภาษีเงินได้รัฐ 0%, เล่นสวนน้ำฟรี</t>
-        </is>
-      </c>
-      <c r="L45" s="7" t="inlineStr">
-        <is>
-          <t>🥩 Gristmill River Restaurant (Gruene): Busser ร้านอาหารริมแม่น้ำสุดคึกคัก 18:30-23:30 น. ($12/ชม. + ทิปสด $60-$100)</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>🦫 Buc-ee’s New Braunfels (ใหญ่ที่สุดในโลก): แคชเชียร์/Food Prep กะดึก 19:00-00:00 น. ($17-$19/ชม. จ่ายหนักมาก)</t>
-        </is>
-      </c>
-      <c r="N45" s="7" t="inlineStr">
-        <is>
-          <t>🍺 Krause’s Cafe &amp; Biergarten: Barback/Runner ร้านเบียร์เยอรมัน 18:00-23:00 น. ($13/ชม. + ทิป)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Texas (TX)</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>Kalahari Resorts &amp; Conventions Round Rock (Austin, TX)</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>OEG, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>Lifeguard / Housekeeping / F&amp;B</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 19:30 (10 ชม.)</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J46" s="8" t="inlineStr">
-        <is>
-          <t>$120</t>
-        </is>
-      </c>
-      <c r="K46" s="10" t="inlineStr">
-        <is>
-          <t>สวนน้ำในร่มใหญ่ที่สุดในอเมริกา สาขาเท็กซัส, ปลอดภาษีรัฐ 0%, ใกล้ออสติน</t>
-        </is>
-      </c>
-      <c r="L46" s="10" t="inlineStr">
-        <is>
-          <t>🥩 Double Cut Steak House (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. ($13/ชม. + ทิปสด $70-$120)</t>
-        </is>
-      </c>
-      <c r="M46" s="10" t="inlineStr">
-        <is>
-          <t>🍕 Tom Foolerys Adventure Park (ในรีสอร์ต): คุมเครื่องเล่น/เกมรอบค่ำ 18:00-23:00 น. (ขอ OT $23.25)</t>
-        </is>
-      </c>
-      <c r="N46" s="10" t="inlineStr">
-        <is>
-          <t>🍔 Round Rock Local Eateries: Busser/ล้างจานร้านอาหารรอบนอก 18:30-23:30 น.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Texas (TX)</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Six Flags Fiesta Texas &amp; SeaWorld San Antonio</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>New Step, Higher, IEE, IEO</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>Ride Operator / Lifeguard / Culinary</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
-พีค: 09:30 – 21:30 (11.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $14.50 / OT $21.75</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>$115</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>สวนสนุกและสวนน้ำระดับโลก ซานอันโตนิโอ, ปลอดภาษีรัฐ 0%, หอพักพนักงาน</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>🥩 The County Line BBQ (River Walk): Busser ร้านบาร์บีคิวริมแม่น้ำ 19:00-00:00 น. (ทิปสด $60-$100/คืน)</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>🎸 Hard Rock Cafe San Antonio: Food Runner/Busser 19:00-00:30 น. ($13/ชม. + ทิป)</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="inlineStr">
-        <is>
-          <t>🌮 Boudro’s on the Riverwalk: ล้างจาน/ผู้ช่วยครัว 19:00-01:00 น. ($15/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Texas (TX)</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>Kemah Boardwalk &amp; Galveston Pleasure Pier</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>OEG, New Step, IEO</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>Ride Operator / Retail / F&amp;B</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 10:30 – 18:30 (8 ชม.)
-พีค: 10:00 – 22:30 (12 ชม.)</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $14.50 / OT $21.75</t>
-        </is>
-      </c>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>$15 - $30</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J48" s="8" t="inlineStr">
-        <is>
-          <t>$110</t>
-        </is>
-      </c>
-      <c r="K48" s="10" t="inlineStr">
-        <is>
-          <t>สวนสนุกริมอ่าวเม็กซิโก เครือ Landry’s, ปลอดภาษีรัฐ 0%, บรรยากาศชายทะเล</t>
-        </is>
-      </c>
-      <c r="L48" s="10" t="inlineStr">
-        <is>
-          <t>🦞 Aquarium Restaurant Kemah (ในเครือ): Busser ร้านอาหารใต้น้ำ 18:30-23:30 น. (ทิปสด $60-$100/คืน)</t>
-        </is>
-      </c>
-      <c r="M48" s="10" t="inlineStr">
-        <is>
-          <t>🍤 Bubba Gump Shrimp Co. (Galveston Pier): Food Runner/Busser 18:30-00:00 น. (ทิปดี)</t>
-        </is>
-      </c>
-      <c r="N48" s="10" t="inlineStr">
-        <is>
-          <t>🏖️ The Spot (Galveston Seawall): Barback/Busser ร้านอาหารริมหาดคนแน่น 19:00-01:00 น.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Florida (FL)</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Universal Orlando Resort &amp; Volcano Bay</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>OEG, IEE, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>Attractions Attendant / Culinary / Lifeguard</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 22:00 (12 ชม.)</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>$130</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="inlineStr">
-        <is>
-          <t>สวนสนุกระดับโลก ยูนิเวอร์แซล ออร์แลนโด, ปลอดภาษีเงินได้รัฐ 0%, บัตรเข้าสวนสนุกฟรี</t>
-        </is>
-      </c>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>🎸 Universal CityWalk Eateries: Food Runner/Busser บาร์ดึก 18:30-01:00 น. (ทิปสด $60-$100/คืน)</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="inlineStr">
-        <is>
-          <t>🍔 The Cowfish Sushi Burger Bar: ล้างจาน/ผู้ช่วยครัว 19:00-01:00 น. ($15/ชม. + ทิป)</t>
-        </is>
-      </c>
-      <c r="N49" s="7" t="inlineStr">
-        <is>
-          <t>🍕 Red Oven Pizza Bakery: ผู้ช่วยทำพิซซ่ากะดึก 18:30-00:30 น.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Florida (FL)</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>Busch Gardens Tampa Bay &amp; Adventure Island</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>New Step, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>Ride Operator / Lifeguard / Food Service</t>
-        </is>
-      </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 21:30 (11.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J50" s="8" t="inlineStr">
-        <is>
-          <t>$120</t>
-        </is>
-      </c>
-      <c r="K50" s="10" t="inlineStr">
-        <is>
-          <t>สวนสนุกโรลเลอร์โคสเตอร์อันดับ 1 ในแทมปาและสวนน้ำ, ปลอดภาษีรัฐ 0%</t>
-        </is>
-      </c>
-      <c r="L50" s="10" t="inlineStr">
-        <is>
-          <t>🍺 Ybor City Historic Bars (แทมปา): Barback ผับประวัติศาสตร์ 19:00-01:30 น. (ทิปสด $60-$110/คืน)</t>
-        </is>
-      </c>
-      <c r="M50" s="10" t="inlineStr">
-        <is>
-          <t>🦀 Columbia Restaurant (ร้านสเปนชื่อดังที่สุด): Busser 18:30-23:30 น. (ทิปดี)</t>
-        </is>
-      </c>
-      <c r="N50" s="10" t="inlineStr">
-        <is>
-          <t>🍔 Portillo’s Hot Dogs Tampa: ครัว/แคชเชียร์รอบดึก 18:30-00:00 น. ($15/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Florida (FL)</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Gaylord Palms Resort &amp; Convention Center (Kissimmee)</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>OEG, Acadex, Higher</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>Housekeeping / Banquet Server / Steward</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>$20 - $50</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>$125</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>รีสอร์ตศูนย์ประชุมโดมกระจกยักษ์ระดับ 4 ดาว Marriott, ปลอดภาษีรัฐ 0%</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>🥩 Old Hickory Steakhouse (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. (ทิปสด $70-$120)</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>🌴 Wreckers Sports Bar (ในรีสอร์ต): Barback ผับกีฬาจอ 2 ชั้น 18:30-00:30 น. (ขอ OT ในรีสอร์ต $24/ชม.)</t>
-        </is>
-      </c>
-      <c r="N51" s="7" t="inlineStr">
-        <is>
-          <t>🛍️ Disney Springs Eateries: Food Runner ร้านอาหารฝั่งดิสนีย์ 19:00-01:00 น.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>New Jersey (NJ)</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>Morey’s Piers &amp; Beachfront Waterparks (Wildwood, NJ)</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>OEG, IEE, New Step, IEO</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>Ride Operator / Lifeguard / Pier Services</t>
-        </is>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 11:00 – 19:00 (8 ชม.)
-พีค: 10:30 – 23:30 (12 ชม.)</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>45 – 52 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J52" s="8" t="inlineStr">
-        <is>
-          <t>$120</t>
-        </is>
-      </c>
-      <c r="K52" s="10" t="inlineStr">
-        <is>
-          <t>สวนสนุกริมสะพานปลาชานหาดที่ใหญ่ที่สุดในฝั่ง East Coast, เล่นเครื่องเล่นฟรี, เมืองจักรยาน</t>
-        </is>
-      </c>
-      <c r="L52" s="10" t="inlineStr">
-        <is>
-          <t>🍕 Mack’s Pizza / Sam’s Pizza (Boardwalk): ล้างจาน/ทำพิซซ่ากะดึก 19:30-01:30 น. ($15/ชม.)</t>
-        </is>
-      </c>
-      <c r="M52" s="10" t="inlineStr">
-        <is>
-          <t>🍺 The Wharf Restaurant &amp; Bar: Barback/Busser ร้านอาหารริมน้ำ 19:00-01:00 น. (ทิปสด $70-$120/คืน)</t>
-        </is>
-      </c>
-      <c r="N52" s="10" t="inlineStr">
-        <is>
-          <t>🍦 Curley’s Fries / Kohr Brothers: แคชเชียร์/ตักไอศกรีม 19:00-23:30 น. ($15.50/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>South Dakota (SD)</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Xanterra Mount Rushmore / Keystone Lodges</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>OEG, IEE, Higher, IEO</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>Retail / Food Service / Housekeeping</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>$105</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>ทำงานหน้าอนุสรณ์สถานแห่งชาติ Mount Rushmore, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>🍔 Carver’s Cafe at Mt Rushmore: ล้างจาน/ปิดครัว 17:00-21:30 น. (ขอ OT ในอุทยาน $23.25/ชม.)</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="inlineStr">
-        <is>
-          <t>🥩 Ruby House Restaurant (Keystone): Busser ร้านอาหารธีมคาวบอยย้อนยุค 17:30-22:30 น. ($13/ชม. + ทิป)</t>
-        </is>
-      </c>
-      <c r="N53" s="7" t="inlineStr">
-        <is>
-          <t>🚂 1880 Train / Keystone Gift Shops: พนักงานร้านของฝาก/สถานีรถไฟโบราณ 17:00-21:30 น. ($15/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>South Dakota (SD)</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>Custer State Park Resorts (State Game Lodge / Sylvan)</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>Higher, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>Guest Service / Housekeeping</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
-พีค: 07:00 – 16:30 (9 ชม.)</t>
-        </is>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J54" s="8" t="inlineStr">
-        <is>
-          <t>$105 (รวมกิน)</t>
-        </is>
-      </c>
-      <c r="K54" s="10" t="inlineStr">
-        <is>
-          <t>อุทยานธรรมชาติฝูงควายไบซัน Custer SP, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
-        </is>
-      </c>
-      <c r="L54" s="10" t="inlineStr">
-        <is>
-          <t>🥩 State Game Lodge Dining Room: Busser ร้านสเต๊กควายไบซันหรู 17:00-22:00 น. ($13/ชม. + ทิปสด $50-$80)</t>
-        </is>
-      </c>
-      <c r="M54" s="10" t="inlineStr">
-        <is>
-          <t>🍔 Black Hills Burger &amp; Bun (เมือง Custer): ล้างจาน/ครัว 17:00-21:30 น. ($15/ชม. + กินฟรี)</t>
-        </is>
-      </c>
-      <c r="N54" s="10" t="inlineStr">
-        <is>
-          <t>🏕️ Sylvan Lake General Store: พนักงานมินิมาร์ท/เช่าเรือแคนู 16:30-21:00 น.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>South Dakota (SD)</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Wall Drug Store (Wall, SD)</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>IEE, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Retail / Restaurant Staff / Fast Food</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>45 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>$85 (ถูกมาก)</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>ห้างคาวบอยระดับตำนานของอเมริกา จุดแวะพักยอดฮิตก่อนเข้า Badlands NP, หอพักราคาถูก</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>☕ Wall Drug Western Art Dining Room: Busser/Steward 17:00-22:00 น. (ขอ OT ในตัว $23.25)</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="inlineStr">
-        <is>
-          <t>🍩 Wall Drug Famous Donut Kitchen: ช่วยทำโดนัท/เบเกอรี่รอบเย็น 16:30-21:00 น.</t>
-        </is>
-      </c>
-      <c r="N55" s="7" t="inlineStr">
-        <is>
-          <t>🌵 Badlands Saloon &amp; Grille: Barback/ล้างจาน 18:00-23:00 น. ($14.50/ชม. + ทิป)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>South Dakota (SD)</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>Deadwood Historic Hotels &amp; Casinos (The Lodge at Deadwood)</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>Higher, New Step, IEO</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>Housekeeping / Food &amp; Beverage</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G56" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H56" s="8" t="inlineStr">
-        <is>
-          <t>$20 - $50</t>
-        </is>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J56" s="8" t="inlineStr">
-        <is>
-          <t>$100</t>
-        </is>
-      </c>
-      <c r="K56" s="10" t="inlineStr">
-        <is>
-          <t>เมืองคาวบอยคาสิโนประวัติศาสตร์ ปลอดภาษีรัฐ 0%, มีรถราง Deadwood Trolley $1</t>
-        </is>
-      </c>
-      <c r="L56" s="10" t="inlineStr">
-        <is>
-          <t>🥩 Deadwood Grille / O’Shea’s: Busser/Runner 17:30-23:00 น. ($13/ชม. + ทิปสด $50-$90/คืน)</t>
-        </is>
-      </c>
-      <c r="M56" s="10" t="inlineStr">
-        <is>
-          <t>🎰 Mineral Palace / Silverado Casino: Barback บาร์ในคาสิโน 18:30-01:00 น. (ทิปดี)</t>
-        </is>
-      </c>
-      <c r="N56" s="10" t="inlineStr">
-        <is>
-          <t>🍕 Mustang Sally’s Sports Bar: ผู้ช่วยครัว/ล้างจาน 18:00-00:00 น. ($14.50/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Virginia (VA)</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Busch Gardens Williamsburg &amp; Water Country USA</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>New Step, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>Ride Operator / Culinary Operations</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึก)</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $14.50 / OT $21.75</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>$115</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>สวนสนุกธีมยุโรปชื่อดัง, บัตรเข้าสวนสนุกและสวนน้ำฟรี, หอพักพนักงาน Williamsburg</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>🏰 Kingsmill Resort (ริมแม่น้ำ James River): Banquet Server/Busser งานจัดเลี้ยง 18:30-23:00 น. (ทิปสด $50-$90/คืน)</t>
-        </is>
-      </c>
-      <c r="M57" s="7" t="inlineStr">
-        <is>
-          <t>🦀 Captain George’s Seafood Buffet: Busser/Dishwasher บุฟเฟต์ซีฟู้ดยักษ์ใหญ่ 18:30-23:30 น. (คนแน่นมาก ทิปดี)</t>
-        </is>
-      </c>
-      <c r="N57" s="7" t="inlineStr">
-        <is>
-          <t>🥞 Cracker Barrel / Pancake House: ผู้ช่วยครัว/ล้างจานรอบค่ำ 18:00-22:00 น. ($14.50/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Virginia (VA)</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>Virginia Beach Oceanfront Resorts &amp; Boardwalk</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>IEE, New Step, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>Housekeeping / Beach Attendant</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
-        </is>
-      </c>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>$15 - $30</t>
-        </is>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J58" s="8" t="inlineStr">
-        <is>
-          <t>$130</t>
-        </is>
-      </c>
-      <c r="K58" s="10" t="inlineStr">
-        <is>
-          <t>เมืองตากอากาศชายทะเลเวอร์จิเนีย มีทางเดินเลียบหาดยาว 3 ไมล์, รถราง Wave Trolley สะดวก</t>
-        </is>
-      </c>
-      <c r="L58" s="10" t="inlineStr">
-        <is>
-          <t>🍺 Waterman’s Surfside Grille: Barback/Busser ร้านริมหาดคนแน่น 18:00-00:30 น. (ทิปสด $70-$120/คืน)</t>
-        </is>
-      </c>
-      <c r="M58" s="10" t="inlineStr">
-        <is>
-          <t>🦀 Catch 31 Fish Bar: Food Runner/Busser 18:00-23:30 น. (ทิปดี)</t>
-        </is>
-      </c>
-      <c r="N58" s="10" t="inlineStr">
-        <is>
-          <t>🍕 Dough Boy’s California Pizza: ผู้ช่วยครัว/ล้างจาน 18:30-00:00 น. ($14.50/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Massachusetts (MA)</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Cape Cod Oceanfront Resorts &amp; Inns (Hyannis / Yarmouth)</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>OEG, IEE, Acadex, Higher</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>Housekeeping / Banquet / F&amp;B</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $16.50 / OT $24.75</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>$20 - $50</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>$135</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>แหลมตากอากาศระดับตำนานของตระกูลเคนเนดี้ Cape Cod, ปั่นจักรยานเลียบหาดสะดวก</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>🦞 The Lobster Pot (Provincetown): Busser/Steward ร้านซีฟู้ดดัง 17:30-23:30 น. (ทิปสด $70-$130/คืน)</t>
-        </is>
-      </c>
-      <c r="M59" s="7" t="inlineStr">
-        <is>
-          <t>🍔 The Black Cat Tavern (Hyannis Harbor): Food Runner/Busser 18:00-00:00 น. (ทิปดี)</t>
-        </is>
-      </c>
-      <c r="N59" s="7" t="inlineStr">
-        <is>
-          <t>🍦 Four Seas Ice Cream: ตักไอศกรีมกะค่ำ 18:00-22:30 น. ($16.00/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>New Hampshire (NH)</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>Omni Mount Washington Resort (Bretton Woods)</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>OEG, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>Housekeeping / Culinary / Steward</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
-        </is>
-      </c>
-      <c r="H60" s="8" t="inlineStr">
-        <is>
-          <t>$15 - $35</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J60" s="8" t="inlineStr">
-        <is>
-          <t>$110 (รวมกิน)</t>
-        </is>
-      </c>
-      <c r="K60" s="10" t="inlineStr">
-        <is>
-          <t>โรงแรมปราสาทประวัติศาสตร์ระดับ 4 ดาวหน้าเทือกเขา White Mountains, ปลอดภาษีซื้อ 0% Sales Tax</t>
-        </is>
-      </c>
-      <c r="L60" s="10" t="inlineStr">
-        <is>
-          <t>🥩 Main Dining Room (ในโรงแรม): Busser ร้าน Fine Dining 17:30-23:00 น. (ทิปสด $60-$100/คืน)</t>
-        </is>
-      </c>
-      <c r="M60" s="10" t="inlineStr">
-        <is>
-          <t>🍺 The Cave (ผับใต้ดินในโรงแรม): Barback บาร์ยุค Prohibition 19:00-01:00 น. (ขอ OT ในรีสอร์ต $24)</t>
-        </is>
-      </c>
-      <c r="N60" s="10" t="inlineStr">
-        <is>
-          <t>🍕 Fabyan’s Station Restaurant: ล้างจาน/ผู้ช่วยครัว 17:30-22:30 น. ($15/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Missouri (MO)</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Silver Dollar City Theme Park &amp; Showboat Branson Belle</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>New Step, IEE, IEO</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>Ride Operator / Attractions Host / Culinary</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 21:30 (12 ชม.)</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $14.50 / OT $21.75</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>$95</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>สวนสนุกธีมยุคคาวบอย 1880s และเรือสำราญดินเนอร์โชว์ Branson, ค่าครองชีพถูกมาก</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>🚢 Showboat Branson Belle (เรือสำราญ): Banquet Server/Busser 18:00-22:30 น. (ทิปสด $50-$90/รอบ)</t>
-        </is>
-      </c>
-      <c r="M61" s="7" t="inlineStr">
-        <is>
-          <t>🥩 Guy Fieri’s Branson Kitchen: Food Runner/Busser 18:30-23:30 น. ($13/ชม. + ทิป)</t>
-        </is>
-      </c>
-      <c r="N61" s="7" t="inlineStr">
-        <is>
-          <t>🥞 Billy Gail’s Cafe: ผู้ช่วยเตรียมวัตถุดิบ/ล้างจานรอบบ่าย-เย็น ($14.50/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Pennsylvania (PA)</t>
-        </is>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>Hersheypark &amp; The Hotel Hershey</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>OEG, IEE, New Step</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>Ride Operator / Food Service / Housekeeping</t>
-        </is>
-      </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
-พีค: 09:30 – 22:30 (12 ชม.)</t>
-        </is>
-      </c>
-      <c r="G62" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
-        </is>
-      </c>
-      <c r="H62" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J62" s="8" t="inlineStr">
-        <is>
-          <t>$110</t>
-        </is>
-      </c>
-      <c r="K62" s="10" t="inlineStr">
-        <is>
-          <t>สวนสนุกเมืองช็อกโกแลต Hershey, หอพักพนักงาน Hershey Co-Op + รถรับส่งฟรี, เข้าสวนสนุกฟรี</t>
-        </is>
-      </c>
-      <c r="L62" s="10" t="inlineStr">
-        <is>
-          <t>🍫 The Circular at The Hotel Hershey: Busser ร้านอาหารหรู 17:30-23:00 น. (ทิปสด $60-$110/คืน)</t>
-        </is>
-      </c>
-      <c r="M62" s="10" t="inlineStr">
-        <is>
-          <t>🍺 Troegs Independent Brewing: Barback โรงเบียร์ดังข้างสวนสนุก 18:30-00:00 น. (ทิปดีมาก)</t>
-        </is>
-      </c>
-      <c r="N62" s="10" t="inlineStr">
-        <is>
-          <t>🍕 Hershey Grill / Local Diners: ล้างจาน/ผู้ช่วยครัว 18:00-23:00 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
@@ -6180,104 +5815,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="65" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="79" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="31" customWidth="1" min="15" max="15"/>
-    <col width="35" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="31" customWidth="1" min="16" max="16"/>
+    <col width="35" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>สัปดาห์ (Week)</t>
+          <t>สัปดาห์ (Summer Week)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>สถานการณ์ &amp; รายละเอียดกะงาน</t>
+          <t>ช่วงวันที่ (Summer Timeline)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>สถานการณ์ &amp; รายละเอียดกะงานซัมเมอร์</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>ชม. งานหลัก (ชม.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ชม. งานสอง (ชม.)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>รวม ชม./สัปดาห์</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>รายรับงานหลัก ($)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>รายรับงานสอง ($)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>เงินทิปสด ($)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>รายรับรวมรายสัปดาห์ ($)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>รายรับรวม (บาท)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>หักภาษี Fed 10% ($)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>หักหอพัก/EDR ($)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>หักของใช้ส่วนตัว ($)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>เงินสดสุทธิสัปดาห์นั้น ($)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>เงินสดสะสมคงเหลือ ($)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>เงินสดสะสมคงเหลือ (บาท)</t>
         </is>
@@ -6289,51 +5930,56 @@
           <t>Week 1</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>ปฐมนิเทศ, อบรม, ทำ SSN ที่แฟร์แบงก์ส</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>7 พ.ค. - 14 พ.ค.</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>เดินทางถึง, ปฐมนิเทศ, อบรม, ทำ SSN ที่แฟร์แบงก์ส</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="E2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="F2" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="F2" s="11" t="n">
+      <c r="G2" s="11" t="n">
         <v>512</v>
-      </c>
-      <c r="G2" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="H2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="11" t="n">
         <v>512</v>
       </c>
-      <c r="J2" s="12" t="n">
+      <c r="K2" s="12" t="n">
         <v>16819</v>
       </c>
-      <c r="K2" s="11" t="n">
+      <c r="L2" s="11" t="n">
         <v>51.2</v>
       </c>
-      <c r="L2" s="11" t="n">
+      <c r="M2" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="M2" s="11" t="n">
+      <c r="N2" s="11" t="n">
         <v>25</v>
-      </c>
-      <c r="N2" s="11" t="n">
-        <v>330.8</v>
       </c>
       <c r="O2" s="11" t="n">
         <v>330.8</v>
       </c>
-      <c r="P2" s="12" t="n">
+      <c r="P2" s="11" t="n">
+        <v>330.8</v>
+      </c>
+      <c r="Q2" s="12" t="n">
         <v>10867</v>
       </c>
     </row>
@@ -6343,51 +5989,56 @@
           <t>Week 2</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>เริ่มแม่บ้านจริง, เรือสำราญรอบแรก, สมัครงาน 2</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>15 พ.ค. - 21 พ.ค.</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>เปิดซีซันซัมเมอร์, เรือสำราญรอบแรกเข้า, สมัครงาน 2</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="E3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="F3" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="G3" s="11" t="n">
         <v>608</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="H3" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11" t="n">
         <v>608</v>
       </c>
-      <c r="J3" s="12" t="n">
+      <c r="K3" s="12" t="n">
         <v>19973</v>
       </c>
-      <c r="K3" s="11" t="n">
+      <c r="L3" s="11" t="n">
         <v>60.8</v>
       </c>
-      <c r="L3" s="11" t="n">
+      <c r="M3" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="M3" s="11" t="n">
+      <c r="N3" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="N3" s="11" t="n">
+      <c r="O3" s="11" t="n">
         <v>417.2</v>
       </c>
-      <c r="O3" s="11" t="n">
+      <c r="P3" s="11" t="n">
         <v>748</v>
       </c>
-      <c r="P3" s="12" t="n">
+      <c r="Q3" s="12" t="n">
         <v>24572</v>
       </c>
     </row>
@@ -6397,51 +6048,56 @@
           <t>Week 3</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>รถไฟทัวร์แน่น, งานสองเริ่มทำ 2-3 วัน</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>22 พ.ค. - 28 พ.ค. (Memorial Day)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>วันหยุด Memorial Day เปิดซัมเมอร์เต็มรูปแบบ งานสองเริ่มทำ</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="E4" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="F4" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="G4" s="11" t="n">
         <v>832</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="H4" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="H4" s="11" t="n">
+      <c r="I4" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="I4" s="11" t="n">
+      <c r="J4" s="11" t="n">
         <v>1042</v>
       </c>
-      <c r="J4" s="12" t="n">
+      <c r="K4" s="12" t="n">
         <v>34230</v>
       </c>
-      <c r="K4" s="11" t="n">
+      <c r="L4" s="11" t="n">
         <v>104.2</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="M4" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="N4" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="N4" s="11" t="n">
+      <c r="O4" s="11" t="n">
         <v>807.8</v>
       </c>
-      <c r="O4" s="11" t="n">
+      <c r="P4" s="11" t="n">
         <v>1555.8</v>
       </c>
-      <c r="P4" s="12" t="n">
+      <c r="Q4" s="12" t="n">
         <v>51108</v>
       </c>
     </row>
@@ -6451,51 +6107,56 @@
           <t>Week 4</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>เข้าที่เต็มตัว, งานสอง Barback 4 วัน</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>29 พ.ค. - 4 มิ.ย.</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>รถไฟทัวร์แน่น, เข้าที่เต็มตัว, งานสอง Barback 4 วัน</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="E5" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="G5" s="11" t="n">
         <v>976</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="H5" s="11" t="n">
         <v>210</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="I5" s="11" t="n">
         <v>120</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="J5" s="11" t="n">
         <v>1306</v>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="K5" s="12" t="n">
         <v>42902</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="L5" s="11" t="n">
         <v>130.6</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="M5" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="N5" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="O5" s="11" t="n">
         <v>1045.4</v>
       </c>
-      <c r="O5" s="11" t="n">
+      <c r="P5" s="11" t="n">
         <v>2601.2</v>
       </c>
-      <c r="P5" s="12" t="n">
+      <c r="Q5" s="12" t="n">
         <v>85449</v>
       </c>
     </row>
@@ -6505,52 +6166,57 @@
           <t>Week 5</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>PEAK จัด วันชาติ 4th of July แขกล้น</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>58</v>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>5 มิ.ย. - 11 มิ.ย.</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>ช่วง Midnight Sun สว่าง 24 ชม. แขกแน่นตลอดคืน</t>
+        </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>1072</v>
+        <v>14</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>70</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>225</v>
+        <v>1024</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>1457</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>47862</v>
-      </c>
-      <c r="K6" s="11" t="n">
-        <v>145.7</v>
+        <v>140</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>1374</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <v>45136</v>
       </c>
       <c r="L6" s="11" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="M6" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="N6" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="N6" s="11" t="n">
-        <v>1181.3</v>
-      </c>
       <c r="O6" s="11" t="n">
-        <v>3782.5</v>
-      </c>
-      <c r="P6" s="12" t="n">
-        <v>124255</v>
+        <v>1106.6</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>3707.8</v>
+      </c>
+      <c r="Q6" s="12" t="n">
+        <v>121801</v>
       </c>
     </row>
     <row r="7">
@@ -6559,52 +6225,57 @@
           <t>Week 6</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>PEAK ต่อเนื่อง เรือสำราญเข้าทุกวัน</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>12 มิ.ย. - 18 มิ.ย.</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>PEAK ซัมเมอร์ เรือสำราญและรถไฟเข้าเต็มพิกัด</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="E7" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="G7" s="11" t="n">
         <v>1024</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="H7" s="11" t="n">
         <v>210</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="I7" s="11" t="n">
         <v>140</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="J7" s="11" t="n">
         <v>1374</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="K7" s="12" t="n">
         <v>45136</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="L7" s="11" t="n">
         <v>137.4</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="M7" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="N7" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="O7" s="11" t="n">
         <v>1106.6</v>
       </c>
-      <c r="O7" s="11" t="n">
-        <v>4889.1</v>
-      </c>
-      <c r="P7" s="12" t="n">
-        <v>160607</v>
+      <c r="P7" s="11" t="n">
+        <v>4814.4</v>
+      </c>
+      <c r="Q7" s="12" t="n">
+        <v>158153</v>
       </c>
     </row>
     <row r="8">
@@ -6613,52 +6284,57 @@
           <t>Week 7</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>ฝนตกหนัก/รถไฟดีเลย์ ร่างกายเริ่มล้า</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>19 มิ.ย. - 25 มิ.ย.</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>ฝนตกในหุบเขา/รถไฟดีเลย์ ร่างกายเริ่มล้า พักผ่อน</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="E8" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="F8" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="G8" s="11" t="n">
         <v>736</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="H8" s="11" t="n">
         <v>180</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="I8" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="J8" s="11" t="n">
         <v>996</v>
       </c>
-      <c r="J8" s="12" t="n">
+      <c r="K8" s="12" t="n">
         <v>32719</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="L8" s="11" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="M8" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="N8" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="N8" s="11" t="n">
+      <c r="O8" s="11" t="n">
         <v>766.4</v>
       </c>
-      <c r="O8" s="11" t="n">
-        <v>5655.5</v>
-      </c>
-      <c r="P8" s="12" t="n">
-        <v>185783</v>
+      <c r="P8" s="11" t="n">
+        <v>5580.8</v>
+      </c>
+      <c r="Q8" s="12" t="n">
+        <v>183330</v>
       </c>
     </row>
     <row r="9">
@@ -6667,52 +6343,57 @@
           <t>Week 8</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>ฟื้นตัวกลับมาพีค ทัวร์ครอบครัวแน่น</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>55</v>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>26 มิ.ย. - 4 ก.ค. (4th of July PEAK)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>วันชาติอเมริกา PEAK ที่สุดในรอบปี แขกล้น ทิปมหาศาล</t>
+        </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>1000</v>
+        <v>15</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>73</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>210</v>
+        <v>1072</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>44348</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>135</v>
+        <v>160</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>1457</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>47862</v>
       </c>
       <c r="L9" s="11" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="M9" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="N9" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="N9" s="11" t="n">
-        <v>1085</v>
-      </c>
       <c r="O9" s="11" t="n">
-        <v>6740.5</v>
-      </c>
-      <c r="P9" s="12" t="n">
-        <v>221425</v>
+        <v>1181.3</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>6762.1</v>
+      </c>
+      <c r="Q9" s="12" t="n">
+        <v>222135</v>
       </c>
     </row>
     <row r="10">
@@ -6721,52 +6402,57 @@
           <t>Week 9</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>ช่วงท้ายพีคซีซัน ชั่วโมงยังแน่น</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>5 ก.ค. - 15 ก.ค.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>ช่วงพีคต่อเนื่อง นักท่องเที่ยวครอบครัวสหรัฐฯ แน่น</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="E10" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="G10" s="11" t="n">
         <v>928</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="H10" s="11" t="n">
         <v>180</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="I10" s="11" t="n">
         <v>120</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="J10" s="11" t="n">
         <v>1228</v>
       </c>
-      <c r="J10" s="12" t="n">
+      <c r="K10" s="12" t="n">
         <v>40340</v>
       </c>
-      <c r="K10" s="11" t="n">
+      <c r="L10" s="11" t="n">
         <v>122.8</v>
       </c>
-      <c r="L10" s="11" t="n">
+      <c r="M10" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="M10" s="11" t="n">
+      <c r="N10" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="N10" s="11" t="n">
+      <c r="O10" s="11" t="n">
         <v>975.2</v>
       </c>
-      <c r="O10" s="11" t="n">
-        <v>7715.7</v>
-      </c>
-      <c r="P10" s="12" t="n">
-        <v>253461</v>
+      <c r="P10" s="11" t="n">
+        <v>7737.3</v>
+      </c>
+      <c r="Q10" s="12" t="n">
+        <v>254171</v>
       </c>
     </row>
     <row r="11">
@@ -6775,52 +6461,57 @@
           <t>Week 10</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>อากาศเย็นลง นักศึกษาฝรั่งเริ่มกลับ</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>16 ก.ค. - 31 ก.ค.</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>เข้าสู่ปลายซัมเมอร์ นักศึกษาฝรั่งเริ่มทยอยกลับ</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="E11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="G11" s="11" t="n">
         <v>832</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="H11" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="I11" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="J11" s="11" t="n">
         <v>1082</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>35544</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="L11" s="11" t="n">
         <v>108.2</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="M11" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="M11" s="11" t="n">
+      <c r="N11" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="N11" s="11" t="n">
+      <c r="O11" s="11" t="n">
         <v>843.8</v>
       </c>
-      <c r="O11" s="11" t="n">
-        <v>8559.5</v>
-      </c>
-      <c r="P11" s="12" t="n">
-        <v>281180</v>
+      <c r="P11" s="11" t="n">
+        <v>8581.1</v>
+      </c>
+      <c r="Q11" s="12" t="n">
+        <v>281890</v>
       </c>
     </row>
     <row r="12">
@@ -6829,52 +6520,57 @@
           <t>Week 11</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>ทัวร์เริ่มซา ปิดห้องพักบางโซน</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1 ส.ค. - 15 ส.ค.</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>ใบไม้เริ่มเปลี่ยนสี ทัวร์ซา ปิดห้องพักบางโซน</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="E12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>736</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>120</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="I12" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="J12" s="11" t="n">
         <v>916</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>30091</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="L12" s="11" t="n">
         <v>91.59999999999999</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="M12" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="N12" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="N12" s="11" t="n">
+      <c r="O12" s="11" t="n">
         <v>694.4</v>
       </c>
-      <c r="O12" s="11" t="n">
-        <v>9253.9</v>
-      </c>
-      <c r="P12" s="12" t="n">
-        <v>303991</v>
+      <c r="P12" s="11" t="n">
+        <v>9275.5</v>
+      </c>
+      <c r="Q12" s="12" t="n">
+        <v>304701</v>
       </c>
     </row>
     <row r="13">
@@ -6883,52 +6579,57 @@
           <t>Week 12</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>สัปดาห์สุดท้าย เคลียร์ห้องพัก คืนมัดจำ</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>16 ส.ค. - 7 ก.ย. (Wrap Up)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>สัปดาห์สุดท้าย เคลียร์ห้อง ปิดซีซันซัมเมอร์ คืนมัดจำ</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="E13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="G13" s="11" t="n">
         <v>576</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="H13" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="11" t="n">
         <v>576</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>18922</v>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="L13" s="11" t="n">
         <v>57.6</v>
       </c>
-      <c r="L13" s="11" t="n">
+      <c r="M13" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="M13" s="11" t="n">
+      <c r="N13" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="N13" s="11" t="n">
+      <c r="O13" s="11" t="n">
         <v>388.4</v>
       </c>
-      <c r="O13" s="11" t="n">
-        <v>9642.299999999999</v>
-      </c>
-      <c r="P13" s="12" t="n">
-        <v>316750</v>
+      <c r="P13" s="11" t="n">
+        <v>9663.9</v>
+      </c>
+      <c r="Q13" s="12" t="n">
+        <v>317459</v>
       </c>
     </row>
   </sheetData>
@@ -6947,13 +6648,13 @@
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="103" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="105" customWidth="1" min="9" max="9"/>
+    <col width="115" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6969,7 +6670,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ค่าโครงการโดยประมาณ (บาท)</t>
+          <t>ค่าโครงการ Summer โดยประมาณ</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -6979,7 +6680,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>งานเด่นใน Tier S &amp; Tier A</t>
+          <t>งานเด่น Summer ใน Tier S &amp; Tier A</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -6999,7 +6700,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>จุดเด่น &amp; คำแนะนำ</t>
+          <t>จุดเด่น &amp; คำแนะนำสำหรับ Summer</t>
         </is>
       </c>
     </row>
@@ -7046,7 +6747,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>สปอนเซอร์ CIEE มั่นคงที่สุด ระบบติวสัมภาษณ์และดูแลมาตรฐานสูงสุด</t>
+          <t>สปอนเซอร์ CIEE มั่นคงที่สุด ระบบติวสัมภาษณ์และดูแลมาตรฐานสูงสุดช่วง Summer</t>
         </is>
       </c>
     </row>
@@ -7140,7 +6841,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>ค่าโครงการย่อมเยา เครือข่ายสปอนเซอร์ CCUSA แน่นแฟ้นกับงานอุทยานและรีสอร์ต</t>
+          <t>ค่าโครงการย่อมเยา เครือข่ายสปอนเซอร์ CCUSA แน่นแฟ้นกับงานอุทยานและรีสอร์ตช่วง Summer</t>
         </is>
       </c>
     </row>

--- a/Work_and_Travel_Master_Job_Database_2027.xlsx
+++ b/Work_and_Travel_Master_Job_Database_2027.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top Employers (Summer Only)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier S-A Summer Jobs &amp; Options" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summer 12-Wk Simulator (พ.ค-ก.ย)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summer 12-Week Simulator" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summer Agency Directory" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>

--- a/Work_and_Travel_Master_Job_Database_2027.xlsx
+++ b/Work_and_Travel_Master_Job_Database_2027.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top Employers (Summer Only)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier S-A Summer Jobs &amp; Options" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier S-A Summer Jobs" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summer 12-Week Simulator" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summer Agency Directory" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>

--- a/Work_and_Travel_Master_Job_Database_2027.xlsx
+++ b/Work_and_Travel_Master_Job_Database_2027.xlsx
@@ -497,20 +497,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -599,7 +599,7 @@
       <c r="F2" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 07:30 – 15:30 (8 ชม.)
-พีคซัมเมอร์ (มิ.ย.-ส.ค.): 07:00 – 17:30 (10 ชม. ควงกะ)</t>
+พีคซัมเมอร์: 07:00 – 17:30 (10 ชม. ควงกะ)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>50 – 54 ชม./wk (พีคจัด 58-62 ชม. / หัวท้าย พ.ค., ก.ย. 35-42 ชม.)</t>
+          <t>50 – 54 ชม./wk</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
           <t>$105</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR ตักไม่อั้น 7 วัน, ทิปหัวเตียง, รถรับส่งพนักงาน, ส่วนลดทัวร์/รถไฟ 50%</t>
         </is>
@@ -672,7 +672,7 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>50 – 55 ชม./wk (ควงกะ Banquet และรอบรถไฟได้)</t>
+          <t>50 – 55 ชม./wk</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
@@ -680,7 +680,7 @@
           <t>$105</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>อาหารบุฟเฟต์ 3 มื้อใน EDR + เชฟทำสเต๊ก/เบอร์เกอร์เลี้ยงในครัวฟรีทุกกะ</t>
         </is>
@@ -699,23 +699,23 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Denali Princess Wilderness Lodge (Summer Season)</t>
+          <t>Grande Denali Lodge &amp; Denali Bluffs Hotel (Summer Only)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Acadex, OEG, IEE, Higher, IEO</t>
+          <t>Acadex Thailand, IEO</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Luggage Handler (พนักงานยกกระเป๋าทัวร์)</t>
+          <t>Housekeeping / Public Area</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 หรือ 12:00 – 20:30
-พีคซัมเมอร์: 07:00 – 18:30 (ตามรอบรถไฟ)</t>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -725,22 +725,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>$40 - $70</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>46 – 52 ชม./wk (ช่วงรถไฟ Wilderness Express วิ่งเต็มรอบ)</t>
+          <t>42 – 46 ชม./wk</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>$105</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, ทิปเงินสดจากกรุ๊ปทัวร์ผู้สูงอายุ</t>
+          <t>$140</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>โบนัส Summer Bonus +$1.00/ชม. ท้ายทริป, โรงแรมหรู 4 ดาวบนยอดเขา, รถชัตเติลบัส, ส่วนลดอาหาร</t>
         </is>
       </c>
     </row>
@@ -757,48 +757,48 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Denali Princess Wilderness Lodge</t>
+          <t>Seward Windsong Lodge &amp; Kenai Fjords Tours (Pursuit)</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>ขอทำเพิ่มหน้างาน (Internal Summer 2nd Job)</t>
+          <t>OEG, Acadex, ALC, IEO</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Fleet Detailer (งานเสริมล้างรถทัวร์กะดึกซัมเมอร์)</t>
+          <t>Housekeeping / Tour Operations / F&amp;B</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 21:00 – 01:30 (4.5 ชม.)
-พีคซัมเมอร์: 21:00 – 02:30 (5.5 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>คิดเรต OT $24.00/ชม. ทันที</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$20 - $50</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>20 – 25 ชม./wk (ทำควบหลังงานหลักแม่บ้าน)</t>
+          <t>44 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>นับเป็นชั่วโมง OT $24.00 ทั้งหมด, ทำงานในอู่รถบัส Princess, อาหาร EDR 3 มื้อ</t>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายทะเล Seward ท่าเรือล่องเรือชมวาฬและธารน้ำแข็งซัมเมอร์, หอพักพนักงาน, ล่องเรือฟรี</t>
         </is>
       </c>
     </row>
@@ -815,48 +815,48 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Denali Bluffs Hotel (เปิดเฉพาะ Summer)</t>
+          <t>Talkeetna Alaskan Lodge (Pursuit Collection)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Acadex Thailand, IEO</t>
+          <t>OEG, Acadex, Higher, IEO</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Housekeeping / Laundry</t>
+          <t>Housekeeping / Kitchen / Steward</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีคซัมเมอร์: 08:00 – 17:00 (9 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$15 - $30</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>40 – 45 ชม./wk (หัวท้าย 32-38 ชม.)</t>
+          <t>44 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>$140</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>โบนัสพิเศษ Summer Bonus +$1.00/ชม. ท้ายทริป (ครบสัญญา), รถชัตเติลบัส, ส่วนลดอาหาร The Perk</t>
+          <t>$115</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>โรงแรมหรูชมวิวยอดเขา Denali ในเมืองคาวบอย Talkeetna, หอพักพนักงาน + รถรับส่ง</t>
         </is>
       </c>
     </row>
@@ -873,106 +873,106 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Grande Denali Lodge (เปิดเฉพาะ Summer)</t>
+          <t>Alyeska Resort &amp; Hotel Alyeska (Girdwood)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Acadex Thailand, IEO</t>
+          <t>OEG, Higher, Acadex</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Public Area Cleaner</t>
+          <t>Housekeeping / Culinary / Lift Ops</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.50 / OT $24.75</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>$135</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>รีสอร์ตหรูระดับโลก นั่งกระเช้าชมวิวภูเขาและธารน้ำแข็งซัมเมอร์, หอพักพนักงาน Glacier Valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Alaska (AK)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Mt. McKinley Princess Lodge (Trapper Creek)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Higher, OEG, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Kitchen</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
 พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>42 – 46 ชม./wk (หัวท้าย 35-40 ชม.)</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>$140</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>โบนัสพิเศษ Summer Bonus +$1.00/ชม. ท้ายทริป, โรงแรมหรู 4 ดาว, รถชัตเติลบัส</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Grande Denali Lodge (เปิดเฉพาะ Summer)</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Acadex Thailand, IEO</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Busser / Food Runner (Alpenglow Restaurant)</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>ปกติ: 16:30 – 22:30 (6 ชม.)
-พีคซัมเมอร์: 16:00 – 23:30 (7.5 ชม.)</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>ฐาน $14.00 / OT $21.00</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>$200 - $350</t>
+          <t>$10 - $20</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>40 – 45 ชม./wk</t>
+          <t>44 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>$140</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>โบนัส +$1.00/ชม., ทิปเงินสดจากแขกไฮเอนด์ร้านอาหารวิวพาโนรามาช่วง Midnight Sun ($40-$70/คืน)</t>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, รถรับส่ง, ชมวิวยอดเขาเดนาลี บรรยากาศสงบ</t>
         </is>
       </c>
     </row>
@@ -989,512 +989,512 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Mt. McKinley Princess Lodge (Summer Season)</t>
+          <t>Fairbanks Princess Riverside Lodge (Summer Season)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Higher, OEG, Acadex, IEO</t>
+          <t>IEE, Acadex, Higher, IEO</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Kitchen / Laundry</t>
+          <t>Food Runner / Laundry / Steward</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 06:30 – 14:30 หรือ 15:00 – 23:00
+พีคซัมเมอร์: กะสลับตามรอบรถไฟ 8 ชม.</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>$20 - $40</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>36 – 40 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>หอพักในเมืองแฟร์แบงก์ส + รถชัตเติลบัส, ใกล้ Walmart และร้านอาหารไทย หางาน 2 ง่าย</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Wyoming (WY)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Grand Teton Lodge Company - Jackson Lake Lodge (Summer)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Acadex, Higher, OEG, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Crew Member</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:00 – 17:30 (10 ชม. ควงกะ)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $17.75 / OT $26.62</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>54 – 60 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>$0 (ฟรี!)</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), ส่วนลด 40%, บัตรผ่าน 2 อุทยานฟรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Wyoming (WY)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Grand Teton Lodge Company - Colter Bay Village (Summer)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Acadex, Higher, OEG, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Cabin Attendant / Grocery Clerk / Marina</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $17.75 / OT $26.62</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>52 – 58 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>$0 (ฟรี!)</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), หมู่บ้านริมทะเลสาบ Jackson Lake</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Wyoming (WY)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Signal Mountain Lodge (Grand Teton NP - Forever Resorts)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Higher, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Front Desk / Marina</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
 พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>$10 - $20</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>44 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>$105</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, รถรับส่งพนักงาน, ชมวิวยอดเขาเดนาลี บรรยากาศสงบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $16.50 / OT $24.75</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>45 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>$110 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>รีสอร์ตริมทะเลสาบ Signal Mountain, หอพักพนักงาน + อาหาร 3 มื้อ, ส่วนลดเช่าเรือซัมเมอร์</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Alaska (AK)</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Fairbanks Princess Riverside Lodge (Summer Season)</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>IEE, Acadex, Higher, IEO</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Food Runner / Laundry / Steward</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>ปกติ: 06:30 – 14:30 หรือ 15:00 – 23:00
-พีคซัมเมอร์: กะสลับตามรอบรถไฟ 8 ชม.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>$20 - $40</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>36 – 40 ชม./wk (ไม่ค่อยมี OT)</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>$105</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>หอพักในเมืองแฟร์แบงก์ส + รถชัตเติลบัส, ใกล้ Walmart และร้านอาหารไทย หางาน 2 ง่าย</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Wyoming (WY)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Xanterra Yellowstone Lodges (Old Faithful / Canyon)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE Thailand, IEO</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Hospitality Crew / Kitchen Steward</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:00 – 15:30 หรือ 15:00 – 23:30
+พีคซัมเมอร์: 06:30 – 16:30 (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.70 / OT $23.55</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>46 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>$120 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>รวมหอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR, หอพักใหม่ Arnica, เที่ยวบ่อน้ำพุร้อน Yellowstone ฟรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Wyoming (WY)</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Grand Teton Lodge Company - Jackson Lake Lodge (Summer)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Acadex, Higher, OEG, IEE, IEO</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Housekeeping / Crew Member</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีคซัมเมอร์ (มิ.ย.-ส.ค.): 07:00 – 17:30 (10 ชม. ควงกะ)</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $17.75 / OT $26.62</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>54 – 60 ชม./wk (พีคซัมเมอร์ 60-64 ชม. / หัวท้าย 40 ชม.)</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>$0 (ฟรี!)</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), ส่วนลดซื้อของ 40%, เข้าอุทยาน Grand Teton &amp; Yellowstone ฟรี</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Wyoming (WY)</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Grand Teton Lodge Company - Colter Bay Village (Summer)</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Acadex, Higher, OEG, IEE, IEO</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Cabin Attendant / Grocery Clerk / Marina</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Four Seasons Resort &amp; Snake River Lodge (Teton Village)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Stewarding</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
 พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>ฐาน $17.75 / OT $26.62</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $17.50 / OT $26.25</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>52 – 58 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>$0 (ฟรี!)</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>หอพักฟรี 100%! + อาหาร 3 มื้อ EDR, หมู่บ้านริมทะเลสาบ Jackson Lake สวยที่สุดในซัมเมอร์</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>45 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>$140</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>รีสอร์ตหรู 5 ดาวใน Teton Village, หอพักพนักงาน, นั่งรถบัส START Bus ฟรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Wyoming (WY)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Xanterra Yellowstone Lodges (Summer Season)</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>OEG, IEE Thailand, IEO</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Hospitality Crew / Kitchen / Steward</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 07:00 – 15:30 หรือ 15:00 – 23:30
-พีคซัมเมอร์: 06:30 – 16:30 (10 ชม.)</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $15.70 / OT $23.55</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>46 – 52 ชม./wk (หัวท้าย 38-42 ชม.)</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>$120</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>รวมหอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR, หอพักใหม่ Arnica, เที่ยวบ่อน้ำพุร้อน Yellowstone ฟรี</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>The Wort Hotel &amp; Silver Dollar Bar (Jackson Town)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Acadex, OEG, IEO</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Banquet Server / Steward</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $17.00 / OT $25.50</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>$30 - $60</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>โรงแรมประวัติศาสตร์ใจกลางเมือง Jackson, เดินทางสะดวกที่สุด มีร้านค้าล้อมรอบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Wyoming (WY)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Under Canvas Grand Teton / Yellowstone (เปิดเฉพาะ Summer)</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Under Canvas Grand Teton / Yellowstone (Summer Only)</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Higher Education, IEO</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Housekeeping / Guest Service</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:30 – 16:30 (8 ชม.)
 พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>$50 - $100</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>42 – 46 ชม./wk</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>$100</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>แคมป์กระโจมซาฟารีหรูเปิดเฉพาะ พ.ค.-ก.ย., อาหารพนักงาน, ทิปเงินสดจากแขกไฮเอนด์</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Wisconsin (WI)</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Kalahari Resorts &amp; Conventions (Summer Season)</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Kalahari Resorts &amp; Conventions (Wisconsin Dells)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>OEG, Acadex, Higher, IEO, New Step</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Lifeguard / Housekeeping (งานหลักซัมเมอร์)</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Lifeguard / Housekeeping (Summer High Season)</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 09:30 – 18:00 หรือ 12:00 – 20:30
 พีคซัมเมอร์: 09:00 – 19:30 (10 ชม.)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>38 – 44 ชม./wk (เกลี่ยกะ 40 ชม.)</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>38 – 44 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>หอพัก Kalahari Village, บัตรเล่นสวนน้ำฟรี, เมืองปั่นจักรยาน 100%, หางาน 2 ร้านอาหารง่าย</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Wisconsin (WI)</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Wisconsin Dells Riverfront Eateries (Summer High Season)</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Walk-in สมัครเองหน้างาน</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Barback / Busser / Runner (งานที่สองช่วงซัมเมอร์)</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>ปกติ: 17:30 – 22:30 (5 ชม.)
-พีคซัมเมอร์: 17:00 – 00:30 (7.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>ฐาน $12.00 – $14.00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>$250 - $500</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>20 – 25 ชม./wk (กะค่ำ 17:30-23:00)</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>รับทิปเงินสดทุกคืน ยัดกระเป๋ากลับห้องทันที ($50-$100/คืน), อาหารพนักงานในกะ (ทำควบกับงานหลัก)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Tier S</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Tennessee (TN)</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Dollywood Theme Park &amp; Splash Country (Summer Festival)</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>New Step, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Ride Operator / Food Service / Retail</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีคซัมเมอร์: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึกมีพลุทุกคืน)</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk (หัวท้าย 35-40 ชม.)</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>$110</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>ปลอดภาษีเงินได้รัฐ 0%, นั่งรถราง Pigeon Forge Trolley $1/วัน, บัตรเข้าสวนสนุก Dollywood ฟรี</t>
         </is>
       </c>
     </row>
@@ -1506,111 +1506,2547 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>Wisconsin (WI)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Wilderness Resort &amp; Glacier Canyon Lodge (WI Dells)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Waterpark Attendant / Housekeeping</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
+พีคซัมเมอร์: 08:30 – 19:00 (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>40 – 46 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>อาณาจักรรีสอร์ตสวนน้ำที่ใหญ่ที่สุดในอเมริกา (600 เอเคอร์), หอพักพนักงานในรีสอร์ต</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Wisconsin (WI)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Mt. Olympus Water &amp; Theme Park (WI Dells)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>New Step, Acadex, Higher, IEO</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Housekeeping / Lifeguard</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 21:00 (11.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>$95</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกธีมกรีกโบราณ โรลเลอร์โคสเตอร์ไม้, หอพักราคาถูก, ทำเลติดถนนใหญ่ Parkway</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Wisconsin (WI)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Noah’s Ark Waterpark (Wisconsin Dells - Summer Only)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>OEG, IEE, New Step, IEO</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Ride Operator / Park Services</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
+พีคซัมเมอร์: 08:30 – 18:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>40 – 46 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>สวนน้ำกลางแจ้งใหญ่ที่สุดในอเมริกา เปิดเฉพาะซัมเมอร์, เล่นสวนน้ำฟรี, หอพักพนักงานใกล้ที่ทำงาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Wisconsin (WI)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Chula Vista Resort &amp; Waterpark (WI Dells)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Higher, Acadex, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Lifeguard</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>40 – 45 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>รีสอร์ตริมแม่น้ำ Wisconsin River, สวนน้ำในร่ม/กลางแจ้ง, หอพักในรีสอร์ต</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Wisconsin (WI)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Grand Geneva Resort &amp; Spa (Lake Geneva, WI)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Acadex, OEG, IEO</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Banquet / Culinary</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>รีสอร์ตหรูระดับ 4 เพชร AAA เมืองตากอากาศทะเลสาบคนรวยชิคาโกช่วงซัมเมอร์, หอพักพนักงาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Tennessee (TN)</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Dollywood Theme Park &amp; Splash Country (Pigeon Forge)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>New Step, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Food Service / Retail</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึกมีพลุ)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>ปลอดภาษีเงินได้รัฐ 0%, นั่งรถราง Pigeon Forge Trolley $1/วัน, บัตรเข้าสวนสนุก Dollywood ฟรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Tennessee (TN)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>The Island in Pigeon Forge (Arcades &amp; Attractions)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>New Step, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Attractions Host / Retail / F&amp;B</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 10:00 – 23:00 (กะดึก)</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>$20 - $40</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>ศูนย์รวมความบันเทิง ชิงช้าสวรรค์ยักษ์และร้านอาหารกลางเมือง, รถรางผ่านหน้าร้าน</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Tennessee (TN)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Wilderness at the Smokies (Sevierville)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, Higher, IEO</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Lifeguard / Housekeeping</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
+พีคซัมเมอร์: 08:30 – 19:30 (10.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>สวนน้ำในร่มและกลางแจ้งใหญ่ที่สุดในเทนเนสซี, ปลอดภาษีรัฐ 0%, หอพักพนักงาน Sevierville</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Tennessee (TN)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Anakeesta Mountaintop Theme Park (Gatlinburg)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Higher, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Guest Host / F&amp;B / Retail</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
+พีคซัมเมอร์: 08:30 – 20:00 (10.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>สวนสนุกธรรมชาติบนยอดเขา Gatlinburg นั่งกระเช้า Chondola, ปลอดภาษีรัฐ 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Montana (MT)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Glacier National Park Lodges (Pursuit / Xanterra)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, Higher, IEO</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Hospitality Crew / Housekeeping</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>46 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>$115 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>อุทยานธรรมชาติธารน้ำแข็ง Glacier NP เปิดเฉพาะซัมเมอร์, ปลอดภาษีมูลค่าเพิ่ม 0% Sales Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Montana (MT)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Many Glacier Hotel &amp; Glacier Park Lodge (East Glacier)</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Dining Room / Steward</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีคซัมเมอร์: 07:00 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>46 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>$115 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>โรงแรมสไตล์สวิสชาเลต์ริมทะเลสาบ Swiftcurrent Lake สวยที่สุดใน Glacier NP, อาหาร EDR 3 มื้อ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Montana (MT)</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Big Sky Resort / Montage Big Sky</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Acadex, Higher, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Mountain Operations / Housekeeping</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $17.50 / OT $26.25</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>46 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>$140</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>รีสอร์ตภูเขาหรูหราไฮเอนด์, ค่าแรงฐานสูงมาก, มีรถบัส Skyline Bus ฟรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Maine (ME)</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Bar Harbor Grand Hotel / Harborside Hotel</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Acadex, OEG, Higher, IEO</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Laundry</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $16.50 / OT $24.75</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายทะเล Bar Harbor &amp; อุทยาน Acadia NP, รถบัส Island Explorer ฟรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Maine (ME)</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Cliff House Maine (Cape Neddick / Ogunquit)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Higher, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Culinary / Stewarding</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $17.00 / OT $25.50</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>$135</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>รีสอร์ตหรูบนหน้าผาริมมหาสมุทรแอตแลนติก แขกไฮเอนด์ระดับมหาเศรษฐีบอสตันและนิวยอร์ก</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Maine (ME)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>The Nonantum Resort (Kennebunkport, ME)</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Higher, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Banquet / F&amp;B</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $16.50 / OT $24.75</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>$125</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>รีสอร์ตตากอากาศริมน้ำประวัติศาสตร์ เมืองของประธานาธิบดีบุช, หอพักพนักงาน Kennebunkport</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Utah (UT)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Zion National Park Lodge (Xanterra Springdale)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Hospitality Crew / Housekeeping</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีคซัมเมอร์: 07:00 – 16:30 (9 ชม.)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>อุทยานแห่งชาติหุบเขาผาแดง Zion NP, มีรถชัตเติลบัสฟรีวิ่งตลอดถนน Springdale</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Utah (UT)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Ruby’s Inn / Bryce Canyon Grand Hotel</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Higher, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Fast Food / Retail</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>อาณาจักรโรงแรมและรีสอร์ต Ruby’s Inn หน้าปากทาง Bryce Canyon NP, หอพักพนักงานใกล้ที่ทำงาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Utah (UT)</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Park City Mountain Resort (Vail Resorts - Summer Ops)</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Mountain Host / Housekeeping / F&amp;B</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $17.50 / OT $26.25</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>สกีรีสอร์ตและเมืองภูเขาที่ใหญ่ที่สุดในสหรัฐฯ ซัมเมอร์มีกิจกรรมเดินป่าและปั่นจักรยาน, รถเมล์ฟรีทั้งเมือง</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>Maryland (MD)</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Premier Aquatics / High Sierra Pools (Summer Pools)</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Acadex, New Step, ALC, IEO</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Pool Lifeguard (เปิดเฉพาะ Summer พ.ค.-ก.ย.)</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Pool Lifeguard (Summer Only)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 10:30 – 19:30 (9 ชม.)
 พีคซัมเมอร์: 10:00 – 20:30 (10.5 ชม. สระเปิดยาว)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>50 – 54 ชม./wk (การันตี OT 10-14 ชม. สม่ำเสมอ)</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>50 – 54 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>$120</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>การันตีชั่วโมง OT แน่นอนสัปดาห์ละ 10-14 ชม., อพาร์ตเมนต์แชร์กับเพื่อน, รถไฟใต้ดิน Metro เข้า DC</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Tier S</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Maryland (MD)</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Ocean City Boardwalk Hotels &amp; Resorts (Summer)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>IEE, New Step, OEG, IEO</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Ride Operator</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>$125</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายหาด Atlantic, รถบัส Coastal Highway วิ่ง 24 ชม., หางานสองง่ายมากช่วงซัมเมอร์</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Maryland (MD)</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Jolly Roger Amusement Park &amp; Splash Mountain (Ocean City)</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>New Step, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Park Services</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 11:00 – 19:00 (8 ชม.)
+พีคซัมเมอร์: 10:00 – 23:00 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>45 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>สวนสนุกและสวนน้ำที่ใหญ่ที่สุดใน Ocean City, เล่นสวนสนุกฟรี, มีรถเมล์ผ่านหน้าสวนสนุก</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Ohio (OH)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Cedar Point Amusement Park (Summer Peak Season)</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Cedar Point Amusement Park &amp; Resorts (Sandusky)</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>OEG, IEE Thailand, IEO</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>Ride Operator / Food Service</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 10:00 – 18:30 (8 ชม.)
 พีคซัมเมอร์: 09:30 – 22:30 (12 ชม. สวนสนุกปิดดึก)</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>ฐาน $14.50 / OT $21.75</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>46 – 52 ชม./wk (หัวท้าย 38-42 ชม.)</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>46 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>$80 (ถูกสุด)</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>หอพักราคาถูกมาก ($80/wk), รถบัสรับส่งฟรี, บัตรเล่นเครื่องเล่นสวนสนุกระดับโลกฟรี</t>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกเครื่องเล่นระดับโลก, หอพักราคาถูกที่สุดในอเมริกา ($80/wk), รถบัสรับส่งฟรี, เล่นสวนสนุกฟรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Ohio (OH)</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Kings Island Amusement Park (Mason / Cincinnati)</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>OEG, IEE Thailand, IEO</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Ride Operator / Park Services / Culinary</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีคซัมเมอร์: 09:30 – 22:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>$90</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>สวนสนุกชั้นนำเครือ Cedar Fair ใกล้เมือง Cincinnati, หอพักพนักงาน + รถรับส่งฟรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Colorado (CO)</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>YMCA of the Rockies (Estes Park Center)</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Higher, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Food Service</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีคซัมเมอร์: 07:00 – 16:30 (9 ชม.)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>$110 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>แคมป์รีสอร์ตกลางเทือกเขา Rocky Mountain NP, หอพัก+อาหารบุฟเฟต์ 3 มื้อ, รถชัตเติลบัสเข้าเมืองฟรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>South Carolina (SC)</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Myrtle Beach Oceanfront Resorts &amp; Boardwalk (Summer)</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>OEG, IEE, New Step, IEO</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Lifeguard / Attractions</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>$115</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายหาดยอดนิยมอันดับ 1 ฝั่งใต้, ชายหาดยาว 60 ไมล์, เมืองเดินเท้า/จักรยาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>North Carolina (NC)</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Outer Banks Coastal Resorts (Nags Head / Kill Devil Hills)</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>IEE, New Step, Acadex</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Beach Operations / F&amp;B</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>$20 - $40</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>$125</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>หมู่เกาะตากอากาศ Outer Banks ทะเลสวย สงบ คนรวยมาพักผ่อน, บ้านพักแชร์ J-1 ริมทะเล</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Texas (TX)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Schlitterbahn Waterpark (New Braunfels / Galveston)</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>Lifeguard / Park Operations</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 19:30 (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>สวนน้ำระดับตำนานของเท็กซัส, ปลอดภาษีเงินได้รัฐ 0%, เล่นสวนน้ำฟรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Texas (TX)</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Kalahari Resorts &amp; Conventions Round Rock (Austin, TX)</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Lifeguard / Housekeeping / F&amp;B</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 19:30 (10 ชม.)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>สวนน้ำในร่มใหญ่ที่สุดในอเมริกา สาขาเท็กซัส, ปลอดภาษีรัฐ 0%, ใกล้ออสติน</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Texas (TX)</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Six Flags Fiesta Texas &amp; SeaWorld San Antonio</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>New Step, Higher, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Culinary</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีคซัมเมอร์: 09:30 – 21:30 (11.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>$115</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกและสวนน้ำระดับโลก ซานอันโตนิโอ, ปลอดภาษีรัฐ 0%, หอพักพนักงาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Texas (TX)</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Kemah Boardwalk &amp; Galveston Pleasure Pier</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>OEG, New Step, IEO</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Retail / F&amp;B</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:30 – 18:30 (8 ชม.)
+พีคซัมเมอร์: 10:00 – 22:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกริมอ่าวเม็กซิโก เครือ Landry’s, ปลอดภาษีรัฐ 0%, บรรยากาศชายทะเล</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Florida (FL)</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Universal Orlando Resort &amp; Volcano Bay</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>Attractions Attendant / Culinary / Lifeguard</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 22:00 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกระดับโลก ยูนิเวอร์แซล ออร์แลนโด, ปลอดภาษีเงินได้รัฐ 0%, บัตรเข้าสวนสนุกฟรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Florida (FL)</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Busch Gardens Tampa Bay &amp; Adventure Island</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>New Step, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Food Service</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 21:30 (11.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกโรลเลอร์โคสเตอร์อันดับ 1 ในแทมปาและสวนน้ำ, ปลอดภาษีรัฐ 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Florida (FL)</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Gaylord Palms Resort &amp; Convention Center (Kissimmee)</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, Higher</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Banquet Server / Steward</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>$125</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>รีสอร์ตศูนย์ประชุมโดมกระจกยักษ์ระดับ 4 ดาว Marriott, ปลอดภาษีรัฐ 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>New Jersey (NJ)</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Morey’s Piers &amp; Beachfront Waterparks (Wildwood, NJ)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE, New Step, IEO</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Pier Services</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 11:00 – 19:00 (8 ชม.)
+พีคซัมเมอร์: 10:30 – 23:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>45 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกริมสะพานปลาชานหาดที่ใหญ่ที่สุดในฝั่ง East Coast เปิดเฉพาะซัมเมอร์, เล่นเครื่องเล่นฟรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>South Dakota (SD)</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Xanterra Mount Rushmore / Keystone Lodges</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Higher, IEO</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>Retail / Food Service / Housekeeping</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>ทำงานหน้าอนุสรณ์สถานแห่งชาติ Mount Rushmore, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>South Dakota (SD)</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Custer State Park Resorts (State Game Lodge / Sylvan)</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Higher, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Guest Service / Housekeeping</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีคซัมเมอร์: 07:00 – 16:30 (9 ชม.)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>$105 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>อุทยานธรรมชาติฝูงควายไบซัน Custer SP, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>South Dakota (SD)</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Wall Drug Store (Wall, SD)</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>Retail / Restaurant Staff / Fast Food</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>45 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>$85 (ถูกมาก)</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>ห้างคาวบอยระดับตำนานของอเมริกา จุดแวะพักยอดฮิตก่อนเข้า Badlands NP, หอพักราคาถูก</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>South Dakota (SD)</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Deadwood Historic Hotels &amp; Casinos (The Lodge at Deadwood)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Higher, New Step, IEO</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Food &amp; Beverage</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.50 / OT $23.25</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>เมืองคาวบอยคาสิโนประวัติศาสตร์ ปลอดภาษีรัฐ 0%, มีรถราง Deadwood Trolley $1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Virginia (VA)</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Busch Gardens Williamsburg &amp; Water Country USA</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>New Step, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>Ride Operator / Culinary Operations</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึก)</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>$115</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกธีมยุโรปชื่อดัง, บัตรเข้าสวนสนุกและสวนน้ำฟรี, หอพักพนักงาน Williamsburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Virginia (VA)</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Virginia Beach Oceanfront Resorts &amp; Boardwalk</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>IEE, New Step, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Beach Attendant</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายทะเลเวอร์จิเนีย มีทางเดินเลียบหาดยาว 3 ไมล์, รถราง Wave Trolley สะดวก</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Massachusetts (MA)</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Cape Cod Oceanfront Resorts &amp; Inns (Hyannis / Yarmouth)</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Acadex, Higher</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Banquet / F&amp;B</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $16.50 / OT $24.75</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>$135</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>แหลมตากอากาศระดับตำนานของตระกูลเคนเนดี้ Cape Cod, ปั่นจักรยานเลียบหาดสะดวก</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>New Hampshire (NH)</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Omni Mount Washington Resort (Bretton Woods)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Culinary / Steward</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>$15 - $35</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>$110 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>โรงแรมปราสาทประวัติศาสตร์ระดับ 4 ดาวหน้าเทือกเขา White Mountains, ปลอดภาษีซื้อ 0% Sales Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Missouri (MO)</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Silver Dollar City Theme Park &amp; Showboat Branson Belle</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>New Step, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Ride Operator / Attractions Host / Culinary</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 21:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>$95</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกธีมยุคคาวบอย 1880s และเรือสำราญดินเนอร์โชว์ Branson, ค่าครองชีพถูกมาก</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Pennsylvania (PA)</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Hersheypark &amp; The Hotel Hershey</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE, New Step</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Food Service / Housekeeping</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีคซัมเมอร์: 09:30 – 22:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกเมืองช็อกโกแลต Hershey, หอพักพนักงาน Hershey Co-Op + รถรับส่งฟรี, เข้าสวนสนุกฟรี</t>
         </is>
       </c>
     </row>
@@ -1625,18 +4061,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="49" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
@@ -1729,7 +4165,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Denali Princess Wilderness Lodge (Denali NP)</t>
+          <t>Denali Princess Wilderness Lodge (Summer Season)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1745,7 +4181,7 @@
       <c r="F2" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 07:30 – 15:30 (8 ชม.)
-พีค: 07:00 – 17:30 (10 ชม. ควงกะ)</t>
+พีคซัมเมอร์: 07:00 – 17:30 (10 ชม. ควงกะ)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1770,7 +4206,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR ตักไม่อั้น 7 วัน, ทิปหัวเตียง, รถรับส่งพนักงาน, ส่วนลดทัวร์ 50%</t>
+          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR ตักไม่อั้น 7 วัน, ทิปหัวเตียง, รถรับส่งพนักงาน, ส่วนลดทัวร์/รถไฟ 50%</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -1802,7 +4238,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Denali Princess Wilderness Lodge (Denali NP)</t>
+          <t>Denali Princess Wilderness Lodge (Summer Season)</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -1812,13 +4248,13 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Kitchen Stewarding / Dishwasher</t>
+          <t>Kitchen Stewarding / Dishwasher (ล้างจาน)</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 16:00 – 00:00 (8 ชม.)
-พีค: 15:00 – 01:30 (10.5 ชม.)</t>
+พีคซัมเมอร์: 15:00 – 01:30 (10.5 ชม.)</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1875,7 +4311,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Grande Denali Lodge &amp; Denali Bluffs Hotel</t>
+          <t>Grande Denali Lodge &amp; Denali Bluffs Hotel (Summer Only)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1891,7 +4327,7 @@
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1916,7 +4352,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>โบนัส +$1.00/ชม. ท้ายทริป, โรงแรมหรู 4 ดาวบนยอดเขา, รถชัตเติลบัส, ส่วนลดอาหาร</t>
+          <t>โบนัส Summer Bonus +$1.00/ชม. ท้ายทริป, โรงแรมหรู 4 ดาวบนยอดเขา, รถชัตเติลบัส, ส่วนลดอาหาร</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -1948,23 +4384,23 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Mt. McKinley Princess Lodge (Trapper Creek)</t>
+          <t>Seward Windsong Lodge &amp; Kenai Fjords Tours (Pursuit)</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Higher, OEG, Acadex, IEO</t>
+          <t>OEG, Acadex, ALC, IEO</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Kitchen</t>
+          <t>Housekeeping / Tour Operations / F&amp;B</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1974,37 +4410,37 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>$10 - $20</t>
+          <t>$20 - $50</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>44 – 48 ชม./wk</t>
+          <t>44 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$120</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, รถรับส่ง, ชมวิวยอดเขาเดนาลี บรรยากาศสงบ</t>
+          <t>เมืองตากอากาศชายทะเล Seward ท่าเรือล่องเรือชมวาฬและธารน้ำแข็งซัมเมอร์, หอพักพนักงาน, ล่องเรือฟรี</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>🥩 20,320 Alaskan Grill (ในโรงแรม): Busser/Steward กะค่ำ 17:30-22:30 น. (เรต OT $24/ชม. + ทิป)</t>
+          <t>🦀 Ray’s Waterfront (ริมท่าเรือ Seward): Busser/Steward ร้านซีฟู้ดดัง 17:30-23:00 น. ($14/ชม. + ทิปสด $60-$100)</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>🍕 Northland Wood Fired Pizza (ในโรงแรม): ผู้ช่วยทำพิซซ่า/ครัว 16:30-21:30 น. (เรต OT $24/ชม.)</t>
+          <t>🍺 Seward Brewing Company: Barback/Dishwasher กะค่ำ 18:00-00:00 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>🥐 Talkeetna Roadhouse: นั่งรถตู้พนักงานเข้าเมือง Talkeetna ช่วยล้างจาน/ทำขนมวันหยุด</t>
+          <t>🛥️ Kenai Fjords Boat Cleaning: ล้างทำความสะอาดเรือทัวร์รอบเย็น 18:00-21:30 น. ($16.50/ชม.)</t>
         </is>
       </c>
     </row>
@@ -2021,63 +4457,63 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Fairbanks Princess Riverside Lodge</t>
+          <t>Talkeetna Alaskan Lodge (Pursuit Collection)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>IEE, Acadex, Higher, IEO</t>
+          <t>OEG, Acadex, Higher, IEO</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Food Runner / Laundry / Steward</t>
+          <t>Housekeeping / Kitchen / Steward</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 06:30 – 14:30 หรือ 15:00 – 23:00
-พีค: กะสลับตามรอบรถไฟ 8 ชม.</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>$20 - $40</t>
+          <t>$15 - $30</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>36 – 40 ชม./wk</t>
+          <t>44 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$115</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>หอพักในเมืองแฟร์แบงก์ส + รถชัตเติลบัส, ใกล้ Walmart และร้านอาหารไทย หางาน 2 ง่าย</t>
+          <t>โรงแรมหรูชมวิวยอดเขา Denali ในเมืองคาวบอย Talkeetna, หอพักพนักงาน + รถรับส่ง</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>🛒 Walmart Supercenter Fairbanks: จัดสต็อกสินค้า/แคชเชียร์ 16:30-22:30 น. ($16-$17/ชม. มีรถเมล์ผ่าน)</t>
+          <t>🥩 Foraker Dining Room (ในโรงแรม): Busser ร้านอาหาร Fine Dining 17:30-23:00 น. (ทิปสด $50-$90/คืน)</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>🍜 Pad Thai Restaurant / Thai House: ผู้ช่วยครัว/เสิร์ฟ 17:00-22:30 น. (ทิปสด + กินอาหารไทยฟรี)</t>
+          <t>🍕 Mountain High Pizza Pie: ผู้ช่วยทำพิซซ่า/ล้างจาน 18:00-23:30 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>🍺 The Pump House Restaurant: Busser/Dishwasher ร้านอาหารริมน้ำดัง 17:30-23:00 น. ($15/ชม. + ทิป)</t>
+          <t>🍺 Denali Brewing Company (Talkeetna Pub): Barback กะค่ำ 18:30-00:30 น. ($14/ชม. + ทิปสด)</t>
         </is>
       </c>
     </row>
@@ -2094,63 +4530,63 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Seward Windsong Lodge &amp; Kenai Fjords Tours (Pursuit)</t>
+          <t>Alyeska Resort &amp; Hotel Alyeska (Girdwood)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>OEG, Acadex, ALC, IEO</t>
+          <t>OEG, Higher, Acadex</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Tour Operations / F&amp;B</t>
+          <t>Housekeeping / Culinary / Lift Ops</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
+          <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>$20 - $50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>44 – 50 ชม./wk</t>
+          <t>42 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>$120</t>
+          <t>$135</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>เมืองตากอากาศชายทะเล Seward ท่าเรือล่องเรือชมวาฬและธารน้ำแข็ง, หอพักพนักงาน, ล่องเรือฟรี</t>
+          <t>รีสอร์ตหรูระดับโลก นั่งกระเช้าชมวิวภูเขาและธารน้ำแข็งซัมเมอร์, หอพักพนักงาน Glacier Valley</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>🦀 Ray’s Waterfront (ริมท่าเรือ Seward): Busser/Steward ร้านซีฟู้ดดัง 17:30-23:00 น. ($14/ชม. + ทิปสด $60-$100)</t>
+          <t>🥩 Seven Glaciers Restaurant (บนยอดเขา): Busser 17:30-23:00 น. (ร้าน 4 ดาว AAA ทิปมหาศาล $70-$120)</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>🍺 Seward Brewing Company: Barback/Dishwasher กะค่ำ 18:00-00:00 น. ($15/ชม. + ทิป)</t>
+          <t>🍕 Coast Pizza / Girdwood Brewing: ผู้ช่วยครัว/Barback 18:00-23:00 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>🛥️ Kenai Fjords Boat Cleaning: ล้างทำความสะอาดเรือทัวร์รอบเย็น 18:00-21:30 น. ($16.50/ชม.)</t>
+          <t>🥖 The Bake Shop Girdwood: ช่วยเตรียมเบเกอรี่/ล้างจานช่วงเช้าตรู่หรือเย็น</t>
         </is>
       </c>
     </row>
@@ -2167,23 +4603,23 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Talkeetna Alaskan Lodge (Pursuit Collection)</t>
+          <t>Mt. McKinley Princess Lodge (Trapper Creek)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>OEG, Acadex, Higher, IEO</t>
+          <t>Higher, OEG, Acadex, IEO</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Housekeeping / Kitchen / Steward</t>
+          <t>Housekeeping / Kitchen</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2193,37 +4629,37 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>$15 - $30</t>
+          <t>$10 - $20</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>44 – 50 ชม./wk</t>
+          <t>44 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>$115</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>โรงแรมหรูชมวิวยอดเขา Denali ในเมืองคาวบอย Talkeetna, หอพักพนักงาน + รถรับส่ง</t>
+          <t>อาหารบุฟเฟต์ 3 มื้อฟรีใน EDR, รถรับส่ง, ชมวิวยอดเขาเดนาลี บรรยากาศสงบ</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>🥩 Foraker Dining Room (ในโรงแรม): Busser ร้านอาหาร Fine Dining 17:30-23:00 น. (ทิปสด $50-$90/คืน)</t>
+          <t>🥩 20,320 Alaskan Grill (ในโรงแรม): Busser/Steward กะค่ำ 17:30-22:30 น. (เรต OT $24/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>🍕 Mountain High Pizza Pie: ผู้ช่วยทำพิซซ่า/ล้างจาน 18:00-23:30 น. ($15/ชม. + ทิป)</t>
+          <t>🍕 Northland Wood Fired Pizza (ในโรงแรม): ผู้ช่วยทำพิซซ่า/ครัว 16:30-21:30 น. (เรต OT $24/ชม.)</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>🍺 Denali Brewing Company (Talkeetna Pub): Barback กะค่ำ 18:30-00:30 น. ($14/ชม. + ทิปสด)</t>
+          <t>🥐 Talkeetna Roadhouse: นั่งรถตู้พนักงานเข้าเมือง Talkeetna ช่วยล้างจาน/ทำขนมวันหยุด</t>
         </is>
       </c>
     </row>
@@ -2240,63 +4676,63 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Alyeska Resort &amp; Hotel Alyeska (Girdwood)</t>
+          <t>Fairbanks Princess Riverside Lodge (Summer Season)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>OEG, Higher, Acadex</t>
+          <t>IEE, Acadex, Higher, IEO</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Culinary / Lift Ops</t>
+          <t>Food Runner / Laundry / Steward</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 06:30 – 14:30 หรือ 15:00 – 23:00
+พีคซัมเมอร์: กะสลับตามรอบรถไฟ 8 ชม.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $16.50 / OT $24.75</t>
+          <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$20 - $40</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>42 – 48 ชม./wk</t>
+          <t>36 – 40 ชม./wk</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>$135</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>รีสอร์ตหรูระดับโลก นั่งกระเช้าชมวิวภูเขาและธารน้ำแข็ง, หอพักพนักงาน Glacier Valley</t>
+          <t>หอพักในเมืองแฟร์แบงก์ส + รถชัตเติลบัส, ใกล้ Walmart และร้านอาหารไทย หางาน 2 ง่าย</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>🥩 Seven Glaciers Restaurant (บนยอดเขา): Busser 17:30-23:00 น. (ร้าน 4 ดาว AAA ทิปมหาศาล $70-$120)</t>
+          <t>🛒 Walmart Supercenter Fairbanks: จัดสต็อกสินค้า/แคชเชียร์ 16:30-22:30 น. ($16-$17/ชม. มีรถเมล์ผ่าน)</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>🍕 Coast Pizza / Girdwood Brewing: ผู้ช่วยครัว/Barback 18:00-23:00 น. ($15/ชม. + ทิป)</t>
+          <t>🍜 Pad Thai Restaurant / Thai House: ผู้ช่วยครัว/เสิร์ฟ 17:00-22:30 น. (ทิปสด + กินอาหารไทยฟรี)</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>🥖 The Bake Shop Girdwood: ช่วยเตรียมเบเกอรี่/ล้างจานช่วงเช้าตรู่หรือเย็น</t>
+          <t>🍺 The Pump House Restaurant: Busser/Dishwasher ร้านอาหารริมน้ำดัง 17:30-23:00 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
     </row>
@@ -2308,68 +4744,68 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Alaska (AK)</t>
+          <t>Wyoming (WY)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Copper River Princess Wilderness Lodge</t>
+          <t>Grand Teton Lodge Company - Jackson Lake Lodge (Summer)</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Higher, IEE, Acadex, IEO</t>
+          <t>Acadex, Higher, OEG, IEE, IEO</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Housekeeping / Kitchen / Laundry</t>
+          <t>Housekeeping / Crew Member</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:00 – 17:30 (10 ชม. ควงกะ)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
+          <t>ฐาน $17.75 / OT $26.62</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>$10 - $20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>42 – 48 ชม./wk</t>
+          <t>54 – 60 ชม./wk</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$0 (ฟรี!)</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>รีสอร์ตริมแม่น้ำ Copper River อุทยาน Wrangell-St. Elias, อาหาร EDR ฟรี 3 มื้อ</t>
+          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), ส่วนลด 40%, บัตรผ่าน 2 อุทยานฟรี</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>🐟 Two Rivers Salmon Grill (ในโรงแรม): Busser/Steward 17:30-22:30 น. (เรต OT $24/ชม. + ทิป)</t>
+          <t>🍽️ Mural Room &amp; Pioneer Grill (ในโรงแรม): Busser 17:30-22:30 น. ได้เรต OT $26.62/ชม. + ทิป</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>🛶 Copper Oar Rafting Base: ช่วยล้างทำความสะอาดเรือยาง/ชูชีพ 17:00-21:00 น. ($16/ชม.)</t>
+          <t>🍸 Blue Heron Lounge (ในโรงแรม): Barback ช่วยยกน้ำแข็ง/ล้างแก้ว 18:00-23:30 น. (เรต OT $26.62 + Tip-Out)</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>🌲 Whistle Stop Gift Shop: แคชเชียร์ร้านของฝากกะค่ำ 18:00-22:00 น.</t>
+          <t>🛶 Colter Bay Chuckwagon &amp; Marina: นั่งชัตเติลฟรีไปช่วยมินิมาร์ท/เรือแคนู 17:00-21:30 น.</t>
         </is>
       </c>
     </row>
@@ -2386,7 +4822,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Grand Teton Lodge Company - Jackson Lake Lodge</t>
+          <t>Grand Teton Lodge Company - Colter Bay Village (Summer)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -2396,13 +4832,13 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Crew Member</t>
+          <t>Cabin Attendant / Grocery Clerk / Marina</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:00 – 17:30 (10 ชม. ควงกะ)</t>
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -2417,7 +4853,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>54 – 60 ชม./wk</t>
+          <t>52 – 58 ชม./wk</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -2427,22 +4863,22 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), ส่วนลด 40%, บัตรผ่าน 2 อุทยานฟรี</t>
+          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), หมู่บ้านริมทะเลสาบ Jackson Lake</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>🍽️ Mural Room &amp; Pioneer Grill (ในโรงแรม): Busser 17:30-22:30 น. ได้เรต OT $26.62/ชม. + ทิป</t>
+          <t>🥩 Chuckwagon Restaurant (ในหมู่บ้าน): Busser/Steward บุฟเฟต์มื้อเย็น 17:00-22:00 น. (เรต OT $26.62)</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>🍸 Blue Heron Lounge (ในโรงแรม): Barback ช่วยยกน้ำแข็ง/ล้างแก้ว 18:00-23:30 น. (เรต OT $26.62 + Tip-Out)</t>
+          <t>🛒 Colter Bay General Store: แคชเชียร์/เติมสต็อกมินิมาร์ท 17:30-22:00 น. (เรต OT $26.62)</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>🛶 Colter Bay Chuckwagon &amp; Marina: นั่งชัตเติลฟรีไปช่วยมินิมาร์ท/เรือแคนู 17:00-21:30 น.</t>
+          <t>🛶 Colter Bay Marina: ล้างเรือยนต์/เรือแคนู 16:30-20:30 น. (เรต OT $26.62)</t>
         </is>
       </c>
     </row>
@@ -2459,63 +4895,63 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Grand Teton Lodge Company - Colter Bay Village</t>
+          <t>Signal Mountain Lodge (Grand Teton NP - Forever Resorts)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Acadex, Higher, OEG, IEE, IEO</t>
+          <t>Higher, Acadex, IEO</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Cabin Attendant / Grocery Clerk / Marina</t>
+          <t>Housekeeping / Front Desk / Marina</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ฐาน $17.75 / OT $26.62</t>
+          <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$15 - $30</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>52 – 58 ชม./wk</t>
+          <t>45 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>$0 (ฟรี!)</t>
+          <t>$110 (รวมกิน)</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), หมู่บ้านริมทะเลสาบ Jackson Lake</t>
+          <t>รีสอร์ตริมทะเลสาบ Signal Mountain, หอพักพนักงาน + อาหาร 3 มื้อ, ส่วนลดเช่าเรือซัมเมอร์</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>🥩 Chuckwagon Restaurant (ในหมู่บ้าน): Busser/Steward บุฟเฟต์มื้อเย็น 17:00-22:00 น. (เรต OT $26.62)</t>
+          <t>🥩 The Peaks Restaurant (ในรีสอร์ต): Busser/Runner 17:30-22:30 น. ($14/ชม. + ทิปสด $50-$90/คืน)</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>🛒 Colter Bay General Store: แคชเชียร์/เติมสต็อกมินิมาร์ท 17:30-22:00 น. (เรต OT $26.62)</t>
+          <t>🌮 Trapper Grill (ในรีสอร์ต): ผู้ช่วยครัว/ทำนาโชส์ 17:00-22:00 น. (ขอ OT $24.75/ชม.)</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>🛶 Colter Bay Marina: ล้างเรือยนต์/เรือแคนู 16:30-20:30 น. (เรต OT $26.62)</t>
+          <t>⛽ Signal Mountain Gas Station &amp; Store: แคชเชียร์รอบค่ำ 17:00-21:30 น.</t>
         </is>
       </c>
     </row>
@@ -2532,63 +4968,63 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Signal Mountain Lodge (Grand Teton NP - Forever Resorts)</t>
+          <t>Xanterra Yellowstone Lodges (Old Faithful / Canyon)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Higher, Acadex, IEO</t>
+          <t>OEG, IEE Thailand, IEO</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Front Desk / Marina</t>
+          <t>Hospitality Crew / Kitchen Steward</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+          <t>ปกติ: 07:00 – 15:30 หรือ 15:00 – 23:30
+พีคซัมเมอร์: 06:30 – 16:30 (10 ชม.)</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $16.50 / OT $24.75</t>
+          <t>ฐาน $15.70 / OT $23.55</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>$15 - $30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>45 – 50 ชม./wk</t>
+          <t>46 – 52 ชม./wk</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>$110 (รวมกิน)</t>
+          <t>$120 (รวมกิน)</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>รีสอร์ตริมทะเลสาบ Signal Mountain, หอพักพนักงาน + อาหาร 3 มื้อ, ส่วนลดเช่าเรือ</t>
+          <t>รวมหอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR, หอพักใหม่ Arnica, เที่ยวบ่อน้ำพุร้อน Yellowstone ฟรี</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>🥩 The Peaks Restaurant (ในรีสอร์ต): Busser/Runner 17:30-22:30 น. ($14/ชม. + ทิปสด $50-$90/คืน)</t>
+          <t>🌋 Old Faithful Snow Lodge Dining: Busser/Steward กะค่ำ 17:00-22:30 น. (เรต OT $23.55/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>🌮 Trapper Grill (ในรีสอร์ต): ผู้ช่วยครัว/ทำนาโชส์ 17:00-22:00 น. (ขอ OT $24.75/ชม.)</t>
+          <t>🛍️ Delaware North General Stores: แคชเชียร์ร้านของฝากข้างๆ เดิน 3 นาที 17:00-21:30 น. ($15.50/ชม.)</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>⛽ Signal Mountain Gas Station &amp; Store: แคชเชียร์รอบค่ำ 17:00-21:30 น.</t>
+          <t>🍻 Employee Pub &amp; Rec Hall: ผู้ช่วยผับพนักงาน/ทำความสะอาด 19:30-23:30 น.</t>
         </is>
       </c>
     </row>
@@ -2605,28 +5041,28 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Xanterra Yellowstone Lodges (Old Faithful / Canyon)</t>
+          <t>Four Seasons Resort &amp; Snake River Lodge (Teton Village)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>OEG, IEE Thailand, IEO</t>
+          <t>OEG, Acadex, IEO</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Hospitality Crew / Kitchen Steward</t>
+          <t>Housekeeping / Stewarding</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 07:00 – 15:30 หรือ 15:00 – 23:30
-พีค: 06:30 – 16:30 (10 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ฐาน $15.70 / OT $23.55</t>
+          <t>ฐาน $17.50 / OT $26.25</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2636,32 +5072,32 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>46 – 52 ชม./wk</t>
+          <t>45 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>$120 (รวมกิน)</t>
+          <t>$140</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>รวมหอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR, หอพักใหม่ Arnica, เที่ยวบ่อน้ำพุร้อน Yellowstone ฟรี</t>
+          <t>รีสอร์ตหรู 5 ดาวใน Teton Village, หอพักพนักงาน, นั่งรถบัส START Bus ฟรี</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>🌋 Old Faithful Snow Lodge Dining: Busser/Steward กะค่ำ 17:00-22:30 น. (เรต OT $23.55/ชม. + ทิป)</t>
+          <t>🍺 The Mangy Moose Saloon (Teton Village): Barback/Busser ผับดัง 18:00-00:30 น. (ทิปสดเศรษฐี $60-$120/คืน)</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>🛍️ Delaware North General Stores: แคชเชียร์ร้านของฝากข้างๆ เดิน 3 นาที 17:00-21:30 น. ($15.50/ชม.)</t>
+          <t>🤠 Million Dollar Cowboy Bar (เมือง Jackson): นั่ง START Bus เข้าเมือง ทำ Barback 19:00-01:30 น.</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>🍻 Employee Pub &amp; Rec Hall: ผู้ช่วยผับพนักงาน/ทำความสะอาด 19:30-23:30 น.</t>
+          <t>🍕 Alpenhof Bistro: ล้างจาน/ผู้ช่วยครัว 17:30-22:30 น. ($16/ชม. + อาหารฟรี)</t>
         </is>
       </c>
     </row>
@@ -2678,63 +5114,63 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Four Seasons Resort &amp; Snake River Lodge (Teton Village)</t>
+          <t>The Wort Hotel &amp; Silver Dollar Bar (Jackson Town)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>OEG, Acadex, IEO</t>
+          <t>Acadex, OEG, IEO</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Stewarding</t>
+          <t>Housekeeping / Banquet Server / Steward</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $17.50 / OT $26.25</t>
+          <t>ฐาน $17.00 / OT $25.50</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$30 - $60</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>45 – 50 ชม./wk</t>
+          <t>44 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>$140</t>
+          <t>$150</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>รีสอร์ตหรู 5 ดาวใน Teton Village, หอพักพนักงาน, นั่งรถบัส START Bus ฟรี</t>
+          <t>โรงแรมประวัติศาสตร์ใจกลางเมือง Jackson, เดินทางสะดวกที่สุด มีร้านค้าล้อมรอบ</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>🍺 The Mangy Moose Saloon (Teton Village): Barback/Busser ผับดัง 18:00-00:30 น. (ทิปสดเศรษฐี $60-$120/คืน)</t>
+          <t>💵 Silver Dollar Bar (ในโรงแรม): Barback/Busser บาร์ดนตรีสดคนแน่น 18:30-01:00 น. (ทิปสด $70-$130/คืน)</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>🤠 Million Dollar Cowboy Bar (เมือง Jackson): นั่ง START Bus เข้าเมือง ทำ Barback 19:00-01:30 น.</t>
+          <t>🥩 Gun Barrel Steak &amp; Game House: Busser ร้านสเต๊กเนื้อสัตว์ป่า 17:30-22:30 น. ($14/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>🍕 Alpenhof Bistro: ล้างจาน/ผู้ช่วยครัว 17:30-22:30 น. ($16/ชม. + อาหารฟรี)</t>
+          <t>🛒 Albertsons Jackson: จัดสต็อกสินค้ากะดึก 20:00-00:00 น. ($18/ชม.)</t>
         </is>
       </c>
     </row>
@@ -2751,63 +5187,63 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>The Wort Hotel &amp; Silver Dollar Bar (Jackson Town)</t>
+          <t>Under Canvas Grand Teton / Yellowstone (Summer Only)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Acadex, OEG, IEO</t>
+          <t>Higher Education, IEO</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Housekeeping / Banquet Server / Steward</t>
+          <t>Housekeeping / Guest Service</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ฐาน $17.00 / OT $25.50</t>
+          <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>$30 - $60</t>
+          <t>$50 - $100</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>44 – 50 ชม./wk</t>
+          <t>42 – 46 ชม./wk</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>$150</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>โรงแรมประวัติศาสตร์ใจกลางเมือง Jackson, เดินทางสะดวกที่สุด มีร้านค้าล้อมรอบ</t>
+          <t>แคมป์กระโจมซาฟารีหรูเปิดเฉพาะ พ.ค.-ก.ย., อาหารพนักงาน, ทิปเงินสดจากแขกไฮเอนด์</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>💵 Silver Dollar Bar (ในโรงแรม): Barback/Busser บาร์ดนตรีสดคนแน่น 18:30-01:00 น. (ทิปสด $70-$130/คืน)</t>
+          <t>🏕️ Embers Restaurant (ในแกลมปิ้ง): Food Runner กะค่ำ 17:30-22:00 น. (ได้ทิปสดคืนละ $40-$60)</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>🥩 Gun Barrel Steak &amp; Game House: Busser ร้านสเต๊กเนื้อสัตว์ป่า 17:30-22:30 น. ($14/ชม. + ทิป)</t>
+          <t>☕ Moose-Wilson Road Cafes: ผู้ช่วยบาริสต้า/เบเกอรี่ช่วงเช้าตรู่ 06:00-08:00 น. หรือเย็น</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>🛒 Albertsons Jackson: จัดสต็อกสินค้ากะดึก 20:00-00:00 น. ($18/ชม.)</t>
+          <t>🛒 Jackson Town Local Diners: นั่งรถเข้าเมืองแจ็กสัน ทำงานร้านอาหารวันหยุด</t>
         </is>
       </c>
     </row>
@@ -2819,68 +5255,68 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Wyoming (WY)</t>
+          <t>Wisconsin (WI)</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Under Canvas Grand Teton / Yellowstone</t>
+          <t>Kalahari Resorts &amp; Conventions (Wisconsin Dells)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Higher Education, IEO</t>
+          <t>OEG, Acadex, Higher, IEO, New Step</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Guest Service</t>
+          <t>Lifeguard / Housekeeping (Summer High Season)</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 09:30 – 18:00 หรือ 12:00 – 20:30
+พีคซัมเมอร์: 09:00 – 19:30 (10 ชม.)</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $16.50 / OT $24.75</t>
+          <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>$50 - $100</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>42 – 46 ชม./wk</t>
+          <t>38 – 44 ชม./wk</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>แคมป์กระโจมซาฟารีหรู, อาหารพนักงาน, ทิปเงินสดจากแขกไฮเอนด์ บรรยากาศเป็นกันเอง</t>
+          <t>หอพัก Kalahari Village, บัตรเล่นสวนน้ำฟรี, เมืองปั่นจักรยาน 100%, หางาน 2 ร้านอาหารง่าย</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>🏕️ Embers Restaurant (ในแกลมปิ้ง): Food Runner กะค่ำ 17:30-22:00 น. (ได้ทิปสดคืนละ $40-$60)</t>
+          <t>🍕 Moosejaw Pizza &amp; Dells Brewing: ปั่นจักรยาน 10 นาที Busser/Barback 18:30-23:30 น. ($13/ชม. + ทิปสด $60-$90/คืน)</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>☕ Moose-Wilson Road Cafes: ผู้ช่วยบาริสต้า/เบเกอรี่ช่วงเช้าตรู่ 06:00-08:00 น. หรือเย็น</t>
+          <t>🍔 Buffalo Phil’s Grille: Food Runner/Busser เสิร์ฟอาหารด้วยรถไฟจิ๋ว 18:00-22:30 น. ($13/ชม. + ทิปสด $50-$80)</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>🛒 Jackson Town Local Diners: นั่งรถเข้าเมืองแจ็กสัน ทำงานร้านอาหารวันหยุด</t>
+          <t>🧀 MACS Mac &amp; Cheese / Dairy Queen: แคชเชียร์/ครัวกะดึก 18:30-23:00 น. ($14.50-$15.50/ชม.)</t>
         </is>
       </c>
     </row>
@@ -2897,23 +5333,23 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Kalahari Resorts &amp; Conventions (Wisconsin Dells)</t>
+          <t>Wilderness Resort &amp; Glacier Canyon Lodge (WI Dells)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>OEG, Acadex, Higher, IEO, New Step</t>
+          <t>OEG, IEE, Acadex, IEO</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Lifeguard / Housekeeping</t>
+          <t>Waterpark Attendant / Housekeeping</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 09:30 – 18:00 หรือ 12:00 – 20:30
-พีค: 09:00 – 19:30 (10 ชม.)</t>
+          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
+พีคซัมเมอร์: 08:30 – 19:00 (10 ชม.)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2928,7 +5364,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>38 – 44 ชม./wk</t>
+          <t>40 – 46 ชม./wk</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2938,22 +5374,22 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>หอพัก Kalahari Village, บัตรเล่นสวนน้ำฟรี, เมืองปั่นจักรยาน 100%, หางาน 2 ง่ายที่สุดในอเมริกา</t>
+          <t>อาณาจักรรีสอร์ตสวนน้ำที่ใหญ่ที่สุดในอเมริกา (600 เอเคอร์), หอพักพนักงานในรีสอร์ต</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>🍕 Moosejaw Pizza &amp; Dells Brewing: ปั่นจักรยาน 10 นาที Busser/Barback 18:30-23:30 น. ($13/ชม. + ทิปสด $60-$90/คืน)</t>
+          <t>🥩 Field’s at the Wilderness (สเต๊กหรูในรีสอร์ต): Busser 17:30-23:00 น. ($12/ชม. + ทิปสด $70-$120/คืน)</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>🍔 Buffalo Phil’s Grille: Food Runner/Busser เสิร์ฟอาหารด้วยรถไฟจิ๋ว 18:00-22:30 น. ($13/ชม. + ทิปสด $50-$80)</t>
+          <t>🍕 Sarento’s Restaurant (ในรีสอร์ต): Food Runner/ล้างจาน 17:00-22:30 น. (ขอ OT ในรีสอร์ต $22.50)</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>🧀 MACS Mac &amp; Cheese / Dairy Queen: แคชเชียร์/ครัวกะดึก 18:30-23:00 น. ($14.50-$15.50/ชม.)</t>
+          <t>🍔 B-LUX Grill &amp; Bar: Barback/Busser ร้านเบอร์เกอร์คราฟต์เบียร์ 18:00-00:00 น. (ทิปสดดีมาก)</t>
         </is>
       </c>
     </row>
@@ -2970,23 +5406,23 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Wilderness Resort &amp; Glacier Canyon Lodge (WI Dells)</t>
+          <t>Mt. Olympus Water &amp; Theme Park (WI Dells)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>OEG, IEE, Acadex, IEO</t>
+          <t>New Step, Acadex, Higher, IEO</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Waterpark Attendant / Housekeeping</t>
+          <t>Ride Operator / Housekeeping / Lifeguard</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
-พีค: 08:30 – 19:00 (10 ชม.)</t>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 21:00 (11.5 ชม.)</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -3001,32 +5437,32 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>40 – 46 ชม./wk</t>
+          <t>42 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$95</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>อาณาจักรรีสอร์ตสวนน้ำที่ใหญ่ที่สุดในอเมริกา (600 เอเคอร์), หอพักพนักงานในรีสอร์ต</t>
+          <t>สวนสนุกธีมกรีกโบราณ โรลเลอร์โคสเตอร์ไม้, หอพักราคาถูก, ทำเลติดถนนใหญ่ Parkway</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>🥩 Field’s at the Wilderness (สเต๊กหรูในรีสอร์ต): Busser 17:30-23:00 น. ($12/ชม. + ทิปสด $70-$120/คืน)</t>
+          <t>🥞 Paul Bunyan’s Cook Shanty: ล้างจาน/ทำความสะอาดรอบค่ำ 17:30-22:00 น. ($14.50/ชม. + กินฟรี)</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>🍕 Sarento’s Restaurant (ในรีสอร์ต): Food Runner/ล้างจาน 17:00-22:30 น. (ขอ OT ในรีสอร์ต $22.50)</t>
+          <t>🌭 Hot Dog Avenue: แคชเชียร์/ครัวปิด 18:00-22:30 น. ($14.50/ชม.)</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>🍔 B-LUX Grill &amp; Bar: Barback/Busser ร้านเบอร์เกอร์คราฟต์เบียร์ 18:00-00:00 น. (ทิปสดดีมาก)</t>
+          <t>🍺 Showboat Saloon (Downtown): Barback ผับดนตรีสด 19:00-01:30 น. (ทิปสดแน่น)</t>
         </is>
       </c>
     </row>
@@ -3043,28 +5479,28 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Mt. Olympus Water &amp; Theme Park (WI Dells)</t>
+          <t>Noah’s Ark Waterpark (Wisconsin Dells - Summer Only)</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>New Step, Acadex, Higher, IEO</t>
+          <t>OEG, IEE, New Step, IEO</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Ride Operator / Housekeeping / Lifeguard</t>
+          <t>Ride Operator / Park Services</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 21:00 (11.5 ชม.)</t>
+          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
+พีคซัมเมอร์: 08:30 – 18:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
+          <t>ฐาน $14.50 / OT $21.75</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -3074,32 +5510,32 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>42 – 48 ชม./wk</t>
+          <t>40 – 46 ชม./wk</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>$95</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>สวนสนุกธีมกรีกโบราณ โรลเลอร์โคสเตอร์ไม้, หอพักราคาถูก, ทำเลติดถนนใหญ่ Parkway</t>
+          <t>สวนน้ำกลางแจ้งใหญ่ที่สุดในอเมริกา เปิดเฉพาะซัมเมอร์, เล่นสวนน้ำฟรี, หอพักพนักงานใกล้ที่ทำงาน</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>🥞 Paul Bunyan’s Cook Shanty: ล้างจาน/ทำความสะอาดรอบค่ำ 17:30-22:00 น. ($14.50/ชม. + กินฟรี)</t>
+          <t>🍻 Monk’s Bar &amp; Grill (Downtown Dells): ปั่นจักรยานไปทำ Barback/Busser 18:30-00:00 น. (ทิปสดแน่นมาก)</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>🌭 Hot Dog Avenue: แคชเชียร์/ครัวปิด 18:00-22:30 น. ($14.50/ชม.)</t>
+          <t>🍕 Pizza Pub Dells: ช่วยส่งอาหาร/ทำพิซซ่า/ล้างจานรอบดึก 18:00-00:00 น. ($14/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>🍺 Showboat Saloon (Downtown): Barback ผับดนตรีสด 19:00-01:30 น. (ทิปสดแน่น)</t>
+          <t>🍦 Dairy Queen / Cold Stone Dells: ตักไอศกรีมกะค่ำ 18:00-22:30 น. ($14.50/ชม.)</t>
         </is>
       </c>
     </row>
@@ -3116,28 +5552,28 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Noah’s Ark Waterpark (Wisconsin Dells)</t>
+          <t>Chula Vista Resort &amp; Waterpark (WI Dells)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>OEG, IEE, New Step, IEO</t>
+          <t>Higher, Acadex, IEE, IEO</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Ride Operator / Park Services</t>
+          <t>Housekeeping / Lifeguard</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
-พีค: 08:30 – 18:30 (9.5 ชม.)</t>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $14.50 / OT $21.75</t>
+          <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3147,32 +5583,32 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>40 – 46 ชม./wk</t>
+          <t>40 – 45 ชม./wk</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>สวนน้ำกลางแจ้งใหญ่ที่สุดในอเมริกา, เล่นสวนน้ำฟรี, หอพักพนักงานใกล้ที่ทำงาน</t>
+          <t>รีสอร์ตริมแม่น้ำ Wisconsin River, สวนน้ำในร่ม/กลางแจ้ง, หอพักในรีสอร์ต</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>🍻 Monk’s Bar &amp; Grill (Downtown Dells): ปั่นจักรยานไปทำ Barback/Busser 18:30-00:00 น. (ทิปสดแน่นมาก)</t>
+          <t>🥩 Kaminski’s Chop House (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. ($12/ชม. + ทิปสดเศรษฐี $70-$120/คืน)</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>🍕 Pizza Pub Dells: ช่วยส่งอาหาร/ทำพิซซ่า/ล้างจานรอบดึก 18:00-00:00 น. ($14/ชม. + ทิป)</t>
+          <t>🌮 Mexicali Rose: Busser/Runner ร้านอาหารเม็กซิกันริมน้ำ 18:00-23:00 น. ($13/ชม. + ทิปสด)</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>🍦 Dairy Queen / Cold Stone Dells: ตักไอศกรีมกะค่ำ 18:00-22:30 น. ($14.50/ชม.)</t>
+          <t>🍕 Kilbourn City Grill (ในรีสอร์ต): ล้างจาน/ผู้ช่วยครัว 17:00-22:00 น. (ขอ OT ในรีสอร์ตได้)</t>
         </is>
       </c>
     </row>
@@ -3189,63 +5625,63 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Chula Vista Resort &amp; Waterpark (WI Dells)</t>
+          <t>Grand Geneva Resort &amp; Spa (Lake Geneva, WI)</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Higher, Acadex, IEE, IEO</t>
+          <t>Acadex, OEG, IEO</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Housekeeping / Lifeguard</t>
+          <t>Housekeeping / Banquet / Culinary</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$20 - $50</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>40 – 45 ชม./wk</t>
+          <t>42 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$110</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>รีสอร์ตริมแม่น้ำ Wisconsin River, สวนน้ำในร่ม/กลางแจ้ง, หอพักในรีสอร์ต</t>
+          <t>รีสอร์ตหรูระดับ 4 เพชร AAA เมืองตากอากาศทะเลสาบคนรวยชิคาโกช่วงซัมเมอร์, หอพักพนักงาน</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>🥩 Kaminski’s Chop House (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. ($12/ชม. + ทิปสดเศรษฐี $70-$120/คืน)</t>
+          <t>🥩 Geneva ChopHouse (ในรีสอร์ต): Busser 17:30-23:00 น. ($13/ชม. + ทิปสด $60-$100/คืน)</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>🌮 Mexicali Rose: Busser/Runner ร้านอาหารเม็กซิกันริมน้ำ 18:00-23:00 น. ($13/ชม. + ทิปสด)</t>
+          <t>🍕 Popeye’s on Lake Geneva: Busser/Dishwasher ร้านอาหารริมทะเลสาบดัง 18:00-23:30 น. (ทิปดี)</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>🍕 Kilbourn City Grill (ในรีสอร์ต): ล้างจาน/ผู้ช่วยครัว 17:00-22:00 น. (ขอ OT ในรีสอร์ตได้)</t>
+          <t>🍺 The Bottle Shop / Local Pubs: Barback ร้านคราฟต์เบียร์ 18:30-00:00 น.</t>
         </is>
       </c>
     </row>
@@ -3257,43 +5693,43 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Wisconsin (WI)</t>
+          <t>Tennessee (TN)</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Grand Geneva Resort &amp; Spa (Lake Geneva, WI)</t>
+          <t>Dollywood Theme Park &amp; Splash Country (Pigeon Forge)</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Acadex, OEG, IEO</t>
+          <t>New Step, Acadex, IEO</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Banquet / Culinary</t>
+          <t>Ride Operator / Food Service / Retail</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึกมีพลุ)</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
+          <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>$20 - $50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>42 – 48 ชม./wk</t>
+          <t>44 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -3303,22 +5739,22 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>รีสอร์ตหรูระดับ 4 เพชร AAA เมืองตากอากาศทะเลสาบคนรวยชิคาโก, หอพักพนักงาน</t>
+          <t>ปลอดภาษีเงินได้รัฐ 0%, นั่งรถราง Pigeon Forge Trolley $1/วัน, บัตรเข้าสวนสนุก Dollywood ฟรี</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>🥩 Geneva ChopHouse (ในรีสอร์ต): Busser 17:30-23:00 น. ($13/ชม. + ทิปสด $60-$100/คืน)</t>
+          <t>🍗 Paula Deen’s Family Kitchen (The Island): นั่งรถรางไปทำ Busser 18:30-23:00 น. ($13/ชม. + ทิปสด $60-$90)</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>🍕 Popeye’s on Lake Geneva: Busser/Dishwasher ร้านอาหารริมทะเลสาบดัง 18:00-23:30 น. (ทิปดี)</t>
+          <t>🍕 Mellow Mushroom Pizza: Barback/Busser ร้านพิซซ่าคราฟต์เบียร์ 18:30-00:00 น. ($12/ชม. + ทิปสด $50-$80)</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>🍺 The Bottle Shop / Local Pubs: Barback ร้านคราฟต์เบียร์ 18:30-00:00 น.</t>
+          <t>🥞 Puckett’s Grocery &amp; Restaurant: Food Runner 18:00-23:00 น. ($13/ชม. + ทิป)</t>
         </is>
       </c>
     </row>
@@ -3335,7 +5771,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Dollywood Theme Park &amp; Splash Country (Pigeon Forge)</t>
+          <t>The Island in Pigeon Forge (Arcades &amp; Attractions)</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3345,13 +5781,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Ride Operator / Food Service / Retail</t>
+          <t>Attractions Host / Retail / F&amp;B</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึก)</t>
+          <t>ปกติ: 10:00 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 10:00 – 23:00 (กะดึก)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3361,12 +5797,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$20 - $40</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>44 – 50 ชม./wk</t>
+          <t>42 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3376,22 +5812,22 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>ปลอดภาษีเงินได้รัฐ 0%, นั่งรถราง Pigeon Forge Trolley $1/วัน, บัตรเข้าสวนสนุก Dollywood ฟรี</t>
+          <t>ศูนย์รวมความบันเทิง ชิงช้าสวรรค์ยักษ์และร้านอาหารกลางเมือง, รถรางผ่านหน้าร้าน</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>🍗 Paula Deen’s Family Kitchen (The Island): นั่งรถรางไปทำ Busser 18:30-23:00 น. ($13/ชม. + ทิปสด $60-$90)</t>
+          <t>🦜 Margaritaville Restaurant (ใน The Island): Busser/Barback 18:30-00:00 น. ($13/ชม. + ทิปสด $60-$100)</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>🍕 Mellow Mushroom Pizza: Barback/Busser ร้านพิซซ่าคราฟต์เบียร์ 18:30-00:00 น. ($12/ชม. + ทิปสด $50-$80)</t>
+          <t>🥞 Timberwood Grill (ใน The Island): ล้างจาน/ผู้ช่วยครัว 18:00-23:30 น. ($14.50/ชม.)</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>🥞 Puckett’s Grocery &amp; Restaurant: Food Runner 18:00-23:00 น. ($13/ชม. + ทิป)</t>
+          <t>🍭 The Island Candy Kitchen: แคชเชียร์/ทำขนม 18:00-22:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
@@ -3408,23 +5844,23 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>The Island in Pigeon Forge (Arcades &amp; Attractions)</t>
+          <t>Wilderness at the Smokies (Sevierville)</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>New Step, Acadex, IEO</t>
+          <t>OEG, Acadex, Higher, IEO</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Attractions Host / Retail / F&amp;B</t>
+          <t>Lifeguard / Housekeeping</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 10:00 – 18:00 (8 ชม.)
-พีค: 10:00 – 23:00 (กะดึก)</t>
+          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
+พีคซัมเมอร์: 08:30 – 19:30 (10.5 ชม.)</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -3434,7 +5870,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>$20 - $40</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -3444,27 +5880,27 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>$110</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>ศูนย์รวมความบันเทิง ชิงช้าสวรรค์ยักษ์และร้านอาหารกลางเมือง, รถรางผ่านหน้าร้าน</t>
+          <t>สวนน้ำในร่มและกลางแจ้งใหญ่ที่สุดในเทนเนสซี, ปลอดภาษีรัฐ 0%, หอพักพนักงาน Sevierville</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>🦜 Margaritaville Restaurant (ใน The Island): Busser/Barback 18:30-00:00 น. ($13/ชม. + ทิปสด $60-$100)</t>
+          <t>🍏 Applewood Farmhouse Restaurant: Busser ร้านอาหารดังคนแน่น 18:00-22:30 น. (ทิปสด $60-$100/คืน)</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
         <is>
-          <t>🥞 Timberwood Grill (ใน The Island): ล้างจาน/ผู้ช่วยครัว 18:00-23:30 น. ($14.50/ชม.)</t>
+          <t>🥩 Hidden Trail Restaurant (ในรีสอร์ต): ล้างจาน/Busser กะค่ำ 18:00-22:30 น. (ขอ OT ในรีสอร์ต $22.50/ชม.)</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>🍭 The Island Candy Kitchen: แคชเชียร์/ทำขนม 18:00-22:30 น. ($15/ชม.)</t>
+          <t>🛍️ Tanger Outlets Sevierville: จัดสต็อกสินค้า/ปิดร้าน 18:00-21:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
@@ -3481,23 +5917,23 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Wilderness at the Smokies (Sevierville)</t>
+          <t>Anakeesta Mountaintop Theme Park (Gatlinburg)</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>OEG, Acadex, Higher, IEO</t>
+          <t>Higher, IEE, IEO</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Lifeguard / Housekeeping</t>
+          <t>Guest Host / F&amp;B / Retail</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>ปกติ: 09:00 – 17:30 (8 ชม.)
-พีค: 08:30 – 19:30 (10.5 ชม.)</t>
+พีคซัมเมอร์: 08:30 – 20:00 (10.5 ชม.)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3507,7 +5943,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$15 - $30</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -3517,27 +5953,27 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$110</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>สวนน้ำในร่มใหญ่ที่สุดในเทนเนสซี, ปลอดภาษีรัฐ 0%, หอพักพนักงาน Sevierville</t>
+          <t>สวนสนุกธรรมชาติบนยอดเขา Gatlinburg นั่งกระเช้า Chondola, ปลอดภาษีรัฐ 0%</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>🍏 Applewood Farmhouse Restaurant: Busser ร้านอาหารดังคนแน่น 18:00-22:30 น. (ทิปสด $60-$100/คืน)</t>
+          <t>🍺 Smoky Mountain Brewery (Gatlinburg): Barback/Busser 18:30-00:30 น. ($12/ชม. + ทิปสด $70-$120/คืน)</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>🥩 Hidden Trail Restaurant (ในรีสอร์ต): ล้างจาน/Busser กะค่ำ 18:00-22:30 น. (ขอ OT ในรีสอร์ต $22.50/ชม.)</t>
+          <t>🥩 Alamo Steakhouse: Busser/Dishwasher ร้านสเต๊กคาวบอย 17:30-23:00 น. ($13/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>🛍️ Tanger Outlets Sevierville: จัดสต็อกสินค้า/ปิดร้าน 18:00-21:30 น. ($15/ชม.)</t>
+          <t>🥞 Pancake Pantry (ร้านแพนเค้กอันดับ 1): ช่วยเตรียมวัตถุดิบ/ล้างจานรอบบ่าย-เย็น</t>
         </is>
       </c>
     </row>
@@ -3549,68 +5985,68 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Tennessee (TN)</t>
+          <t>Montana (MT)</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Anakeesta Mountaintop Theme Park (Gatlinburg)</t>
+          <t>Glacier National Park Lodges (Pursuit / Xanterra)</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Higher, IEE, IEO</t>
+          <t>OEG, Acadex, Higher, IEO</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Guest Host / F&amp;B / Retail</t>
+          <t>Hospitality Crew / Housekeeping</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 09:00 – 17:30 (8 ชม.)
-พีค: 08:30 – 20:00 (10.5 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>$15 - $30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>42 – 48 ชม./wk</t>
+          <t>46 – 52 ชม./wk</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>$110</t>
+          <t>$115 (รวมกิน)</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>สวนสนุกธรรมชาติบนยอดเขา Gatlinburg นั่งกระเช้า Chondola, ปลอดภาษีรัฐ 0%</t>
+          <t>อุทยานธรรมชาติธารน้ำแข็ง Glacier NP เปิดเฉพาะซัมเมอร์, ปลอดภาษีมูลค่าเพิ่ม 0% Sales Tax</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>🍺 Smoky Mountain Brewery (Gatlinburg): Barback/Busser 18:30-00:30 น. ($12/ชม. + ทิปสด $70-$120/คืน)</t>
+          <t>🥩 Belton Chalet Dining Room: Busser/Steward ร้านอาหารประวัติศาสตร์ 17:30-22:30 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>🥩 Alamo Steakhouse: Busser/Dishwasher ร้านสเต๊กคาวบอย 17:30-23:00 น. ($13/ชม. + ทิป)</t>
+          <t>🛶 Glacier Raft Company Base: พนักงานล้างทำความสะอาดเรือยาง/อุปกรณ์ล่องแก่ง 17:00-21:30 น. ($16/ชม.)</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>🥞 Pancake Pantry (ร้านแพนเค้กอันดับ 1): ช่วยเตรียมวัตถุดิบ/ล้างจานรอบบ่าย-เย็น</t>
+          <t>🥐 West Glacier Bakery &amp; Cafe: ผู้ช่วยเตรียมวัตถุดิบ/ล้างจาน 17:00-22:00 น.</t>
         </is>
       </c>
     </row>
@@ -3622,68 +6058,68 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Tennessee (TN)</t>
+          <t>Montana (MT)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Ober Mountain / Gatlinburg Area Lodges</t>
+          <t>Many Glacier Hotel &amp; Glacier Park Lodge (East Glacier)</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>IEE, New Step, IEO</t>
+          <t>OEG, Acadex, IEO</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Attractions Operator / Retail</t>
+          <t>Housekeeping / Dining Room / Steward</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 09:00 – 17:00 (8 ชม.)
-พีค: 08:30 – 19:00 (10 ชม.)</t>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีคซัมเมอร์: 07:00 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$15 - $30</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>40 – 46 ชม./wk</t>
+          <t>46 – 52 ชม./wk</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>$110</t>
+          <t>$115 (รวมกิน)</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>กระเช้าลอยฟ้าและสวนสนุกบนยอดเขา Gatlinburg, ปลอดภาษีรัฐ 0%, เมืองเดินเท้า 100%</t>
+          <t>โรงแรมสไตล์สวิสชาเลต์ริมทะเลสาบ Swiftcurrent Lake สวยที่สุดใน Glacier NP, อาหาร EDR 3 มื้อ</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>🥃 Ole Smoky Moonshine Distillery: พนักงานเช็ดแก้ว/เติมสต็อก/แคชเชียร์ 17:30-22:30 น. ($15/ชม.)</t>
+          <t>🥩 Ptarmigan Dining Room (ในโรงแรม): Busser 17:00-22:30 น. (เรต OT $24/ชม. + ทิปสด)</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>🥩 Calhoun’s in Gatlinburg: Busser/Runner ร้านบาร์บีคิวซี่โครงหมูชื่อดัง 17:30-23:00 น. (ทิปดี)</t>
+          <t>☕ Heidi’s Snack Shop (ในโรงแรม): แคชเชียร์/ชงกาแฟ 16:30-21:30 น. (ขอ OT $24/ชม.)</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>🍕 Best Italian Cafe &amp; Pizzeria: ผู้ช่วยครัว/ล้างจาน 18:00-23:30 น. ($14/ชม. + ทิป)</t>
+          <t>🛶 Many Glacier Boat Tours: ช่วยเทียบเรือ/ล้างเรือทัวร์ 17:00-20:30 น.</t>
         </is>
       </c>
     </row>
@@ -3695,33 +6131,33 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Texas (TX)</t>
+          <t>Montana (MT)</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Schlitterbahn Waterpark (New Braunfels / Galveston)</t>
+          <t>Big Sky Resort / Montage Big Sky</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>OEG, Acadex, IEE, IEO</t>
+          <t>Acadex, Higher, IEE, IEO</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Lifeguard / Park Operations</t>
+          <t>Mountain Operations / Housekeeping</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 19:30 (10 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
+          <t>ฐาน $17.50 / OT $26.25</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -3731,32 +6167,32 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>44 – 50 ชม./wk</t>
+          <t>46 – 52 ชม./wk</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>$110</t>
+          <t>$140</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>สวนน้ำระดับตำนานของเท็กซัส, ปลอดภาษีเงินได้รัฐ 0%, เล่นสวนน้ำฟรี</t>
+          <t>รีสอร์ตภูเขาหรูหราไฮเอนด์, ค่าแรงฐานสูงมาก, มีรถบัส Skyline Bus ฟรี</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>🥩 Gristmill River Restaurant (Gruene): Busser ร้านอาหารริมแม่น้ำสุดคึกคัก 18:30-23:30 น. ($12/ชม. + ทิปสด $60-$100)</t>
+          <t>🍺 Lone Peak Brewery (Town Center): Barback/Busser 17:30-23:30 น. ($15/ชม. + ทิปสดเศรษฐี $60-$100/คืน)</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>🦫 Buc-ee’s New Braunfels (ใหญ่ที่สุดในโลก): แคชเชียร์/Food Prep กะดึก 19:00-00:00 น. ($17-$19/ชม. จ่ายหนักมาก)</t>
+          <t>🍖 The Riverhouse BBQ: Busser/Runner ร้านบาร์บีคิวริมแม่น้ำ Gallatin 17:00-22:30 น. ($14/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>🍺 Krause’s Cafe &amp; Biergarten: Barback/Runner ร้านเบียร์เยอรมัน 18:00-23:00 น. ($13/ชม. + ทิป)</t>
+          <t>🛒 Roxy’s Market Big Sky: พนักงานจัดสต็อกซูเปอร์มาร์เก็ต 18:00-22:00 น. ($17/ชม.)</t>
         </is>
       </c>
     </row>
@@ -3768,33 +6204,33 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Texas (TX)</t>
+          <t>Maine (ME)</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Kalahari Resorts &amp; Conventions Round Rock (Austin, TX)</t>
+          <t>Bar Harbor Grand Hotel / Harborside Hotel</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>OEG, Acadex, IEO</t>
+          <t>Acadex, OEG, Higher, IEO</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Lifeguard / Housekeeping / F&amp;B</t>
+          <t>Housekeeping / Laundry</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 19:30 (10 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
+          <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3804,32 +6240,32 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>42 – 48 ชม./wk</t>
+          <t>44 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>$120</t>
+          <t>$130</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>สวนน้ำในร่มใหญ่ที่สุดในอเมริกา สาขาเท็กซัส, ปลอดภาษีรัฐ 0%, ใกล้ออสติน</t>
+          <t>เมืองตากอากาศชายทะเล Bar Harbor &amp; อุทยาน Acadia NP, รถบัส Island Explorer ฟรี</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>🥩 Double Cut Steak House (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. ($13/ชม. + ทิปสด $70-$120)</t>
+          <t>🦞 Stewman’s Lobster Pound (ริมทะเล): Busser/Barback ร้านกุ้งล็อบสเตอร์ 17:30-23:00 น. ($13/ชม. + ทิปสด $60-$120/คืน)</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>🍕 Tom Foolerys Adventure Park (ในรีสอร์ต): คุมเครื่องเล่น/เกมรอบค่ำ 18:00-23:00 น. (ขอ OT $23.25)</t>
+          <t>🍺 Geddy’s Down Under / The Chart Room: Busser/Runner 18:00-23:30 น. (ทิปสดแน่นมาก)</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>🍔 Round Rock Local Eateries: Busser/ล้างจานร้านอาหารรอบนอก 18:30-23:30 น.</t>
+          <t>🍦 Ben &amp; Bill’s Chocolate Emporium: พนักงานตักไอศกรีม/แคชเชียร์ 17:00-22:00 น. ($15.50/ชม.)</t>
         </is>
       </c>
     </row>
@@ -3841,33 +6277,33 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Texas (TX)</t>
+          <t>Maine (ME)</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Six Flags Fiesta Texas &amp; SeaWorld San Antonio</t>
+          <t>Cliff House Maine (Cape Neddick / Ogunquit)</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>New Step, Higher, IEE, IEO</t>
+          <t>Higher, Acadex, IEO</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Ride Operator / Lifeguard / Culinary</t>
+          <t>Housekeeping / Culinary / Stewarding</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
-พีค: 09:30 – 21:30 (11.5 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $14.50 / OT $21.75</t>
+          <t>ฐาน $17.00 / OT $25.50</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -3882,27 +6318,27 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>$115</t>
+          <t>$135</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>สวนสนุกและสวนน้ำระดับโลก ซานอันโตนิโอ, ปลอดภาษีรัฐ 0%, หอพักพนักงาน</t>
+          <t>รีสอร์ตหรูบนหน้าผาริมมหาสมุทรแอตแลนติก แขกไฮเอนด์ระดับมหาเศรษฐีบอสตันและนิวยอร์ก</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>🥩 The County Line BBQ (River Walk): Busser ร้านบาร์บีคิวริมแม่น้ำ 19:00-00:00 น. (ทิปสด $60-$100/คืน)</t>
+          <t>🦞 The Tiller Restaurant (ในรีสอร์ต): Busser ร้าน Fine Dining วิวมหาสมุทร 17:30-23:00 น. (ทิปสด $70-$130/คืน)</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>🎸 Hard Rock Cafe San Antonio: Food Runner/Busser 19:00-00:30 น. ($13/ชม. + ทิป)</t>
+          <t>🍺 Nubb’s Lobster Shack (ในรีสอร์ต): Food Runner/Barback 17:00-22:30 น. (ขอ OT ในรีสอร์ต $25.50)</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>🌮 Boudro’s on the Riverwalk: ล้างจาน/ผู้ช่วยครัว 19:00-01:00 น. ($15/ชม.)</t>
+          <t>🍦 Ogunquit Beach Cafes: ผู้ช่วยครัว/บริการรอบเย็น</t>
         </is>
       </c>
     </row>
@@ -3914,38 +6350,38 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Texas (TX)</t>
+          <t>Maine (ME)</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Kemah Boardwalk &amp; Galveston Pleasure Pier</t>
+          <t>The Nonantum Resort (Kennebunkport, ME)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>OEG, New Step, IEO</t>
+          <t>Higher, Acadex, IEO</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Ride Operator / Retail / F&amp;B</t>
+          <t>Housekeeping / Banquet / F&amp;B</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>ปกติ: 10:30 – 18:30 (8 ชม.)
-พีค: 10:00 – 22:30 (12 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>ฐาน $14.50 / OT $21.75</t>
+          <t>ฐาน $16.50 / OT $24.75</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>$15 - $30</t>
+          <t>$20 - $50</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -3955,49 +6391,49 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>$110</t>
+          <t>$125</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>สวนสนุกริมอ่าวเม็กซิโก เครือ Landry’s, ปลอดภาษีรัฐ 0%, บรรยากาศชายทะเล</t>
+          <t>รีสอร์ตตากอากาศริมน้ำประวัติศาสตร์ เมืองของประธานาธิบดีบุช, หอพักพนักงาน Kennebunkport</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>🦞 Aquarium Restaurant Kemah (ในเครือ): Busser ร้านอาหารใต้น้ำ 18:30-23:30 น. (ทิปสด $60-$100/คืน)</t>
+          <t>🦞 The Clam Shack (สะพาน Kennebunkport): ล้างจาน/ทอดซีฟู้ดร้านดัง 17:30-22:30 น. ($16/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>🍤 Bubba Gump Shrimp Co. (Galveston Pier): Food Runner/Busser 18:30-00:00 น. (ทิปดี)</t>
+          <t>🥩 Ocean Restaurant: Busser ร้านอาหารหรูริมน้ำ 18:00-23:00 น. (ทิปสด $60-$100/คืน)</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>🏖️ The Spot (Galveston Seawall): Barback/Busser ร้านอาหารริมหาดคนแน่น 19:00-01:00 น.</t>
+          <t>🍦 Rococo Artisan Ice Cream: ตักไอศกรีม 17:00-22:00 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Tier A</t>
+          <t>Tier S</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Montana (MT)</t>
+          <t>Utah (UT)</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Glacier National Park Lodges (Pursuit / Xanterra)</t>
+          <t>Zion National Park Lodge (Xanterra Springdale)</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>OEG, Acadex, Higher, IEO</t>
+          <t>OEG, IEE, Acadex, IEO</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -4007,8 +6443,8 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีคซัมเมอร์: 07:00 – 16:30 (9 ชม.)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -4023,138 +6459,138 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>46 – 52 ชม./wk</t>
+          <t>44 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>$115 (รวมกิน)</t>
+          <t>$110</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>อุทยานธรรมชาติธารน้ำแข็ง Glacier NP, ปลอดภาษีมูลค่าเพิ่ม 0% Sales Tax, หอพัก+อาหาร EDR</t>
+          <t>อุทยานแห่งชาติหุบเขาผาแดง Zion NP, มีรถชัตเติลบัสฟรีวิ่งตลอดถนน Springdale</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>🥩 Belton Chalet Dining Room: Busser/Steward ร้านอาหารประวัติศาสตร์ 17:30-22:30 น. ($15/ชม. + ทิป)</t>
+          <t>🌮 Bit &amp; Spur Restaurant &amp; Saloon: Busser/Barback 17:30-23:00 น. ($13/ชม. + ทิปสดแขกต่างชาติ $50-$90/คืน)</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
         <is>
-          <t>🛶 Glacier Raft Company Base: พนักงานล้างทำความสะอาดเรือยาง/อุปกรณ์ล่องแก่ง 17:00-21:30 น. ($16/ชม.)</t>
+          <t>🍔 Oscar’s Cafe (Springdale): Food Runner/Busser 17:00-22:00 น. ($13/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>🥐 West Glacier Bakery &amp; Cafe: ผู้ช่วยเตรียมวัตถุดิบ/ล้างจาน 17:00-22:00 น.</t>
+          <t>🍺 Zion Canyon Brew Pub: ล้างจาน/ผู้ช่วยครัวหน้าปากทางเข้าอุทยาน 18:00-23:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Montana (MT)</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Many Glacier Hotel &amp; Glacier Park Lodge (East Glacier)</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>OEG, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>Housekeeping / Dining Room / Steward</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
-พีค: 07:00 – 17:00 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>$15 - $30</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>46 – 52 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J34" s="8" t="inlineStr">
-        <is>
-          <t>$115 (รวมกิน)</t>
-        </is>
-      </c>
-      <c r="K34" s="10" t="inlineStr">
-        <is>
-          <t>โรงแรมสไตล์สวิสชาเลต์ริมทะเลสาบ Swiftcurrent Lake สวยที่สุดใน Glacier NP, อาหาร EDR 3 มื้อ</t>
-        </is>
-      </c>
-      <c r="L34" s="10" t="inlineStr">
-        <is>
-          <t>🥩 Ptarmigan Dining Room (ในโรงแรม): Busser 17:00-22:30 น. (เรต OT $24/ชม. + ทิปสด)</t>
-        </is>
-      </c>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>☕ Heidi’s Snack Shop (ในโรงแรม): แคชเชียร์/ชงกาแฟ 16:30-21:30 น. (ขอ OT $24/ชม.)</t>
-        </is>
-      </c>
-      <c r="N34" s="10" t="inlineStr">
-        <is>
-          <t>🛶 Many Glacier Boat Tours: ช่วยเทียบเรือ/ล้างเรือทัวร์ 17:00-20:30 น.</t>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Utah (UT)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Ruby’s Inn / Bryce Canyon Grand Hotel</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Higher, IEE, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Fast Food / Retail</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>อาณาจักรโรงแรมและรีสอร์ต Ruby’s Inn หน้าปากทาง Bryce Canyon NP, หอพักพนักงานใกล้ที่ทำงาน</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>🥩 Cowboy’s Buffet &amp; Steak Room (ในเครือ): Busser/Steward 17:00-22:30 น. (ขอ OT ในเครือ $22.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>🤠 Ebenezer’s Barn &amp; Grill: Food Runner งานดินเนอร์โชว์คาวบอย 18:00-22:00 น. (ได้ส่วนแบ่งทิป)</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>🛒 Ruby’s General Store &amp; Diner: แคชเชียร์/ผู้ช่วยครัว 17:00-21:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Tier A</t>
+          <t>Tier S</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Montana (MT)</t>
+          <t>Utah (UT)</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Big Sky Resort / Montage Big Sky</t>
+          <t>Park City Mountain Resort (Vail Resorts - Summer Ops)</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Acadex, Higher, IEE, IEO</t>
+          <t>OEG, Acadex, IEO</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Mountain Operations / Housekeeping</t>
+          <t>Mountain Host / Housekeeping / F&amp;B</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -4169,138 +6605,138 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>46 – 52 ชม./wk</t>
+          <t>42 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>$140</t>
+          <t>$150</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>รีสอร์ตภูเขาหรูหราไฮเอนด์, ค่าแรงฐานสูงมาก, มีรถบัส Skyline Bus ฟรี</t>
+          <t>สกีรีสอร์ตและเมืองภูเขาที่ใหญ่ที่สุดในสหรัฐฯ ซัมเมอร์มีกิจกรรมเดินป่าและปั่นจักรยาน, รถเมล์ฟรีทั้งเมือง</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>🍺 Lone Peak Brewery (Town Center): Barback/Busser 17:30-23:30 น. ($15/ชม. + ทิปสดเศรษฐี $60-$100/คืน)</t>
+          <t>🥩 High West Distillery &amp; Saloon (Main Street): Barback/Busser โรงกลั่นวิสกี้ดัง 17:30-23:30 น. (ทิปสด $80-$140/คืน)</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>🍖 The Riverhouse BBQ: Busser/Runner ร้านบาร์บีคิวริมแม่น้ำ Gallatin 17:00-22:30 น. ($14/ชม. + ทิป)</t>
+          <t>🍕 Red Banjo Pizza (Historic Main St): ล้างจาน/ผู้ช่วยครัว 18:00-23:00 น. ($16/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>🛒 Roxy’s Market Big Sky: พนักงานจัดสต็อกซูเปอร์มาร์เก็ต 18:00-22:00 น. ($17/ชม.)</t>
+          <t>🛒 Freshies Lobster Co. / Local Cafes: Food Runner 17:00-21:30 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Florida (FL)</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Universal Orlando Resort &amp; Volcano Bay</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>OEG, IEE, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>Attractions Attendant / Culinary / Lifeguard</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 22:00 (12 ชม.)</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Maryland (MD)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Premier Aquatics / High Sierra Pools (Summer Pools)</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Acadex, New Step, ALC, IEO</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Pool Lifeguard (Summer Only)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:30 – 19:30 (9 ชม.)
+พีคซัมเมอร์: 10:00 – 20:30 (10.5 ชม. สระเปิดยาว)</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>$130</t>
-        </is>
-      </c>
-      <c r="K36" s="10" t="inlineStr">
-        <is>
-          <t>สวนสนุกระดับโลก ยูนิเวอร์แซล ออร์แลนโด, ปลอดภาษีเงินได้รัฐ 0%, บัตรเข้าสวนสนุกฟรี</t>
-        </is>
-      </c>
-      <c r="L36" s="10" t="inlineStr">
-        <is>
-          <t>🎸 Universal CityWalk Eateries: Food Runner/Busser บาร์ดึก 18:30-01:00 น. (ทิปสด $60-$100/คืน)</t>
-        </is>
-      </c>
-      <c r="M36" s="10" t="inlineStr">
-        <is>
-          <t>🍔 The Cowfish Sushi Burger Bar: ล้างจาน/ผู้ช่วยครัว 19:00-01:00 น. ($15/ชม. + ทิป)</t>
-        </is>
-      </c>
-      <c r="N36" s="10" t="inlineStr">
-        <is>
-          <t>🍕 Red Oven Pizza Bakery: ผู้ช่วยทำพิซซ่ากะดึก 18:30-00:30 น.</t>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>50 – 54 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>$120</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>การันตีชั่วโมง OT แน่นอนสัปดาห์ละ 10-14 ชม., อพาร์ตเมนต์แชร์กับเพื่อน, รถไฟใต้ดิน Metro เข้า DC</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>🛒 Giant Food / Safeway: พนักงานจัดสต็อกสินค้ากะดึก 20:30-01:00 น. ($16-$17.50/ชม. มีสาขาใกล้ที่พัก)</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>🍜 Thai Tanic / Ruan Thai: ผู้ช่วยครัว/แพ็กอาหาร 20:00-23:30 น. (มีอาหารไทยฟรี)</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>🎯 Target / CVS Pharmacy: แคชเชียร์/ปิดร้าน 20:00-23:30 น. ($16.00/ชม.)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Tier A</t>
+          <t>Tier S</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Florida (FL)</t>
+          <t>Maryland (MD)</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Busch Gardens Tampa Bay &amp; Adventure Island</t>
+          <t>Ocean City Boardwalk Hotels &amp; Resorts (Summer)</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>New Step, Acadex, IEO</t>
+          <t>IEE, New Step, OEG, IEO</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Ride Operator / Lifeguard / Food Service</t>
+          <t>Housekeeping / Ride Operator</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 21:30 (11.5 ชม.)</t>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -4315,143 +6751,143 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>42 – 48 ชม./wk</t>
+          <t>44 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
+          <t>$125</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายหาด Atlantic, รถบัส Coastal Highway วิ่ง 24 ชม., หางานสองง่ายมากช่วงซัมเมอร์</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Seacrets Jamaica USA (ผับริมหาดยักษ์ใหญ่): Barback/Busser 18:00-01:30 น. ($12/ชม. + ทิปสดมหาศาล $80-$150/คืน)</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>🍟 Thrasher’s French Fries (ริมหาด): แคชเชียร์/ทอดเฟรนช์ฟรายส์ 18:00-23:00 น. ($15/ชม.)</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Shenanigans Irish Pub: ล้างจาน/ผู้ช่วยบาร์ 18:30-00:30 น. ($14/ชม. + ทิป)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Maryland (MD)</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Jolly Roger Amusement Park &amp; Splash Mountain (Ocean City)</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>New Step, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Ride Operator / Lifeguard / Park Services</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 11:00 – 19:00 (8 ชม.)
+พีคซัมเมอร์: 10:00 – 23:00 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>45 – 52 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>$120</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>สวนสนุกโรลเลอร์โคสเตอร์อันดับ 1 ในแทมปาและสวนน้ำ, ปลอดภาษีรัฐ 0%</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="inlineStr">
-        <is>
-          <t>🍺 Ybor City Historic Bars (แทมปา): Barback ผับประวัติศาสตร์ 19:00-01:30 น. (ทิปสด $60-$110/คืน)</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="inlineStr">
-        <is>
-          <t>🦀 Columbia Restaurant (ร้านสเปนชื่อดังที่สุด): Busser 18:30-23:30 น. (ทิปดี)</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="inlineStr">
-        <is>
-          <t>🍔 Portillo’s Hot Dogs Tampa: ครัว/แคชเชียร์รอบดึก 18:30-00:00 น. ($15/ชม.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Florida (FL)</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Gaylord Palms Resort &amp; Convention Center (Kissimmee)</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>OEG, Acadex, Higher</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>Housekeeping / Banquet Server / Steward</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>$20 - $50</t>
-        </is>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>44 – 50 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t>$125</t>
-        </is>
-      </c>
-      <c r="K38" s="10" t="inlineStr">
-        <is>
-          <t>รีสอร์ตศูนย์ประชุมโดมกระจกยักษ์ระดับ 4 ดาว Marriott, ปลอดภาษีรัฐ 0%</t>
-        </is>
-      </c>
-      <c r="L38" s="10" t="inlineStr">
-        <is>
-          <t>🥩 Old Hickory Steakhouse (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. (ทิปสด $70-$120)</t>
-        </is>
-      </c>
-      <c r="M38" s="10" t="inlineStr">
-        <is>
-          <t>🌴 Wreckers Sports Bar (ในรีสอร์ต): Barback ผับกีฬาจอ 2 ชั้น 18:30-00:30 น. (ขอ OT ในรีสอร์ต $24/ชม.)</t>
-        </is>
-      </c>
-      <c r="N38" s="10" t="inlineStr">
-        <is>
-          <t>🛍️ Disney Springs Eateries: Food Runner ร้านอาหารฝั่งดิสนีย์ 19:00-01:00 น.</t>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>สวนสนุกและสวนน้ำที่ใหญ่ที่สุดใน Ocean City, เล่นสวนสนุกฟรี, มีรถเมล์ผ่านหน้าสวนสนุก</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>🦀 Higgins Crab House: Busser ร้านปูยักษ์ 19:30-00:30 น. ($13/ชม. + ทิปสด $60-$90/คืน)</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>🍕 Dough Roller Pizza (Boardwalk): ล้างจาน/ทำพิซซ่ากะดึก 19:30-01:00 น. ($15/ชม.)</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>🍦 Dumser’s Dairyland: ตักไอศกรีม/แคชเชียร์ 19:00-23:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Tier A</t>
+          <t>Tier S</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Maryland (MD)</t>
+          <t>Ohio (OH)</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Premier Aquatics / High Sierra Pools (Bethesda/Rockville)</t>
+          <t>Cedar Point Amusement Park &amp; Resorts (Sandusky)</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Acadex, New Step, ALC, IEO</t>
+          <t>OEG, IEE Thailand, IEO</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Pool Lifeguard</t>
+          <t>Ride Operator / Food Service</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 10:30 – 19:30 (9 ชม.)
-พีค: 10:00 – 20:30 (10.5 ชม. สระเปิดยาว)</t>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีคซัมเมอร์: 09:30 – 22:30 (12 ชม. สวนสนุกปิดดึก)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
+          <t>ฐาน $14.50 / OT $21.75</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -4461,143 +6897,143 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>50 – 54 ชม./wk (การันตี OT)</t>
+          <t>46 – 52 ชม./wk</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>$120</t>
+          <t>$80 (ถูกสุด)</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>การันตีชั่วโมง OT แน่นอนสัปดาห์ละ 10-14 ชม., อพาร์ตเมนต์แชร์กับเพื่อน, รถไฟใต้ดิน Metro เข้า DC</t>
+          <t>สวนสนุกเครื่องเล่นระดับโลก, หอพักราคาถูกที่สุดในอเมริกา ($80/wk), รถบัสรับส่งฟรี, เล่นสวนสนุกฟรี</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>🛒 Giant Food / Safeway: พนักงานจัดสต็อกสินค้ากะดึก 20:30-01:00 น. ($16-$17.50/ชม. มีสาขาใกล้ที่พัก)</t>
+          <t>🏨 Hotel Breakers / Castaway Bay (ในสวนสนุก): ล้างจาน/แม่บ้านกะค่ำ 19:00-00:00 น. (ขอ OT ในสวนสนุก $21.75/ชม.)</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>🍜 Thai Tanic / Ruan Thai: ผู้ช่วยครัว/แพ็กอาหาร 20:00-23:30 น. (มีอาหารไทยฟรี)</t>
+          <t>🍖 Famous Dave’s BBQ (Cedar Point Marina): Busser/Dishwasher 18:30-23:30 น. ($13/ชม. + ทิปสด)</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>🎯 Target / CVS Pharmacy: แคชเชียร์/ปิดร้าน 20:00-23:30 น. ($16.00/ชม.)</t>
+          <t>🐴 Thirsty Pony / Kalahari Sandusky: Barback/Busser ร้านอาหารใกล้เคียง 19:00-00:30 น.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Maryland (MD)</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Ocean City Boardwalk Hotels &amp; Resorts</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>IEE, New Step, OEG, IEO</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>Housekeeping / Ride Operator</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Ohio (OH)</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Kings Island Amusement Park (Mason / Cincinnati)</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>OEG, IEE Thailand, IEO</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Ride Operator / Park Services / Culinary</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีคซัมเมอร์: 09:30 – 22:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>$125</t>
-        </is>
-      </c>
-      <c r="K40" s="10" t="inlineStr">
-        <is>
-          <t>เมืองตากอากาศชายหาด Atlantic, รถบัส Coastal Highway วิ่ง 24 ชม., หางานสองง่ายมาก</t>
-        </is>
-      </c>
-      <c r="L40" s="10" t="inlineStr">
-        <is>
-          <t>🌴 Seacrets Jamaica USA (ผับริมหาดยักษ์ใหญ่): Barback/Busser 18:00-01:30 น. ($12/ชม. + ทิปสดมหาศาล $80-$150/คืน)</t>
-        </is>
-      </c>
-      <c r="M40" s="10" t="inlineStr">
-        <is>
-          <t>🍟 Thrasher’s French Fries (ริมหาด): แคชเชียร์/ทอดเฟรนช์ฟรายส์ 18:00-23:00 น. ($15/ชม.)</t>
-        </is>
-      </c>
-      <c r="N40" s="10" t="inlineStr">
-        <is>
-          <t>🍺 Shenanigans Irish Pub: ล้างจาน/ผู้ช่วยบาร์ 18:30-00:30 น. ($14/ชม. + ทิป)</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>$90</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>สวนสนุกชั้นนำเครือ Cedar Fair ใกล้เมือง Cincinnati, หอพักพนักงาน + รถรับส่งฟรี</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>🍕 Mason Local Pizzerias &amp; Diners: ล้างจาน/ผู้ช่วยครัวรอบดึก 19:00-00:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>🍦 Greaters Ice Cream: พนักงานตักไอศกรีมชื่อดัง 19:00-23:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>🏨 Great Wolf Lodge Mason (ข้างๆ สวนสนุก): แม่บ้าน/ผู้ช่วยครัวกะค่ำ (ขอทำเพิ่มได้)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Tier A</t>
+          <t>Tier S</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Maryland (MD)</t>
+          <t>Colorado (CO)</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Jolly Roger Amusement Park &amp; Splash Mountain (Ocean City)</t>
+          <t>YMCA of the Rockies (Estes Park Center)</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>New Step, IEE, IEO</t>
+          <t>Higher, IEE, Acadex, IEO</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Ride Operator / Lifeguard / Park Services</t>
+          <t>Housekeeping / Food Service</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 11:00 – 19:00 (8 ชม.)
-พีค: 10:00 – 23:00 (12 ชม.)</t>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีคซัมเมอร์: 07:00 – 16:30 (9 ชม.)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
+          <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -4607,148 +7043,148 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>45 – 52 ชม./wk</t>
+          <t>42 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>$120</t>
+          <t>$110 (รวมกิน)</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>สวนสนุกและสวนน้ำที่ใหญ่ที่สุดใน Ocean City, เล่นสวนสนุกฟรี, มีรถเมล์ผ่านหน้าสวนสนุก</t>
+          <t>แคมป์รีสอร์ตกลางเทือกเขา Rocky Mountain NP, หอพัก+อาหารบุฟเฟต์ 3 มื้อ, รถชัตเติลบัสเข้าเมืองฟรี</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>🦀 Higgins Crab House: Busser ร้านปูยักษ์ 19:30-00:30 น. ($13/ชม. + ทิปสด $60-$90/คืน)</t>
+          <t>🏨 The Stanley Hotel (โรงแรมประวัติศาสตร์ The Shining): Busser/Steward ร้านอาหารหรู 17:30-23:00 น. (ทิปสด $50-$90)</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>🍕 Dough Roller Pizza (Boardwalk): ล้างจาน/ทำพิซซ่ากะดึก 19:30-01:00 น. ($15/ชม.)</t>
+          <t>🍔 Penelope’s Old Time Burgers: ผู้ช่วยครัว/ทอดเบอร์เกอร์ 17:00-21:30 น. ($15/ชม. + กินฟรี)</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>🍦 Dumser’s Dairyland: ตักไอศกรีม/แคชเชียร์ 19:00-23:30 น. ($15/ชม.)</t>
+          <t>🍺 Estes Park Brewery / Rock Cut Brewing: ล้างแก้ว/ผู้ช่วยบาร์ 18:00-22:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>Tier A</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Virginia (VA)</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Busch Gardens Williamsburg &amp; Water Country USA</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>New Step, Acadex, IEO</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>Ride Operator / Culinary Operations</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
-พีค: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึก)</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Tier S</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>South Carolina (SC)</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Myrtle Beach Oceanfront Resorts &amp; Boardwalk (Summer)</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>OEG, IEE, New Step, IEO</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Housekeeping / Lifeguard / Attractions</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>ฐาน $14.50 / OT $21.75</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>44 – 50 ชม./wk</t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>$115</t>
         </is>
       </c>
-      <c r="K42" s="10" t="inlineStr">
-        <is>
-          <t>สวนสนุกธีมยุโรปชื่อดัง, บัตรเข้าสวนสนุกและสวนน้ำฟรี, หอพักพนักงาน Williamsburg</t>
-        </is>
-      </c>
-      <c r="L42" s="10" t="inlineStr">
-        <is>
-          <t>🏰 Kingsmill Resort (ริมแม่น้ำ James River): Banquet Server/Busser งานจัดเลี้ยง 18:30-23:00 น. (ทิปสด $50-$90/คืน)</t>
-        </is>
-      </c>
-      <c r="M42" s="10" t="inlineStr">
-        <is>
-          <t>🦀 Captain George’s Seafood Buffet: Busser/Dishwasher บุฟเฟต์ซีฟู้ดยักษ์ใหญ่ 18:30-23:30 น. (คนแน่นมาก ทิปดี)</t>
-        </is>
-      </c>
-      <c r="N42" s="10" t="inlineStr">
-        <is>
-          <t>🥞 Cracker Barrel / Pancake House: ผู้ช่วยครัว/ล้างจานรอบค่ำ 18:00-22:00 น. ($14.50/ชม.)</t>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายหาดยอดนิยมอันดับ 1 ฝั่งใต้, ชายหาดยาว 60 ไมล์, เมืองเดินเท้า/จักรยาน</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>🦀 Sea Captain’s House (ร้านซีฟู้ดระดับตำนาน): Busser 17:30-23:00 น. (ทิปสด $70-$120/คืน)</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>🍕 Broadway at the Beach Eateries: Barback/Runner ศูนย์การค้าเปิดโล่ง 18:30-00:30 น. (ทิปแน่น)</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>🍦 Peaches Corner / Mad Myrtle’s Ice Cream: แคชเชียร์ริมหาด 18:00-23:30 น.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Tier A</t>
+          <t>Tier S</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Virginia (VA)</t>
+          <t>North Carolina (NC)</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Virginia Beach Oceanfront Resorts &amp; Boardwalk</t>
+          <t>Outer Banks Coastal Resorts (Nags Head / Kill Devil Hills)</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>IEE, New Step, Acadex, IEO</t>
+          <t>IEE, New Step, Acadex</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Beach Attendant</t>
+          <t>Housekeeping / Beach Operations / F&amp;B</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
+          <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>$15 - $30</t>
+          <t>$20 - $40</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -4758,27 +7194,27 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>$130</t>
+          <t>$125</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>เมืองตากอากาศชายทะเลเวอร์จิเนีย มีทางเดินเลียบหาดยาว 3 ไมล์, รถราง Wave Trolley สะดวก</t>
+          <t>หมู่เกาะตากอากาศ Outer Banks ทะเลสวย สงบ คนรวยมาพักผ่อน, บ้านพักแชร์ J-1 ริมทะเล</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>🍺 Waterman’s Surfside Grille: Barback/Busser ร้านริมหาดคนแน่น 18:00-00:30 น. (ทิปสด $70-$120/คืน)</t>
+          <t>🦞 Owens’ Restaurant (ร้านซีฟู้ดประวัติศาสตร์): Busser 17:30-23:00 น. (ทิปสด $60-$110/คืน)</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>🦀 Catch 31 Fish Bar: Food Runner/Busser 18:00-23:30 น. (ทิปดี)</t>
+          <t>🍺 Outer Banks Brewing Station: Barback ร้านคราฟต์เบียร์กังหันลม 18:00-00:30 น.</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>🍕 Dough Boy’s California Pizza: ผู้ช่วยครัว/ล้างจาน 18:30-00:00 น. ($14.50/ชม.)</t>
+          <t>🍕 Duck Donuts / Kill Devil Grill: ผู้ช่วยครัว/ทอดโดนัทกะเย็น ($15/ชม.)</t>
         </is>
       </c>
     </row>
@@ -4790,33 +7226,33 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>New Jersey (NJ)</t>
+          <t>Texas (TX)</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Morey’s Piers &amp; Beachfront Waterparks (Wildwood, NJ)</t>
+          <t>Schlitterbahn Waterpark (New Braunfels / Galveston)</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>OEG, IEE, New Step, IEO</t>
+          <t>OEG, Acadex, IEE, IEO</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Ride Operator / Lifeguard / Pier Services</t>
+          <t>Lifeguard / Park Operations</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>ปกติ: 11:00 – 19:00 (8 ชม.)
-พีค: 10:30 – 23:30 (12 ชม.)</t>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 19:30 (10 ชม.)</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
+          <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -4826,32 +7262,32 @@
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>45 – 52 ชม./wk</t>
+          <t>44 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>$120</t>
+          <t>$110</t>
         </is>
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>สวนสนุกริมสะพานปลาชานหาดที่ใหญ่ที่สุดในฝั่ง East Coast, เล่นเครื่องเล่นฟรี, เมืองจักรยาน</t>
+          <t>สวนน้ำระดับตำนานของเท็กซัส, ปลอดภาษีเงินได้รัฐ 0%, เล่นสวนน้ำฟรี</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr">
         <is>
-          <t>🍕 Mack’s Pizza / Sam’s Pizza (Boardwalk): ล้างจาน/ทำพิซซ่ากะดึก 19:30-01:30 น. ($15/ชม.)</t>
+          <t>🥩 Gristmill River Restaurant (Gruene): Busser ร้านอาหารริมแม่น้ำสุดคึกคัก 18:30-23:30 น. ($12/ชม. + ทิปสด $60-$100)</t>
         </is>
       </c>
       <c r="M44" s="10" t="inlineStr">
         <is>
-          <t>🍺 The Wharf Restaurant &amp; Bar: Barback/Busser ร้านอาหารริมน้ำ 19:00-01:00 น. (ทิปสด $70-$120/คืน)</t>
+          <t>🦫 Buc-ee’s New Braunfels (ใหญ่ที่สุดในโลก): แคชเชียร์/Food Prep กะดึก 19:00-00:00 น. ($17-$19/ชม. จ่ายหนักมาก)</t>
         </is>
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>🍦 Curley’s Fries / Kohr Brothers: แคชเชียร์/ตักไอศกรีม 19:00-23:30 น. ($15.50/ชม.)</t>
+          <t>🍺 Krause’s Cafe &amp; Biergarten: Barback/Runner ร้านเบียร์เยอรมัน 18:00-23:00 น. ($13/ชม. + ทิป)</t>
         </is>
       </c>
     </row>
@@ -4863,28 +7299,28 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>South Dakota (SD)</t>
+          <t>Texas (TX)</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Xanterra Mount Rushmore / Keystone Lodges</t>
+          <t>Kalahari Resorts &amp; Conventions Round Rock (Austin, TX)</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>OEG, IEE, Higher, IEO</t>
+          <t>OEG, Acadex, IEO</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Retail / Food Service / Housekeeping</t>
+          <t>Lifeguard / Housekeeping / F&amp;B</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 19:30 (10 ชม.)</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -4899,32 +7335,32 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>44 – 50 ชม./wk</t>
+          <t>42 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$120</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>ทำงานหน้าอนุสรณ์สถานแห่งชาติ Mount Rushmore, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
+          <t>สวนน้ำในร่มใหญ่ที่สุดในอเมริกา สาขาเท็กซัส, ปลอดภาษีรัฐ 0%, ใกล้ออสติน</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>🍔 Carver’s Cafe at Mt Rushmore: ล้างจาน/ปิดครัว 17:00-21:30 น. (ขอ OT ในอุทยาน $23.25/ชม.)</t>
+          <t>🥩 Double Cut Steak House (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. ($13/ชม. + ทิปสด $70-$120)</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>🥩 Ruby House Restaurant (Keystone): Busser ร้านอาหารธีมคาวบอยย้อนยุค 17:30-22:30 น. ($13/ชม. + ทิป)</t>
+          <t>🍕 Tom Foolerys Adventure Park (ในรีสอร์ต): คุมเครื่องเล่น/เกมรอบค่ำ 18:00-23:00 น. (ขอ OT $23.25)</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>🚂 1880 Train / Keystone Gift Shops: พนักงานร้านของฝาก/สถานีรถไฟโบราณ 17:00-21:30 น. ($15/ชม.)</t>
+          <t>🍔 Round Rock Local Eateries: Busser/ล้างจานร้านอาหารรอบนอก 18:30-23:30 น.</t>
         </is>
       </c>
     </row>
@@ -4936,33 +7372,33 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>South Dakota (SD)</t>
+          <t>Texas (TX)</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Custer State Park Resorts (State Game Lodge / Sylvan)</t>
+          <t>Six Flags Fiesta Texas &amp; SeaWorld San Antonio</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Higher, Acadex, IEO</t>
+          <t>New Step, Higher, IEE, IEO</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>Guest Service / Housekeeping</t>
+          <t>Ride Operator / Lifeguard / Culinary</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
-พีค: 07:00 – 16:30 (9 ชม.)</t>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีคซัมเมอร์: 09:30 – 21:30 (11.5 ชม.)</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
+          <t>ฐาน $14.50 / OT $21.75</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -4977,27 +7413,27 @@
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>$105 (รวมกิน)</t>
+          <t>$115</t>
         </is>
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>อุทยานธรรมชาติฝูงควายไบซัน Custer SP, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
+          <t>สวนสนุกและสวนน้ำระดับโลก ซานอันโตนิโอ, ปลอดภาษีรัฐ 0%, หอพักพนักงาน</t>
         </is>
       </c>
       <c r="L46" s="10" t="inlineStr">
         <is>
-          <t>🥩 State Game Lodge Dining Room: Busser ร้านสเต๊กควายไบซันหรู 17:00-22:00 น. ($13/ชม. + ทิปสด $50-$80)</t>
+          <t>🥩 The County Line BBQ (River Walk): Busser ร้านบาร์บีคิวริมแม่น้ำ 19:00-00:00 น. (ทิปสด $60-$100/คืน)</t>
         </is>
       </c>
       <c r="M46" s="10" t="inlineStr">
         <is>
-          <t>🍔 Black Hills Burger &amp; Bun (เมือง Custer): ล้างจาน/ครัว 17:00-21:30 น. ($15/ชม. + กินฟรี)</t>
+          <t>🎸 Hard Rock Cafe San Antonio: Food Runner/Busser 19:00-00:30 น. ($13/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="N46" s="10" t="inlineStr">
         <is>
-          <t>🏕️ Sylvan Lake General Store: พนักงานมินิมาร์ท/เช่าเรือแคนู 16:30-21:00 น.</t>
+          <t>🌮 Boudro’s on the Riverwalk: ล้างจาน/ผู้ช่วยครัว 19:00-01:00 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
@@ -5009,68 +7445,68 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>South Dakota (SD)</t>
+          <t>Texas (TX)</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Wall Drug Store (Wall, SD)</t>
+          <t>Kemah Boardwalk &amp; Galveston Pleasure Pier</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>IEE, Acadex, IEO</t>
+          <t>OEG, New Step, IEO</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Retail / Restaurant Staff / Fast Food</t>
+          <t>Ride Operator / Retail / F&amp;B</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 10:30 – 18:30 (8 ชม.)
+พีคซัมเมอร์: 10:00 – 22:30 (12 ชม.)</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
+          <t>ฐาน $14.50 / OT $21.75</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$15 - $30</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>45 – 50 ชม./wk</t>
+          <t>42 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>$85 (ถูกมาก)</t>
+          <t>$110</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>ห้างคาวบอยระดับตำนานของอเมริกา จุดแวะพักยอดฮิตก่อนเข้า Badlands NP, หอพักราคาถูก</t>
+          <t>สวนสนุกริมอ่าวเม็กซิโก เครือ Landry’s, ปลอดภาษีรัฐ 0%, บรรยากาศชายทะเล</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>☕ Wall Drug Western Art Dining Room: Busser/Steward 17:00-22:00 น. (ขอ OT ในตัว $23.25)</t>
+          <t>🦞 Aquarium Restaurant Kemah (ในเครือ): Busser ร้านอาหารใต้น้ำ 18:30-23:30 น. (ทิปสด $60-$100/คืน)</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>🍩 Wall Drug Famous Donut Kitchen: ช่วยทำโดนัท/เบเกอรี่รอบเย็น 16:30-21:00 น.</t>
+          <t>🍤 Bubba Gump Shrimp Co. (Galveston Pier): Food Runner/Busser 18:30-00:00 น. (ทิปดี)</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>🌵 Badlands Saloon &amp; Grille: Barback/ล้างจาน 18:00-23:00 น. ($14.50/ชม. + ทิป)</t>
+          <t>🏖️ The Spot (Galveston Seawall): Barback/Busser ร้านอาหารริมหาดคนแน่น 19:00-01:00 น.</t>
         </is>
       </c>
     </row>
@@ -5082,28 +7518,28 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>South Dakota (SD)</t>
+          <t>Florida (FL)</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Deadwood Historic Hotels &amp; Casinos (The Lodge at Deadwood)</t>
+          <t>Universal Orlando Resort &amp; Volcano Bay</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Higher, New Step, IEO</t>
+          <t>OEG, IEE, Acadex, IEO</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>Housekeeping / Food &amp; Beverage</t>
+          <t>Attractions Attendant / Culinary / Lifeguard</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 22:00 (12 ชม.)</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -5113,7 +7549,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>$20 - $50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="9" t="inlineStr">
@@ -5123,27 +7559,27 @@
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>$130</t>
         </is>
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>เมืองคาวบอยคาสิโนประวัติศาสตร์ ปลอดภาษีรัฐ 0%, มีรถราง Deadwood Trolley $1</t>
+          <t>สวนสนุกระดับโลก ยูนิเวอร์แซล ออร์แลนโด, ปลอดภาษีเงินได้รัฐ 0%, บัตรเข้าสวนสนุกฟรี</t>
         </is>
       </c>
       <c r="L48" s="10" t="inlineStr">
         <is>
-          <t>🥩 Deadwood Grille / O’Shea’s: Busser/Runner 17:30-23:00 น. ($13/ชม. + ทิปสด $50-$90/คืน)</t>
+          <t>🎸 Universal CityWalk Eateries: Food Runner/Busser บาร์ดึก 18:30-01:00 น. (ทิปสด $60-$100/คืน)</t>
         </is>
       </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
-          <t>🎰 Mineral Palace / Silverado Casino: Barback บาร์ในคาสิโน 18:30-01:00 น. (ทิปดี)</t>
+          <t>🍔 The Cowfish Sushi Burger Bar: ล้างจาน/ผู้ช่วยครัว 19:00-01:00 น. ($15/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="N48" s="10" t="inlineStr">
         <is>
-          <t>🍕 Mustang Sally’s Sports Bar: ผู้ช่วยครัว/ล้างจาน 18:00-00:00 น. ($14.50/ชม.)</t>
+          <t>🍕 Red Oven Pizza Bakery: ผู้ช่วยทำพิซซ่ากะดึก 18:30-00:30 น.</t>
         </is>
       </c>
     </row>
@@ -5155,33 +7591,33 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Utah (UT)</t>
+          <t>Florida (FL)</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Zion National Park Lodge (Xanterra Springdale)</t>
+          <t>Busch Gardens Tampa Bay &amp; Adventure Island</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>OEG, IEE, Acadex, IEO</t>
+          <t>New Step, Acadex, IEO</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Hospitality Crew / Housekeeping</t>
+          <t>Ride Operator / Lifeguard / Food Service</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
-พีค: 07:00 – 16:30 (9 ชม.)</t>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 21:30 (11.5 ชม.)</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $16.00 / OT $24.00</t>
+          <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -5191,32 +7627,32 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>44 – 50 ชม./wk</t>
+          <t>42 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>$110</t>
+          <t>$120</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>อุทยานแห่งชาติหุบเขาผาแดง Zion NP, มีรถชัตเติลบัสฟรีวิ่งตลอดถนน Springdale</t>
+          <t>สวนสนุกโรลเลอร์โคสเตอร์อันดับ 1 ในแทมปาและสวนน้ำ, ปลอดภาษีรัฐ 0%</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>🌮 Bit &amp; Spur Restaurant &amp; Saloon: Busser/Barback 17:30-23:00 น. ($13/ชม. + ทิปสดแขกต่างชาติ $50-$90/คืน)</t>
+          <t>🍺 Ybor City Historic Bars (แทมปา): Barback ผับประวัติศาสตร์ 19:00-01:30 น. (ทิปสด $60-$110/คืน)</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>🍔 Oscar’s Cafe (Springdale): Food Runner/Busser 17:00-22:00 น. ($13/ชม. + ทิป)</t>
+          <t>🦀 Columbia Restaurant (ร้านสเปนชื่อดังที่สุด): Busser 18:30-23:30 น. (ทิปดี)</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>🍺 Zion Canyon Brew Pub: ล้างจาน/ผู้ช่วยครัวหน้าปากทางเข้าอุทยาน 18:00-23:30 น. ($15/ชม.)</t>
+          <t>🍔 Portillo’s Hot Dogs Tampa: ครัว/แคชเชียร์รอบดึก 18:30-00:00 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
@@ -5228,68 +7664,68 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Utah (UT)</t>
+          <t>Florida (FL)</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Ruby’s Inn / Bryce Canyon Grand Hotel</t>
+          <t>Gaylord Palms Resort &amp; Convention Center (Kissimmee)</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Higher, IEE, Acadex, IEO</t>
+          <t>OEG, Acadex, Higher</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>Housekeeping / Fast Food / Retail</t>
+          <t>Housekeeping / Banquet Server / Steward</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>ฐาน $15.00 / OT $22.50</t>
+          <t>ฐาน $16.00 / OT $24.00</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$20 - $50</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>42 – 48 ชม./wk</t>
+          <t>44 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>$125</t>
         </is>
       </c>
       <c r="K50" s="10" t="inlineStr">
         <is>
-          <t>อาณาจักรโรงแรมและรีสอร์ต Ruby’s Inn หน้าปากทาง Bryce Canyon NP, หอพักพนักงานใกล้ที่ทำงาน</t>
+          <t>รีสอร์ตศูนย์ประชุมโดมกระจกยักษ์ระดับ 4 ดาว Marriott, ปลอดภาษีรัฐ 0%</t>
         </is>
       </c>
       <c r="L50" s="10" t="inlineStr">
         <is>
-          <t>🥩 Cowboy’s Buffet &amp; Steak Room (ในเครือ): Busser/Steward 17:00-22:30 น. (ขอ OT ในเครือ $22.50/ชม.)</t>
+          <t>🥩 Old Hickory Steakhouse (ในรีสอร์ต): Busser ร้านสเต๊กหรู 17:30-23:00 น. (ทิปสด $70-$120)</t>
         </is>
       </c>
       <c r="M50" s="10" t="inlineStr">
         <is>
-          <t>🤠 Ebenezer’s Barn &amp; Grill: Food Runner งานดินเนอร์โชว์คาวบอย 18:00-22:00 น. (ได้ส่วนแบ่งทิป)</t>
+          <t>🌴 Wreckers Sports Bar (ในรีสอร์ต): Barback ผับกีฬาจอ 2 ชั้น 18:30-00:30 น. (ขอ OT ในรีสอร์ต $24/ชม.)</t>
         </is>
       </c>
       <c r="N50" s="10" t="inlineStr">
         <is>
-          <t>🛒 Ruby’s General Store &amp; Diner: แคชเชียร์/ผู้ช่วยครัว 17:00-21:30 น. ($15/ชม.)</t>
+          <t>🛍️ Disney Springs Eateries: Food Runner ร้านอาหารฝั่งดิสนีย์ 19:00-01:00 น.</t>
         </is>
       </c>
     </row>
@@ -5301,33 +7737,33 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Utah (UT)</t>
+          <t>New Jersey (NJ)</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Park City Mountain Resort (Vail Resorts - Park City)</t>
+          <t>Morey’s Piers &amp; Beachfront Waterparks (Wildwood, NJ)</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>OEG, Acadex, IEO</t>
+          <t>OEG, IEE, New Step, IEO</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Mountain Host / Housekeeping / F&amp;B</t>
+          <t>Ride Operator / Lifeguard / Pier Services</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
-พีค: 08:00 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 11:00 – 19:00 (8 ชม.)
+พีคซัมเมอร์: 10:30 – 23:30 (12 ชม.)</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $17.50 / OT $26.25</t>
+          <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -5337,32 +7773,32 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>42 – 48 ชม./wk</t>
+          <t>45 – 52 ชม./wk</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>$150</t>
+          <t>$120</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>สกีรีสอร์ตและเมืองภูเขาที่ใหญ่ที่สุดในสหรัฐฯ, ระบบรถเมล์ฟรีทั้งเมือง Park City Transit</t>
+          <t>สวนสนุกริมสะพานปลาชานหาดที่ใหญ่ที่สุดในฝั่ง East Coast เปิดเฉพาะซัมเมอร์, เล่นเครื่องเล่นฟรี</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>🥩 High West Distillery &amp; Saloon (Main Street): Barback/Busser โรงกลั่นวิสกี้ดัง 17:30-23:30 น. (ทิปสด $80-$140/คืน)</t>
+          <t>🍕 Mack’s Pizza / Sam’s Pizza (Boardwalk): ล้างจาน/ทำพิซซ่ากะดึก 19:30-01:30 น. ($15/ชม.)</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>🍕 Red Banjo Pizza (Historic Main St): ล้างจาน/ผู้ช่วยครัว 18:00-23:00 น. ($16/ชม. + ทิป)</t>
+          <t>🍺 The Wharf Restaurant &amp; Bar: Barback/Busser ร้านอาหารริมน้ำ 19:00-01:00 น. (ทิปสด $70-$120/คืน)</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>🛒 Freshies Lobster Co. / Local Cafes: Food Runner 17:00-21:30 น. ($15/ชม. + ทิป)</t>
+          <t>🍦 Curley’s Fries / Kohr Brothers: แคชเชียร์/ตักไอศกรีม 19:00-23:30 น. ($15.50/ชม.)</t>
         </is>
       </c>
     </row>
@@ -5374,33 +7810,33 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Maine (ME)</t>
+          <t>South Dakota (SD)</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Bar Harbor Grand Hotel / Harborside Hotel</t>
+          <t>Xanterra Mount Rushmore / Keystone Lodges</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Acadex, OEG, Higher, IEO</t>
+          <t>OEG, IEE, Higher, IEO</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Housekeeping / Laundry</t>
+          <t>Retail / Food Service / Housekeeping</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>ฐาน $16.50 / OT $24.75</t>
+          <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -5415,27 +7851,27 @@
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>$130</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="K52" s="10" t="inlineStr">
         <is>
-          <t>เมืองตากอากาศชายทะเล Bar Harbor &amp; อุทยาน Acadia NP, รถบัส Island Explorer ฟรี</t>
+          <t>ทำงานหน้าอนุสรณ์สถานแห่งชาติ Mount Rushmore, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
         </is>
       </c>
       <c r="L52" s="10" t="inlineStr">
         <is>
-          <t>🦞 Stewman’s Lobster Pound (ริมทะเล): Busser/Barback ร้านกุ้งล็อบสเตอร์ 17:30-23:00 น. ($13/ชม. + ทิปสด $60-$120/คืน)</t>
+          <t>🍔 Carver’s Cafe at Mt Rushmore: ล้างจาน/ปิดครัว 17:00-21:30 น. (ขอ OT ในอุทยาน $23.25/ชม.)</t>
         </is>
       </c>
       <c r="M52" s="10" t="inlineStr">
         <is>
-          <t>🍺 Geddy’s Down Under / The Chart Room: Busser/Runner 18:00-23:30 น. (ทิปสดแน่นมาก)</t>
+          <t>🥩 Ruby House Restaurant (Keystone): Busser ร้านอาหารธีมคาวบอยย้อนยุค 17:30-22:30 น. ($13/ชม. + ทิป)</t>
         </is>
       </c>
       <c r="N52" s="10" t="inlineStr">
         <is>
-          <t>🍦 Ben &amp; Bill’s Chocolate Emporium: พนักงานตักไอศกรีม/แคชเชียร์ 17:00-22:00 น. ($15.50/ชม.)</t>
+          <t>🚂 1880 Train / Keystone Gift Shops: พนักงานร้านของฝาก/สถานีรถไฟโบราณ 17:00-21:30 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>
@@ -5447,12 +7883,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Maine (ME)</t>
+          <t>South Dakota (SD)</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Cliff House Maine (Cape Neddick / Ogunquit)</t>
+          <t>Custer State Park Resorts (State Game Lodge / Sylvan)</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -5462,18 +7898,18 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Culinary / Stewarding</t>
+          <t>Guest Service / Housekeeping</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
-พีค: 07:30 – 17:30 (9.5 ชม.)</t>
+          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
+พีคซัมเมอร์: 07:00 – 16:30 (9 ชม.)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $17.00 / OT $25.50</t>
+          <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -5488,27 +7924,27 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>$135</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>รีสอร์ตหรูบนหน้าผาริมมหาสมุทรแอตแลนติก แขกไฮเอนด์ระดับมหาเศรษฐีบอสตันและนิวยอร์ก</t>
+          <t>อุทยานธรรมชาติฝูงควายไบซัน Custer SP, ปลอดภาษีรัฐ 0%, หอพัก+อาหาร EDR</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>🦞 The Tiller Restaurant (ในรีสอร์ต): Busser ร้าน Fine Dining วิวมหาสมุทร 17:30-23:00 น. (ทิปสด $70-$130/คืน)</t>
+          <t>🥩 State Game Lodge Dining Room: Busser ร้านสเต๊กควายไบซันหรู 17:00-22:00 น. ($13/ชม. + ทิปสด $50-$80)</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>🍺 Nubb’s Lobster Shack (ในรีสอร์ต): Food Runner/Barback 17:00-22:30 น. (ขอ OT ในรีสอร์ต $25.50)</t>
+          <t>🍔 Black Hills Burger &amp; Bun (เมือง Custer): ล้างจาน/ครัว 17:00-21:30 น. ($15/ชม. + กินฟรี)</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>🍦 Ogunquit Beach Cafes: ผู้ช่วยครัว/บริการรอบเย็น</t>
+          <t>🏕️ Sylvan Lake General Store: พนักงานมินิมาร์ท/เช่าเรือแคนู 16:30-21:00 น.</t>
         </is>
       </c>
     </row>
@@ -5520,68 +7956,68 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Maine (ME)</t>
+          <t>South Dakota (SD)</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>The Nonantum Resort (Kennebunkport, ME)</t>
+          <t>Wall Drug Store (Wall, SD)</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Higher, Acadex, IEO</t>
+          <t>IEE, Acadex, IEO</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Housekeeping / Banquet / F&amp;B</t>
+          <t>Retail / Restaurant Staff / Fast Food</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
-พีค: 07:30 – 17:00 (9.5 ชม.)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>ฐาน $16.50 / OT $24.75</t>
+          <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>$20 - $50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>42 – 48 ชม./wk</t>
+          <t>45 – 50 ชม./wk</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>$125</t>
+          <t>$85 (ถูกมาก)</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t>รีสอร์ตตากอากาศริมน้ำประวัติศาสตร์ เมืองของประธานาธิบดีบุช, หอพักพนักงาน Kennebunkport</t>
+          <t>ห้างคาวบอยระดับตำนานของอเมริกา จุดแวะพักยอดฮิตก่อนเข้า Badlands NP, หอพักราคาถูก</t>
         </is>
       </c>
       <c r="L54" s="10" t="inlineStr">
         <is>
-          <t>🦞 The Clam Shack (สะพาน Kennebunkport): ล้างจาน/ทอดซีฟู้ดร้านดัง 17:30-22:30 น. ($16/ชม. + ทิป)</t>
+          <t>☕ Wall Drug Western Art Dining Room: Busser/Steward 17:00-22:00 น. (ขอ OT ในตัว $23.25)</t>
         </is>
       </c>
       <c r="M54" s="10" t="inlineStr">
         <is>
-          <t>🥩 Ocean Restaurant: Busser ร้านอาหารหรูริมน้ำ 18:00-23:00 น. (ทิปสด $60-$100/คืน)</t>
+          <t>🍩 Wall Drug Famous Donut Kitchen: ช่วยทำโดนัท/เบเกอรี่รอบเย็น 16:30-21:00 น.</t>
         </is>
       </c>
       <c r="N54" s="10" t="inlineStr">
         <is>
-          <t>🍦 Rococo Artisan Ice Cream: ตักไอศกรีม 17:00-22:00 น. ($15/ชม.)</t>
+          <t>🌵 Badlands Saloon &amp; Grille: Barback/ล้างจาน 18:00-23:00 น. ($14.50/ชม. + ทิป)</t>
         </is>
       </c>
     </row>
@@ -5593,68 +8029,68 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Ohio (OH)</t>
+          <t>South Dakota (SD)</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Cedar Point Amusement Park &amp; Resorts (Sandusky)</t>
+          <t>Deadwood Historic Hotels &amp; Casinos (The Lodge at Deadwood)</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>OEG, IEE Thailand, IEO</t>
+          <t>Higher, New Step, IEO</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Ride Operator / Food Service</t>
+          <t>Housekeeping / Food &amp; Beverage</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
-พีค: 09:30 – 22:30 (12 ชม. สวนสนุกปิดดึก)</t>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $14.50 / OT $21.75</t>
+          <t>ฐาน $15.50 / OT $23.25</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>$20 - $50</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>46 – 52 ชม./wk</t>
+          <t>42 – 48 ชม./wk</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>$80 (ถูกสุด)</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>สวนสนุกเครื่องเล่นระดับโลก, หอพักราคาถูกที่สุดในอเมริกา ($80/wk), รถบัสรับส่งฟรี, เล่นสวนสนุกฟรี</t>
+          <t>เมืองคาวบอยคาสิโนประวัติศาสตร์ ปลอดภาษีรัฐ 0%, มีรถราง Deadwood Trolley $1</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>🏨 Hotel Breakers / Castaway Bay (ในสวนสนุก): ล้างจาน/แม่บ้านกะค่ำ 19:00-00:00 น. (ขอ OT ในสวนสนุก $21.75/ชม.)</t>
+          <t>🥩 Deadwood Grille / O’Shea’s: Busser/Runner 17:30-23:00 น. ($13/ชม. + ทิปสด $50-$90/คืน)</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
         <is>
-          <t>🍖 Famous Dave’s BBQ (Cedar Point Marina): Busser/Dishwasher 18:30-23:30 น. ($13/ชม. + ทิปสด)</t>
+          <t>🎰 Mineral Palace / Silverado Casino: Barback บาร์ในคาสิโน 18:30-01:00 น. (ทิปดี)</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>🐴 Thirsty Pony / Kalahari Sandusky: Barback/Busser ร้านอาหารใกล้เคียง 19:00-00:30 น.</t>
+          <t>🍕 Mustang Sally’s Sports Bar: ผู้ช่วยครัว/ล้างจาน 18:00-00:00 น. ($14.50/ชม.)</t>
         </is>
       </c>
     </row>
@@ -5666,28 +8102,28 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Ohio (OH)</t>
+          <t>Virginia (VA)</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Kings Island Amusement Park (Mason / Cincinnati)</t>
+          <t>Busch Gardens Williamsburg &amp; Water Country USA</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>OEG, IEE Thailand, IEO</t>
+          <t>New Step, Acadex, IEO</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>Ride Operator / Park Services / Culinary</t>
+          <t>Ride Operator / Culinary Operations</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
-พีค: 09:30 – 22:30 (12 ชม.)</t>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 21:30 (12 ชม. สวนสนุกเปิดดึก)</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
@@ -5707,27 +8143,27 @@
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>$90</t>
+          <t>$115</t>
         </is>
       </c>
       <c r="K56" s="10" t="inlineStr">
         <is>
-          <t>สวนสนุกชั้นนำเครือ Cedar Fair ใกล้เมือง Cincinnati, หอพักพนักงาน + รถรับส่งฟรี</t>
+          <t>สวนสนุกธีมยุโรปชื่อดัง, บัตรเข้าสวนสนุกและสวนน้ำฟรี, หอพักพนักงาน Williamsburg</t>
         </is>
       </c>
       <c r="L56" s="10" t="inlineStr">
         <is>
-          <t>🍕 Mason Local Pizzerias &amp; Diners: ล้างจาน/ผู้ช่วยครัวรอบดึก 19:00-00:00 น. ($14.50/ชม.)</t>
+          <t>🏰 Kingsmill Resort (ริมแม่น้ำ James River): Banquet Server/Busser งานจัดเลี้ยง 18:30-23:00 น. (ทิปสด $50-$90/คืน)</t>
         </is>
       </c>
       <c r="M56" s="10" t="inlineStr">
         <is>
-          <t>🍦 Greaters Ice Cream: พนักงานตักไอศกรีมชื่อดัง 19:00-23:00 น. ($14.50/ชม.)</t>
+          <t>🦀 Captain George’s Seafood Buffet: Busser/Dishwasher บุฟเฟต์ซีฟู้ดยักษ์ใหญ่ 18:30-23:30 น. (คนแน่นมาก ทิปดี)</t>
         </is>
       </c>
       <c r="N56" s="10" t="inlineStr">
         <is>
-          <t>🏨 Great Wolf Lodge Mason (ข้างๆ สวนสนุก): แม่บ้าน/ผู้ช่วยครัวกะค่ำ (ขอทำเพิ่มได้)</t>
+          <t>🥞 Cracker Barrel / Pancake House: ผู้ช่วยครัว/ล้างจานรอบค่ำ 18:00-22:00 น. ($14.50/ชม.)</t>
         </is>
       </c>
     </row>
@@ -5739,68 +8175,360 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Colorado (CO)</t>
+          <t>Virginia (VA)</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>YMCA of the Rockies (Estes Park Center)</t>
+          <t>Virginia Beach Oceanfront Resorts &amp; Boardwalk</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Higher, IEE, Acadex, IEO</t>
+          <t>IEE, New Step, Acadex, IEO</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Housekeeping / Food Service</t>
+          <t>Housekeeping / Beach Attendant</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>ปกติ: 07:30 – 15:30 (8 ชม.)
-พีค: 07:00 – 16:30 (9 ชม.)</t>
+          <t>ปกติ: 08:30 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 08:00 – 17:30 (9.5 ชม.)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>ฐาน $15.50 / OT $23.25</t>
+          <t>ฐาน $15.00 / OT $22.50</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
+          <t>$15 - $30</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>$130</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>เมืองตากอากาศชายทะเลเวอร์จิเนีย มีทางเดินเลียบหาดยาว 3 ไมล์, รถราง Wave Trolley สะดวก</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Waterman’s Surfside Grille: Barback/Busser ร้านริมหาดคนแน่น 18:00-00:30 น. (ทิปสด $70-$120/คืน)</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>🦀 Catch 31 Fish Bar: Food Runner/Busser 18:00-23:30 น. (ทิปดี)</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Dough Boy’s California Pizza: ผู้ช่วยครัว/ล้างจาน 18:30-00:00 น. ($14.50/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Massachusetts (MA)</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Cape Cod Oceanfront Resorts &amp; Inns (Hyannis / Yarmouth)</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>OEG, IEE, Acadex, Higher</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>Housekeeping / Banquet / F&amp;B</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:00 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:00 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $16.50 / OT $24.75</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>$20 - $50</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>42 – 48 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>$135</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>แหลมตากอากาศระดับตำนานของตระกูลเคนเนดี้ Cape Cod, ปั่นจักรยานเลียบหาดสะดวก</t>
+        </is>
+      </c>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>🦞 The Lobster Pot (Provincetown): Busser/Steward ร้านซีฟู้ดดัง 17:30-23:30 น. (ทิปสด $70-$130/คืน)</t>
+        </is>
+      </c>
+      <c r="M58" s="10" t="inlineStr">
+        <is>
+          <t>🍔 The Black Cat Tavern (Hyannis Harbor): Food Runner/Busser 18:00-00:00 น. (ทิปดี)</t>
+        </is>
+      </c>
+      <c r="N58" s="10" t="inlineStr">
+        <is>
+          <t>🍦 Four Seas Ice Cream: ตักไอศกรีมกะค่ำ 18:00-22:30 น. ($16.00/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>New Hampshire (NH)</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Omni Mount Washington Resort (Bretton Woods)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>OEG, Acadex, IEO</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Housekeeping / Culinary / Steward</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 08:00 – 16:30 (8 ชม.)
+พีคซัมเมอร์: 07:30 – 17:30 (9.5 ชม.)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $16.00 / OT $24.00</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>$15 - $35</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>$110 (รวมกิน)</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>โรงแรมปราสาทประวัติศาสตร์ระดับ 4 ดาวหน้าเทือกเขา White Mountains, ปลอดภาษีซื้อ 0% Sales Tax</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>🥩 Main Dining Room (ในโรงแรม): Busser ร้าน Fine Dining 17:30-23:00 น. (ทิปสด $60-$100/คืน)</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>🍺 The Cave (ผับใต้ดินในโรงแรม): Barback บาร์ยุค Prohibition 19:00-01:00 น. (ขอ OT ในรีสอร์ต $24)</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Fabyan’s Station Restaurant: ล้างจาน/ผู้ช่วยครัว 17:30-22:30 น. ($15/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Missouri (MO)</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Silver Dollar City Theme Park &amp; Showboat Branson Belle</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>New Step, IEE, IEO</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Ride Operator / Attractions Host / Culinary</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>ปกติ: 09:30 – 18:00 (8 ชม.)
+พีคซัมเมอร์: 09:00 – 21:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>ฐาน $14.50 / OT $21.75</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>42 – 48 ชม./wk</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>$110 (รวมกิน)</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>แคมป์รีสอร์ตกลางเทือกเขา Rocky Mountain NP, หอพัก+อาหารบุฟเฟต์ 3 มื้อ, รถชัตเติลบัสเข้าเมืองฟรี</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>🏨 The Stanley Hotel (โรงแรมประวัติศาสตร์ The Shining): Busser/Steward ร้านอาหารหรู 17:30-23:00 น. (ทิปสด $50-$90)</t>
-        </is>
-      </c>
-      <c r="M57" s="7" t="inlineStr">
-        <is>
-          <t>🍔 Penelope’s Old Time Burgers: ผู้ช่วยครัว/ทอดเบอร์เกอร์ 17:00-21:30 น. ($15/ชม. + กินฟรี)</t>
-        </is>
-      </c>
-      <c r="N57" s="7" t="inlineStr">
-        <is>
-          <t>🍺 Estes Park Brewery / Rock Cut Brewing: ล้างแก้ว/ผู้ช่วยบาร์ 18:00-22:30 น. ($15/ชม.)</t>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>$95</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>สวนสนุกธีมยุคคาวบอย 1880s และเรือสำราญดินเนอร์โชว์ Branson, ค่าครองชีพถูกมาก</t>
+        </is>
+      </c>
+      <c r="L60" s="10" t="inlineStr">
+        <is>
+          <t>🚢 Showboat Branson Belle (เรือสำราญ): Banquet Server/Busser 18:00-22:30 น. (ทิปสด $50-$90/รอบ)</t>
+        </is>
+      </c>
+      <c r="M60" s="10" t="inlineStr">
+        <is>
+          <t>🥩 Guy Fieri’s Branson Kitchen: Food Runner/Busser 18:30-23:30 น. ($13/ชม. + ทิป)</t>
+        </is>
+      </c>
+      <c r="N60" s="10" t="inlineStr">
+        <is>
+          <t>🥞 Billy Gail’s Cafe: ผู้ช่วยเตรียมวัตถุดิบ/ล้างจานรอบบ่าย-เย็น ($14.50/ชม.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Pennsylvania (PA)</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Hersheypark &amp; The Hotel Hershey</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>OEG, IEE, New Step</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Ride Operator / Food Service / Housekeeping</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>ปกติ: 10:00 – 18:30 (8 ชม.)
+พีคซัมเมอร์: 09:30 – 22:30 (12 ชม.)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>ฐาน $15.00 / OT $22.50</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>44 – 50 ชม./wk</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>$110</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>สวนสนุกเมืองช็อกโกแลต Hershey, หอพักพนักงาน Hershey Co-Op + รถรับส่งฟรี, เข้าสวนสนุกฟรี</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>🍫 The Circular at The Hotel Hershey: Busser ร้านอาหารหรู 17:30-23:00 น. (ทิปสด $60-$110/คืน)</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>🍺 Troegs Independent Brewing: Barback โรงเบียร์ดังข้างสวนสนุก 18:30-00:00 น. (ทิปดีมาก)</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>🍕 Hershey Grill / Local Diners: ล้างจาน/ผู้ช่วยครัว 18:00-23:00 น. ($15/ชม.)</t>
         </is>
       </c>
     </row>

--- a/Work_and_Travel_Master_Job_Database_2027.xlsx
+++ b/Work_and_Travel_Master_Job_Database_2027.xlsx
@@ -9,8 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top Employers (Summer Only)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier S-A Summer Jobs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summer 12-Week Simulator" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summer Agency Directory" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summer Agency Directory" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,10 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0฿"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -94,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -125,12 +121,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8543,834 +8533,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="79" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
-    <col width="31" customWidth="1" min="16" max="16"/>
-    <col width="35" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>สัปดาห์ (Summer Week)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ช่วงวันที่ (Summer Timeline)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>สถานการณ์ &amp; รายละเอียดกะงานซัมเมอร์</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ชม. งานหลัก (ชม.)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ชม. งานสอง (ชม.)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>รวม ชม./สัปดาห์</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>รายรับงานหลัก ($)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>รายรับงานสอง ($)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>เงินทิปสด ($)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>รายรับรวมรายสัปดาห์ ($)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>รายรับรวม (บาท)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>หักภาษี Fed 10% ($)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>หักหอพัก/EDR ($)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>หักของใช้ส่วนตัว ($)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>เงินสดสุทธิสัปดาห์นั้น ($)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>เงินสดสะสมคงเหลือ ($)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>เงินสดสะสมคงเหลือ (บาท)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Week 1</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>7 พ.ค. - 14 พ.ค.</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>เดินทางถึง, ปฐมนิเทศ, อบรม, ทำ SSN ที่แฟร์แบงก์ส</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="G2" s="11" t="n">
-        <v>512</v>
-      </c>
-      <c r="H2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="11" t="n">
-        <v>512</v>
-      </c>
-      <c r="K2" s="12" t="n">
-        <v>16819</v>
-      </c>
-      <c r="L2" s="11" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="M2" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="N2" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="O2" s="11" t="n">
-        <v>330.8</v>
-      </c>
-      <c r="P2" s="11" t="n">
-        <v>330.8</v>
-      </c>
-      <c r="Q2" s="12" t="n">
-        <v>10867</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Week 2</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>15 พ.ค. - 21 พ.ค.</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>เปิดซีซันซัมเมอร์, เรือสำราญรอบแรกเข้า, สมัครงาน 2</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>608</v>
-      </c>
-      <c r="H3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>608</v>
-      </c>
-      <c r="K3" s="12" t="n">
-        <v>19973</v>
-      </c>
-      <c r="L3" s="11" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="M3" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="N3" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="O3" s="11" t="n">
-        <v>417.2</v>
-      </c>
-      <c r="P3" s="11" t="n">
-        <v>748</v>
-      </c>
-      <c r="Q3" s="12" t="n">
-        <v>24572</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>22 พ.ค. - 28 พ.ค. (Memorial Day)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>วันหยุด Memorial Day เปิดซัมเมอร์เต็มรูปแบบ งานสองเริ่มทำ</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>832</v>
-      </c>
-      <c r="H4" s="11" t="n">
-        <v>150</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>1042</v>
-      </c>
-      <c r="K4" s="12" t="n">
-        <v>34230</v>
-      </c>
-      <c r="L4" s="11" t="n">
-        <v>104.2</v>
-      </c>
-      <c r="M4" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="N4" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="O4" s="11" t="n">
-        <v>807.8</v>
-      </c>
-      <c r="P4" s="11" t="n">
-        <v>1555.8</v>
-      </c>
-      <c r="Q4" s="12" t="n">
-        <v>51108</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>29 พ.ค. - 4 มิ.ย.</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>รถไฟทัวร์แน่น, เข้าที่เต็มตัว, งานสอง Barback 4 วัน</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>976</v>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>1306</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <v>42902</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>130.6</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="N5" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="O5" s="11" t="n">
-        <v>1045.4</v>
-      </c>
-      <c r="P5" s="11" t="n">
-        <v>2601.2</v>
-      </c>
-      <c r="Q5" s="12" t="n">
-        <v>85449</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Week 5</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>5 มิ.ย. - 11 มิ.ย.</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>ช่วง Midnight Sun สว่าง 24 ชม. แขกแน่นตลอดคืน</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>1024</v>
-      </c>
-      <c r="H6" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>140</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>1374</v>
-      </c>
-      <c r="K6" s="12" t="n">
-        <v>45136</v>
-      </c>
-      <c r="L6" s="11" t="n">
-        <v>137.4</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="N6" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="O6" s="11" t="n">
-        <v>1106.6</v>
-      </c>
-      <c r="P6" s="11" t="n">
-        <v>3707.8</v>
-      </c>
-      <c r="Q6" s="12" t="n">
-        <v>121801</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Week 6</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>12 มิ.ย. - 18 มิ.ย.</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>PEAK ซัมเมอร์ เรือสำราญและรถไฟเข้าเต็มพิกัด</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>1024</v>
-      </c>
-      <c r="H7" s="11" t="n">
-        <v>210</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>140</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>1374</v>
-      </c>
-      <c r="K7" s="12" t="n">
-        <v>45136</v>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>137.4</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="O7" s="11" t="n">
-        <v>1106.6</v>
-      </c>
-      <c r="P7" s="11" t="n">
-        <v>4814.4</v>
-      </c>
-      <c r="Q7" s="12" t="n">
-        <v>158153</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Week 7</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>19 มิ.ย. - 25 มิ.ย.</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>ฝนตกในหุบเขา/รถไฟดีเลย์ ร่างกายเริ่มล้า พักผ่อน</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>736</v>
-      </c>
-      <c r="H8" s="11" t="n">
-        <v>180</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>996</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>32719</v>
-      </c>
-      <c r="L8" s="11" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="M8" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>766.4</v>
-      </c>
-      <c r="P8" s="11" t="n">
-        <v>5580.8</v>
-      </c>
-      <c r="Q8" s="12" t="n">
-        <v>183330</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Week 8</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>26 มิ.ย. - 4 ก.ค. (4th of July PEAK)</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>วันชาติอเมริกา PEAK ที่สุดในรอบปี แขกล้น ทิปมหาศาล</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>1072</v>
-      </c>
-      <c r="H9" s="11" t="n">
-        <v>225</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>160</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>1457</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>47862</v>
-      </c>
-      <c r="L9" s="11" t="n">
-        <v>145.7</v>
-      </c>
-      <c r="M9" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="N9" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="O9" s="11" t="n">
-        <v>1181.3</v>
-      </c>
-      <c r="P9" s="11" t="n">
-        <v>6762.1</v>
-      </c>
-      <c r="Q9" s="12" t="n">
-        <v>222135</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Week 9</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>5 ก.ค. - 15 ก.ค.</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>ช่วงพีคต่อเนื่อง นักท่องเที่ยวครอบครัวสหรัฐฯ แน่น</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>928</v>
-      </c>
-      <c r="H10" s="11" t="n">
-        <v>180</v>
-      </c>
-      <c r="I10" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>1228</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>40340</v>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>122.8</v>
-      </c>
-      <c r="M10" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="N10" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="O10" s="11" t="n">
-        <v>975.2</v>
-      </c>
-      <c r="P10" s="11" t="n">
-        <v>7737.3</v>
-      </c>
-      <c r="Q10" s="12" t="n">
-        <v>254171</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Week 10</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>16 ก.ค. - 31 ก.ค.</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>เข้าสู่ปลายซัมเมอร์ นักศึกษาฝรั่งเริ่มทยอยกลับ</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>832</v>
-      </c>
-      <c r="H11" s="11" t="n">
-        <v>150</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>1082</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>35544</v>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>108.2</v>
-      </c>
-      <c r="M11" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="O11" s="11" t="n">
-        <v>843.8</v>
-      </c>
-      <c r="P11" s="11" t="n">
-        <v>8581.1</v>
-      </c>
-      <c r="Q11" s="12" t="n">
-        <v>281890</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Week 11</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>1 ส.ค. - 15 ส.ค.</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>ใบไม้เริ่มเปลี่ยนสี ทัวร์ซา ปิดห้องพักบางโซน</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>736</v>
-      </c>
-      <c r="H12" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>916</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>30091</v>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="M12" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="N12" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="O12" s="11" t="n">
-        <v>694.4</v>
-      </c>
-      <c r="P12" s="11" t="n">
-        <v>9275.5</v>
-      </c>
-      <c r="Q12" s="12" t="n">
-        <v>304701</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Week 12</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>16 ส.ค. - 7 ก.ย. (Wrap Up)</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>สัปดาห์สุดท้าย เคลียร์ห้อง ปิดซีซันซัมเมอร์ คืนมัดจำ</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>576</v>
-      </c>
-      <c r="H13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>576</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>18922</v>
-      </c>
-      <c r="L13" s="11" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="M13" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="N13" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="O13" s="11" t="n">
-        <v>388.4</v>
-      </c>
-      <c r="P13" s="11" t="n">
-        <v>9663.9</v>
-      </c>
-      <c r="Q13" s="12" t="n">
-        <v>317459</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Work_and_Travel_Master_Job_Database_2027.xlsx
+++ b/Work_and_Travel_Master_Job_Database_2027.xlsx
@@ -1073,12 +1073,12 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>$0 (ฟรี!)</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), ส่วนลด 40%, บัตรผ่าน 2 อุทยานฟรี</t>
+          <t>หอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR ตักไม่อั้น 7 วัน ($105/wk), ส่วนลดซื้อของ 40%, เข้าอุทยาน Grand Teton &amp; Yellowstone ฟรี</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>$0 (ฟรี!)</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), หมู่บ้านริมทะเลสาบ Jackson Lake</t>
+          <t>หอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), หมู่บ้านริมทะเลสาบ Jackson Lake สวยที่สุดในซัมเมอร์</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>$0 (ฟรี!)</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), ส่วนลด 40%, บัตรผ่าน 2 อุทยานฟรี</t>
+          <t>หอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR ตักไม่อั้น 7 วัน ($105/wk), ส่วนลดซื้อของ 40%, เข้าอุทยาน Grand Teton &amp; Yellowstone ฟรี</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>$0 (ฟรี!)</t>
+          <t>$105</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>หอพักฟรี 100%! + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), หมู่บ้านริมทะเลสาบ Jackson Lake</t>
+          <t>หอพัก + อาหารบุฟเฟต์ 3 มื้อ EDR ($105/wk), หมู่บ้านริมทะเลสาบ Jackson Lake สวยที่สุดในซัมเมอร์</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">

--- a/Work_and_Travel_Master_Job_Database_2027.xlsx
+++ b/Work_and_Travel_Master_Job_Database_2027.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K52" s="10" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>$105</t>
+          <t>$105 (รวมกิน)</t>
         </is>
       </c>
       <c r="K52" s="10" t="inlineStr">
